--- a/data/germany/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
+++ b/data/germany/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:BN1"/>
+  <dimension ref="A1:BN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -754,6 +758,1618 @@
           <t>sum_pot_player_miss_away</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>vJqPCEPP</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>45508.35416666666</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kampka r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">merck stadion am bollenfalltor
+  darmstadt </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>17810</v>
+      </c>
+      <c r="F2" t="n">
+        <v>17810</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>S0hPB9rA</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ne1oL3y7</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M2" t="n">
+        <v>47</v>
+      </c>
+      <c r="N2" t="n">
+        <v>53</v>
+      </c>
+      <c r="O2" t="n">
+        <v>11</v>
+      </c>
+      <c r="P2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>6</v>
+      </c>
+      <c r="R2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S2" t="n">
+        <v>16</v>
+      </c>
+      <c r="T2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>MDhPV0RQ</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>AoL97rX8</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>59</v>
+      </c>
+      <c r="X2" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>183.3</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>2490000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>74</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>25.6875</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>186.25</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1679687.5</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>73.1875</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>21.95454545454545</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>186.4545454545455</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>64.04545454545455</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1346590.909090909</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>72.95454545454545</v>
+      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>2Hl43AnC</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45508.35416666666</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hempel r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sportpark ronhof thomas sommer
+  furth </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>16626</v>
+      </c>
+      <c r="F3" t="n">
+        <v>12664</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>zedZaSL7</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="M3" t="n">
+        <v>47</v>
+      </c>
+      <c r="N3" t="n">
+        <v>53</v>
+      </c>
+      <c r="O3" t="n">
+        <v>22</v>
+      </c>
+      <c r="P3" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>9</v>
+      </c>
+      <c r="R3" t="n">
+        <v>5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>9</v>
+      </c>
+      <c r="T3" t="n">
+        <v>11</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>8E86CPuD</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>pdPRS0me</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>59</v>
+      </c>
+      <c r="X3" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>183.1</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>67</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1480000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>22.72727272727273</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>182.5454545454545</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>64.59090909090909</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1273863.636363636</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>72.86363636363636</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>25.57142857142857</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>181.8571428571429</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>66.71428571428571</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1175000</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>68.42857142857143</v>
+      </c>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>SIOxI915</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45508.35416666666</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schroder r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">donaustadion
+  ulm </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>19500</v>
+      </c>
+      <c r="F4" t="n">
+        <v>17400</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>tbC3EcQn</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>54</v>
+      </c>
+      <c r="N4" t="n">
+        <v>46</v>
+      </c>
+      <c r="O4" t="n">
+        <v>12</v>
+      </c>
+      <c r="P4" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S4" t="n">
+        <v>12</v>
+      </c>
+      <c r="T4" t="n">
+        <v>16</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>QevvB2nf</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>4bJLk19p</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>59</v>
+      </c>
+      <c r="X4" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>184.6363636363636</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>67.63636363636364</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1484090.909090909</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>70.63636363636364</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="n">
+        <v>25.22222222222222</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>180.9444444444445</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1468055.555555556</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>71.11111111111111</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>EeIMLi2t</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45507.64583333334</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stieler t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">veltins arena
+  gelsenkirchen </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>62271</v>
+      </c>
+      <c r="F5" t="n">
+        <v>61000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M5" t="n">
+        <v>52</v>
+      </c>
+      <c r="N5" t="n">
+        <v>48</v>
+      </c>
+      <c r="O5" t="n">
+        <v>14</v>
+      </c>
+      <c r="P5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+      <c r="R5" t="n">
+        <v>5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>13</v>
+      </c>
+      <c r="T5" t="n">
+        <v>11</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>txZLBQVC</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>SQrxFAMl</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>59</v>
+      </c>
+      <c r="X5" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>187.125</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>69</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1740625</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>183.25</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>66.875</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1287500</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>27.22222222222222</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>190.2222222222222</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>67.94444444444444</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1294444.444444444</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>70.88888888888889</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>24.57142857142857</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>184.9285714285714</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>66.07142857142857</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1302142.857142857</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>71.14285714285714</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>fiod5WHa</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45507.33333333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bacher m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heinz von heiden arena
+  hannover </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>49200</v>
+      </c>
+      <c r="F6" t="n">
+        <v>31800</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>UiCmEP56</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="M6" t="n">
+        <v>58</v>
+      </c>
+      <c r="N6" t="n">
+        <v>42</v>
+      </c>
+      <c r="O6" t="n">
+        <v>16</v>
+      </c>
+      <c r="P6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>12</v>
+      </c>
+      <c r="T6" t="n">
+        <v>17</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>t0ZPdkUl</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>zyLSrbZQ</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>59</v>
+      </c>
+      <c r="X6" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2082500</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="n">
+        <v>24.40909090909091</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>183.4545454545455</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>68</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1812500</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>72.81818181818181</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>OWxD1lHO</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45507.33333333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">haslberger w 
+  ger </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">olympiastadion
+  berlin </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>74667</v>
+      </c>
+      <c r="F7" t="n">
+        <v>48591</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2y0u8Wrq</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>G2Op923t</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>57</v>
+      </c>
+      <c r="N7" t="n">
+        <v>43</v>
+      </c>
+      <c r="O7" t="n">
+        <v>10</v>
+      </c>
+      <c r="P7" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>16</v>
+      </c>
+      <c r="T7" t="n">
+        <v>7</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>YmfcAeCo</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0AI1QUJH</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>59</v>
+      </c>
+      <c r="X7" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>23.22222222222222</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>183.7777777777778</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>69.44444444444444</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2422222.222222222</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>76.11111111111111</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>25.125</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>183.625</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>67</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1356250</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>72</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2360000</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>24.9375</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>186.1875</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>66.9375</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1417187.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>72.125</v>
+      </c>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>zkVf7hmm</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45507.33333333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">braun r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bbbank wildpark
+  karlsruhe </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>34302</v>
+      </c>
+      <c r="F8" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>EB3q7jbk</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M8" t="n">
+        <v>51</v>
+      </c>
+      <c r="N8" t="n">
+        <v>49</v>
+      </c>
+      <c r="O8" t="n">
+        <v>15</v>
+      </c>
+      <c r="P8" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="n">
+        <v>12</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>OzPMRhK3</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>tO31cZrF</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>59</v>
+      </c>
+      <c r="X8" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>26.27272727272727</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>184.3636363636364</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>67.81818181818181</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1395454.545454545</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>71.90909090909091</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>22.77777777777778</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>182</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>66</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1697222.222222222</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>72.55555555555556</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>22.78947368421053</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>181.1052631578947</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>64.84210526315789</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1087894.736842105</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>72.84210526315789</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>27.77777777777778</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>181.2222222222222</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>67.44444444444444</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1377777.777777778</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>70.22222222222223</v>
+      </c>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>f5QUJVWh</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45507.33333333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heft f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mdcc arena
+  magdeburg </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>30098</v>
+      </c>
+      <c r="F9" t="n">
+        <v>21469</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>YFuz2RLm</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M9" t="n">
+        <v>63</v>
+      </c>
+      <c r="N9" t="n">
+        <v>37</v>
+      </c>
+      <c r="O9" t="n">
+        <v>21</v>
+      </c>
+      <c r="P9" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>6</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>11</v>
+      </c>
+      <c r="T9" t="n">
+        <v>8</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>IgZoGKFn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>8E8qmw3d</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>59</v>
+      </c>
+      <c r="X9" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>182.3</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>24.93333333333333</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>176.3333333333333</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1375000</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>181.4666666666667</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>64.93333333333334</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>908333.3333333334</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>68.26666666666667</v>
+      </c>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>OA1xkBXI</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45506.64583333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burda m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rheinenergiestadion
+  cologne </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F10" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M10" t="n">
+        <v>58</v>
+      </c>
+      <c r="N10" t="n">
+        <v>42</v>
+      </c>
+      <c r="O10" t="n">
+        <v>26</v>
+      </c>
+      <c r="P10" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6</v>
+      </c>
+      <c r="S10" t="n">
+        <v>18</v>
+      </c>
+      <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>4fX0k7gg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>59</v>
+      </c>
+      <c r="X10" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>186</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>4680000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>79</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>2470000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>25.78947368421053</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>184.7894736842105</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.210526315789474</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>68.63157894736842</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2486315.789473684</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>73.05263157894737</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>183.25</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>2124000</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
+++ b/data/germany/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN10"/>
+  <dimension ref="A1:BN15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,84 +762,84 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vJqPCEPP</t>
+          <t>IViLLjPF</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45508.35416666666</v>
+        <v>45514.33333333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">kampka r 
+          <t xml:space="preserve">hartmann r 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">merck stadion am bollenfalltor
-  darmstadt </t>
+          <t xml:space="preserve">merkur spiel arena
+  dusseldorf </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17810</v>
+        <v>54600</v>
       </c>
       <c r="F2" t="n">
-        <v>17810</v>
+        <v>36103</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>S0hPB9rA</t>
+          <t>ne1oL3y7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ne1oL3y7</t>
+          <t>EB3q7jbk</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.79</v>
+        <v>1.09</v>
       </c>
       <c r="L2" t="n">
-        <v>1.49</v>
+        <v>0.66</v>
       </c>
       <c r="M2" t="n">
+        <v>53</v>
+      </c>
+      <c r="N2" t="n">
         <v>47</v>
       </c>
-      <c r="N2" t="n">
-        <v>53</v>
-      </c>
       <c r="O2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="P2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q2" t="n">
         <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>MDhPV0RQ</t>
+          <t>AoL97rX8</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>AoL97rX8</t>
+          <t>OzPMRhK3</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -856,73 +856,85 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>WG9pOTse</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>25.63636363636364</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>182.7272727272727</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2334090.909090909</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>73.90909090909091</v>
+      </c>
       <c r="AI2" t="n">
-        <v>26.3</v>
+        <v>26.27272727272727</v>
       </c>
       <c r="AJ2" t="n">
-        <v>183.3</v>
+        <v>184.3636363636364</v>
       </c>
       <c r="AK2" t="n">
         <v>1</v>
       </c>
       <c r="AL2" t="n">
-        <v>70.90000000000001</v>
+        <v>67.81818181818181</v>
       </c>
       <c r="AM2" t="n">
-        <v>2490000</v>
+        <v>1395454.545454545</v>
       </c>
       <c r="AN2" t="n">
-        <v>74</v>
+        <v>71.90909090909091</v>
       </c>
       <c r="AO2" t="n">
-        <v>25.6875</v>
+        <v>22.69230769230769</v>
       </c>
       <c r="AP2" t="n">
-        <v>186.25</v>
+        <v>186.3846153846154</v>
       </c>
       <c r="AQ2" t="n">
         <v>1</v>
       </c>
       <c r="AR2" t="n">
-        <v>68.75</v>
+        <v>66</v>
       </c>
       <c r="AS2" t="n">
-        <v>1679687.5</v>
+        <v>1753846.153846154</v>
       </c>
       <c r="AT2" t="n">
-        <v>73.1875</v>
+        <v>73.53846153846153</v>
       </c>
       <c r="AU2" t="n">
-        <v>21.95454545454545</v>
+        <v>23.3125</v>
       </c>
       <c r="AV2" t="n">
-        <v>186.4545454545455</v>
+        <v>181</v>
       </c>
       <c r="AW2" t="n">
         <v>1</v>
       </c>
       <c r="AX2" t="n">
-        <v>64.04545454545455</v>
+        <v>65.25</v>
       </c>
       <c r="AY2" t="n">
-        <v>1346590.909090909</v>
+        <v>1126250</v>
       </c>
       <c r="AZ2" t="n">
-        <v>72.95454545454545</v>
+        <v>72.5625</v>
       </c>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="inlineStr"/>
@@ -942,84 +954,84 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2Hl43AnC</t>
+          <t>tC1Aa08D</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45508.35416666666</v>
+        <v>45514.33333333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">hempel r 
+          <t xml:space="preserve">bauer t 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">sportpark ronhof thomas sommer
-  furth </t>
+          <t xml:space="preserve">waldstadion kaiserlinde
+  spiesen elversberg </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>16626</v>
+        <v>9970</v>
       </c>
       <c r="F3" t="n">
-        <v>12664</v>
+        <v>9502</v>
       </c>
       <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="M3" t="n">
+        <v>45</v>
+      </c>
+      <c r="N3" t="n">
+        <v>55</v>
+      </c>
+      <c r="O3" t="n">
+        <v>10</v>
+      </c>
+      <c r="P3" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q3" t="n">
         <v>3</v>
       </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>CCQGbik8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>zedZaSL7</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="M3" t="n">
-        <v>47</v>
-      </c>
-      <c r="N3" t="n">
-        <v>53</v>
-      </c>
-      <c r="O3" t="n">
-        <v>22</v>
-      </c>
-      <c r="P3" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>9</v>
       </c>
-      <c r="R3" t="n">
-        <v>5</v>
-      </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>8E86CPuD</t>
+          <t>8E8qmw3d</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>pdPRS0me</t>
+          <t>4fX0k7gg</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -1034,71 +1046,83 @@
       <c r="Z3" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>6FDqshzF</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
       <c r="AC3" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>183.1</v>
+        <v>182.3</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>67</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AG3" t="n">
-        <v>1480000</v>
+        <v>1200000</v>
       </c>
       <c r="AH3" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
+        <v>70.5</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>185.4545454545455</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>71.27272727272727</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>4545454.545454546</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>78.63636363636364</v>
+      </c>
       <c r="AO3" t="n">
-        <v>22.72727272727273</v>
+        <v>25.30769230769231</v>
       </c>
       <c r="AP3" t="n">
-        <v>182.5454545454545</v>
+        <v>182.3076923076923</v>
       </c>
       <c r="AQ3" t="n">
         <v>1</v>
       </c>
       <c r="AR3" t="n">
-        <v>64.59090909090909</v>
+        <v>65.23076923076923</v>
       </c>
       <c r="AS3" t="n">
-        <v>1273863.636363636</v>
+        <v>975000</v>
       </c>
       <c r="AT3" t="n">
-        <v>72.86363636363636</v>
+        <v>69.07692307692308</v>
       </c>
       <c r="AU3" t="n">
-        <v>25.57142857142857</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="AV3" t="n">
-        <v>181.8571428571429</v>
+        <v>186.5714285714286</v>
       </c>
       <c r="AW3" t="n">
-        <v>1</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="AX3" t="n">
-        <v>66.71428571428571</v>
+        <v>69.47619047619048</v>
       </c>
       <c r="AY3" t="n">
-        <v>1175000</v>
+        <v>2787619.047619048</v>
       </c>
       <c r="AZ3" t="n">
-        <v>68.42857142857143</v>
+        <v>73.19047619047619</v>
       </c>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="inlineStr"/>
@@ -1118,84 +1142,84 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SIOxI915</t>
+          <t>YJ3eN30K</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45508.35416666666</v>
+        <v>45514.33333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">schroder r 
+          <t xml:space="preserve">winter n 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">donaustadion
-  ulm </t>
+          <t xml:space="preserve">max morlock stadion
+  nuremberg </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>19500</v>
+        <v>44308</v>
       </c>
       <c r="F4" t="n">
-        <v>17400</v>
+        <v>50000</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>tbC3EcQn</t>
+          <t>6FDqshzF</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>naWckLmC</t>
+          <t>0Ija0Ej9</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="M4" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="N4" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="O4" t="n">
+        <v>8</v>
+      </c>
+      <c r="P4" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>5</v>
+      </c>
+      <c r="S4" t="n">
+        <v>11</v>
+      </c>
+      <c r="T4" t="n">
         <v>12</v>
       </c>
-      <c r="P4" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>4</v>
-      </c>
-      <c r="S4" t="n">
-        <v>12</v>
-      </c>
-      <c r="T4" t="n">
-        <v>16</v>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>QevvB2nf</t>
+          <t>tO31cZrF</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>4bJLk19p</t>
+          <t>txZLBQVC</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -1210,55 +1234,87 @@
       <c r="Z4" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>22.77777777777778</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>182</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>66</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1697222.222222222</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>72.55555555555556</v>
+      </c>
       <c r="AI4" t="n">
-        <v>25</v>
+        <v>25.625</v>
       </c>
       <c r="AJ4" t="n">
-        <v>184.6363636363636</v>
+        <v>189.75</v>
       </c>
       <c r="AK4" t="n">
         <v>1</v>
       </c>
       <c r="AL4" t="n">
-        <v>67.63636363636364</v>
+        <v>67.625</v>
       </c>
       <c r="AM4" t="n">
-        <v>1484090.909090909</v>
+        <v>1540625</v>
       </c>
       <c r="AN4" t="n">
-        <v>70.63636363636364</v>
-      </c>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
+        <v>71.5</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>28.125</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>180</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>67.875</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1209375</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>70</v>
+      </c>
       <c r="AU4" t="n">
-        <v>25.22222222222222</v>
+        <v>26.57142857142857</v>
       </c>
       <c r="AV4" t="n">
-        <v>180.9444444444445</v>
+        <v>186.7142857142857</v>
       </c>
       <c r="AW4" t="n">
         <v>1</v>
       </c>
       <c r="AX4" t="n">
-        <v>67.5</v>
+        <v>68.57142857142857</v>
       </c>
       <c r="AY4" t="n">
-        <v>1468055.555555556</v>
+        <v>1428571.428571429</v>
       </c>
       <c r="AZ4" t="n">
-        <v>71.11111111111111</v>
+        <v>70.57142857142857</v>
       </c>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
@@ -1278,84 +1334,84 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EeIMLi2t</t>
+          <t>h4pSHsOs</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45507.64583333334</v>
+        <v>45513.5625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">lechner f 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">veltins arena
-  gelsenkirchen </t>
+          <t xml:space="preserve">fritz walter stadion
+  kaiserslautern </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>62271</v>
+        <v>49500</v>
       </c>
       <c r="F5" t="n">
-        <v>61000</v>
+        <v>41632</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
+          <t>naWckLmC</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>QqLCC3il</t>
+          <t>CCQGbik8</t>
         </is>
       </c>
       <c r="K5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="L5" t="n">
         <v>2.7</v>
       </c>
-      <c r="L5" t="n">
-        <v>1.21</v>
-      </c>
       <c r="M5" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="O5" t="n">
+        <v>13</v>
+      </c>
+      <c r="P5" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>7</v>
+      </c>
+      <c r="R5" t="n">
+        <v>8</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="n">
         <v>14</v>
       </c>
-      <c r="P5" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>8</v>
-      </c>
-      <c r="R5" t="n">
-        <v>5</v>
-      </c>
-      <c r="S5" t="n">
-        <v>13</v>
-      </c>
-      <c r="T5" t="n">
-        <v>11</v>
-      </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>txZLBQVC</t>
+          <t>4bJLk19p</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>SQrxFAMl</t>
+          <t>8E86CPuD</t>
         </is>
       </c>
       <c r="W5" t="n">
@@ -1370,87 +1426,83 @@
       <c r="Z5" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>dfNCCCzS</t>
+          <t>6FDqshzF</t>
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>26.25</v>
+        <v>25</v>
       </c>
       <c r="AD5" t="n">
-        <v>187.125</v>
+        <v>184.6363636363636</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
       </c>
       <c r="AF5" t="n">
-        <v>69</v>
+        <v>67.63636363636364</v>
       </c>
       <c r="AG5" t="n">
-        <v>1740625</v>
+        <v>1484090.909090909</v>
       </c>
       <c r="AH5" t="n">
-        <v>71.5</v>
+        <v>70.63636363636364</v>
       </c>
       <c r="AI5" t="n">
-        <v>25.375</v>
+        <v>25</v>
       </c>
       <c r="AJ5" t="n">
-        <v>183.25</v>
+        <v>183.1</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.125</v>
+        <v>1</v>
       </c>
       <c r="AL5" t="n">
-        <v>66.875</v>
+        <v>67</v>
       </c>
       <c r="AM5" t="n">
-        <v>1287500</v>
+        <v>1480000</v>
       </c>
       <c r="AN5" t="n">
-        <v>71.875</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="AO5" t="n">
-        <v>27.22222222222222</v>
+        <v>25.23529411764706</v>
       </c>
       <c r="AP5" t="n">
-        <v>190.2222222222222</v>
+        <v>181.4705882352941</v>
       </c>
       <c r="AQ5" t="n">
         <v>1</v>
       </c>
       <c r="AR5" t="n">
-        <v>67.94444444444444</v>
+        <v>68.05882352941177</v>
       </c>
       <c r="AS5" t="n">
-        <v>1294444.444444444</v>
+        <v>1691176.470588235</v>
       </c>
       <c r="AT5" t="n">
-        <v>70.88888888888889</v>
+        <v>71.29411764705883</v>
       </c>
       <c r="AU5" t="n">
-        <v>24.57142857142857</v>
+        <v>23.13636363636364</v>
       </c>
       <c r="AV5" t="n">
-        <v>184.9285714285714</v>
+        <v>183.8181818181818</v>
       </c>
       <c r="AW5" t="n">
         <v>1</v>
       </c>
       <c r="AX5" t="n">
-        <v>66.07142857142857</v>
+        <v>65.31818181818181</v>
       </c>
       <c r="AY5" t="n">
-        <v>1302142.857142857</v>
+        <v>1430681.818181818</v>
       </c>
       <c r="AZ5" t="n">
-        <v>71.14285714285714</v>
+        <v>73.09090909090909</v>
       </c>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr"/>
@@ -1470,84 +1522,84 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fiod5WHa</t>
+          <t>StuiCwhJ</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45507.33333333334</v>
+        <v>45513.5625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">bacher m 
+          <t xml:space="preserve">benen l 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">heinz von heiden arena
-  hannover </t>
+          <t xml:space="preserve">jahnstadion regensburg
+  regensburg </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49200</v>
+        <v>15210</v>
       </c>
       <c r="F6" t="n">
-        <v>31800</v>
+        <v>12095</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>dfNCCCzS</t>
+          <t>UiCmEP56</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>UiCmEP56</t>
+          <t>tbC3EcQn</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>0.74</v>
       </c>
       <c r="L6" t="n">
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="M6" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="N6" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="O6" t="n">
+        <v>8</v>
+      </c>
+      <c r="P6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>22</v>
+      </c>
+      <c r="T6" t="n">
         <v>16</v>
       </c>
-      <c r="P6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>12</v>
-      </c>
-      <c r="T6" t="n">
-        <v>17</v>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>t0ZPdkUl</t>
+          <t>zyLSrbZQ</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>zyLSrbZQ</t>
+          <t>QevvB2nf</t>
         </is>
       </c>
       <c r="W6" t="n">
@@ -1562,60 +1614,44 @@
       <c r="Z6" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>QqLCC3il</t>
-        </is>
-      </c>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>184.3</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2082500</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>73.59999999999999</v>
-      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="n">
-        <v>24.40909090909091</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>183.4545454545455</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>68</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1812500</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>72.81818181818181</v>
-      </c>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>183</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>62</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>887500</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>70.5</v>
+      </c>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr"/>
@@ -1634,69 +1670,69 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>OWxD1lHO</t>
+          <t>vJqPCEPP</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45507.33333333334</v>
+        <v>45508.35416666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">haslberger w 
+          <t xml:space="preserve">kampka r 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">olympiastadion
-  berlin </t>
+          <t xml:space="preserve">merck stadion am bollenfalltor
+  darmstadt </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>74667</v>
+        <v>17810</v>
       </c>
       <c r="F7" t="n">
-        <v>48591</v>
+        <v>17810</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2y0u8Wrq</t>
+          <t>S0hPB9rA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>G2Op923t</t>
+          <t>ne1oL3y7</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1.4</v>
+        <v>0.79</v>
       </c>
       <c r="L7" t="n">
-        <v>2.1</v>
+        <v>1.49</v>
       </c>
       <c r="M7" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="N7" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="O7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P7" t="n">
         <v>11</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S7" t="n">
         <v>16</v>
@@ -1706,12 +1742,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>YmfcAeCo</t>
+          <t>MDhPV0RQ</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0AI1QUJH</t>
+          <t>AoL97rX8</t>
         </is>
       </c>
       <c r="W7" t="n">
@@ -1726,79 +1762,75 @@
       <c r="Z7" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="n">
-        <v>23.22222222222222</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>183.7777777777778</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.111111111111111</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>69.44444444444444</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2422222.222222222</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>76.11111111111111</v>
-      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="n">
-        <v>25.125</v>
+        <v>26.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>183.625</v>
+        <v>183.3</v>
       </c>
       <c r="AK7" t="n">
         <v>1</v>
       </c>
       <c r="AL7" t="n">
-        <v>67</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="AM7" t="n">
-        <v>1356250</v>
+        <v>2490000</v>
       </c>
       <c r="AN7" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AO7" t="n">
-        <v>23.55</v>
+        <v>25.6875</v>
       </c>
       <c r="AP7" t="n">
-        <v>184.2</v>
+        <v>186.25</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR7" t="n">
-        <v>69.25</v>
+        <v>68.75</v>
       </c>
       <c r="AS7" t="n">
-        <v>2360000</v>
+        <v>1679687.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>74.75</v>
+        <v>73.1875</v>
       </c>
       <c r="AU7" t="n">
-        <v>24.9375</v>
+        <v>21.95454545454545</v>
       </c>
       <c r="AV7" t="n">
-        <v>186.1875</v>
+        <v>186.4545454545455</v>
       </c>
       <c r="AW7" t="n">
         <v>1</v>
       </c>
       <c r="AX7" t="n">
-        <v>66.9375</v>
+        <v>64.04545454545455</v>
       </c>
       <c r="AY7" t="n">
-        <v>1417187.5</v>
+        <v>1346590.909090909</v>
       </c>
       <c r="AZ7" t="n">
-        <v>72.125</v>
+        <v>72.95454545454545</v>
       </c>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
@@ -1818,84 +1850,84 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>zkVf7hmm</t>
+          <t>2Hl43AnC</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45507.33333333334</v>
+        <v>45508.35416666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">braun r 
+          <t xml:space="preserve">hempel r 
   ger </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">bbbank wildpark
-  karlsruhe </t>
+          <t xml:space="preserve">sportpark ronhof thomas sommer
+  furth </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>34302</v>
+        <v>16626</v>
       </c>
       <c r="F8" t="n">
-        <v>25000</v>
+        <v>12664</v>
       </c>
       <c r="G8" t="n">
         <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>EB3q7jbk</t>
+          <t>CCQGbik8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6FDqshzF</t>
+          <t>zedZaSL7</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.71</v>
+        <v>3.65</v>
       </c>
       <c r="M8" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N8" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O8" t="n">
+        <v>22</v>
+      </c>
+      <c r="P8" t="n">
         <v>15</v>
       </c>
-      <c r="P8" t="n">
-        <v>14</v>
-      </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R8" t="n">
         <v>5</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>OzPMRhK3</t>
+          <t>8E86CPuD</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>tO31cZrF</t>
+          <t>pdPRS0me</t>
         </is>
       </c>
       <c r="W8" t="n">
@@ -1912,85 +1944,69 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>naWckLmC</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>CCQGbik8</t>
-        </is>
-      </c>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>26.27272727272727</v>
+        <v>25</v>
       </c>
       <c r="AD8" t="n">
-        <v>184.3636363636364</v>
+        <v>183.1</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
       </c>
       <c r="AF8" t="n">
-        <v>67.81818181818181</v>
+        <v>67</v>
       </c>
       <c r="AG8" t="n">
-        <v>1395454.545454545</v>
+        <v>1480000</v>
       </c>
       <c r="AH8" t="n">
-        <v>71.90909090909091</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>22.77777777777778</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>182</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.111111111111111</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>66</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1697222.222222222</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>72.55555555555556</v>
-      </c>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
-        <v>22.78947368421053</v>
+        <v>22.72727272727273</v>
       </c>
       <c r="AP8" t="n">
-        <v>181.1052631578947</v>
+        <v>182.5454545454545</v>
       </c>
       <c r="AQ8" t="n">
         <v>1</v>
       </c>
       <c r="AR8" t="n">
-        <v>64.84210526315789</v>
+        <v>64.59090909090909</v>
       </c>
       <c r="AS8" t="n">
-        <v>1087894.736842105</v>
+        <v>1273863.636363636</v>
       </c>
       <c r="AT8" t="n">
-        <v>72.84210526315789</v>
+        <v>72.86363636363636</v>
       </c>
       <c r="AU8" t="n">
-        <v>27.77777777777778</v>
+        <v>25.57142857142857</v>
       </c>
       <c r="AV8" t="n">
-        <v>181.2222222222222</v>
+        <v>181.8571428571429</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.111111111111111</v>
+        <v>1</v>
       </c>
       <c r="AX8" t="n">
-        <v>67.44444444444444</v>
+        <v>66.71428571428571</v>
       </c>
       <c r="AY8" t="n">
-        <v>1377777.777777778</v>
+        <v>1175000</v>
       </c>
       <c r="AZ8" t="n">
-        <v>70.22222222222223</v>
+        <v>68.42857142857143</v>
       </c>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
@@ -2010,84 +2026,84 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>f5QUJVWh</t>
+          <t>SIOxI915</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45507.33333333334</v>
+        <v>45508.35416666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">heft f 
+          <t xml:space="preserve">schroder r 
   ger </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">mdcc arena
-  magdeburg </t>
+          <t xml:space="preserve">donaustadion
+  ulm </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>30098</v>
+        <v>19500</v>
       </c>
       <c r="F9" t="n">
-        <v>21469</v>
+        <v>17400</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>YFuz2RLm</t>
+          <t>tbC3EcQn</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6in2Eknb</t>
+          <t>naWckLmC</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2.49</v>
+        <v>0.98</v>
       </c>
       <c r="L9" t="n">
-        <v>0.72</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="N9" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="O9" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="P9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T9" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>IgZoGKFn</t>
+          <t>QevvB2nf</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>8E8qmw3d</t>
+          <t>4bJLk19p</t>
         </is>
       </c>
       <c r="W9" t="n">
@@ -2111,58 +2127,46 @@
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="AJ9" t="n">
-        <v>182.3</v>
+        <v>184.6363636363636</v>
       </c>
       <c r="AK9" t="n">
         <v>1</v>
       </c>
       <c r="AL9" t="n">
-        <v>66.90000000000001</v>
+        <v>67.63636363636364</v>
       </c>
       <c r="AM9" t="n">
-        <v>1200000</v>
+        <v>1484090.909090909</v>
       </c>
       <c r="AN9" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>24.93333333333333</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>176.3333333333333</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1375000</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>69.59999999999999</v>
-      </c>
+        <v>70.63636363636364</v>
+      </c>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
       <c r="AU9" t="n">
-        <v>25.8</v>
+        <v>25.22222222222222</v>
       </c>
       <c r="AV9" t="n">
-        <v>181.4666666666667</v>
+        <v>180.9444444444445</v>
       </c>
       <c r="AW9" t="n">
         <v>1</v>
       </c>
       <c r="AX9" t="n">
-        <v>64.93333333333334</v>
+        <v>67.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>908333.3333333334</v>
+        <v>1468055.555555556</v>
       </c>
       <c r="AZ9" t="n">
-        <v>68.26666666666667</v>
+        <v>71.11111111111111</v>
       </c>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
@@ -2182,84 +2186,84 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OA1xkBXI</t>
+          <t>EeIMLi2t</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45506.64583333334</v>
+        <v>45507.64583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">burda m 
+          <t xml:space="preserve">stieler t 
   ger </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">rheinenergiestadion
-  cologne </t>
+          <t xml:space="preserve">veltins arena
+  gelsenkirchen </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>50000</v>
+        <v>62271</v>
       </c>
       <c r="F10" t="n">
-        <v>50000</v>
+        <v>61000</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
+          <t>0Ija0Ej9</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>v9k3aY5F</t>
+          <t>QqLCC3il</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>3.29</v>
+        <v>2.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>1.21</v>
       </c>
       <c r="M10" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="N10" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="O10" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="P10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S10" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>4fX0k7gg</t>
+          <t>txZLBQVC</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>EDRZkDzS</t>
+          <t>SQrxFAMl</t>
         </is>
       </c>
       <c r="W10" t="n">
@@ -2276,85 +2280,85 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>dfNCCCzS</t>
         </is>
       </c>
       <c r="AC10" t="n">
-        <v>22.7</v>
+        <v>26.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>186</v>
+        <v>187.125</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AF10" t="n">
-        <v>71.3</v>
+        <v>69</v>
       </c>
       <c r="AG10" t="n">
-        <v>4680000</v>
+        <v>1740625</v>
       </c>
       <c r="AH10" t="n">
-        <v>79</v>
+        <v>71.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>25.7</v>
+        <v>25.375</v>
       </c>
       <c r="AJ10" t="n">
-        <v>183.4</v>
+        <v>183.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
+        <v>1.125</v>
       </c>
       <c r="AL10" t="n">
-        <v>71.2</v>
+        <v>66.875</v>
       </c>
       <c r="AM10" t="n">
-        <v>2470000</v>
+        <v>1287500</v>
       </c>
       <c r="AN10" t="n">
-        <v>73.7</v>
+        <v>71.875</v>
       </c>
       <c r="AO10" t="n">
-        <v>25.78947368421053</v>
+        <v>27.22222222222222</v>
       </c>
       <c r="AP10" t="n">
-        <v>184.7894736842105</v>
+        <v>190.2222222222222</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.210526315789474</v>
+        <v>1</v>
       </c>
       <c r="AR10" t="n">
-        <v>68.63157894736842</v>
+        <v>67.94444444444444</v>
       </c>
       <c r="AS10" t="n">
-        <v>2486315.789473684</v>
+        <v>1294444.444444444</v>
       </c>
       <c r="AT10" t="n">
-        <v>73.05263157894737</v>
+        <v>70.88888888888889</v>
       </c>
       <c r="AU10" t="n">
-        <v>25.25</v>
+        <v>24.57142857142857</v>
       </c>
       <c r="AV10" t="n">
-        <v>183.25</v>
+        <v>184.9285714285714</v>
       </c>
       <c r="AW10" t="n">
         <v>1</v>
       </c>
       <c r="AX10" t="n">
-        <v>69.05</v>
+        <v>66.07142857142857</v>
       </c>
       <c r="AY10" t="n">
-        <v>2124000</v>
+        <v>1302142.857142857</v>
       </c>
       <c r="AZ10" t="n">
-        <v>72.75</v>
+        <v>71.14285714285714</v>
       </c>
       <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="inlineStr"/>
@@ -2371,6 +2375,910 @@
       <c r="BM10" t="inlineStr"/>
       <c r="BN10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fiod5WHa</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45507.33333333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bacher m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heinz von heiden arena
+  hannover </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>49200</v>
+      </c>
+      <c r="F11" t="n">
+        <v>31800</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>UiCmEP56</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="M11" t="n">
+        <v>58</v>
+      </c>
+      <c r="N11" t="n">
+        <v>42</v>
+      </c>
+      <c r="O11" t="n">
+        <v>16</v>
+      </c>
+      <c r="P11" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S11" t="n">
+        <v>12</v>
+      </c>
+      <c r="T11" t="n">
+        <v>17</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>t0ZPdkUl</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>zyLSrbZQ</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>59</v>
+      </c>
+      <c r="X11" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2082500</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="n">
+        <v>24.40909090909091</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>183.4545454545455</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>68</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1812500</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>72.81818181818181</v>
+      </c>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>OWxD1lHO</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45507.33333333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">haslberger w 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">olympiastadion
+  berlin </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>74667</v>
+      </c>
+      <c r="F12" t="n">
+        <v>48591</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2y0u8Wrq</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>G2Op923t</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>57</v>
+      </c>
+      <c r="N12" t="n">
+        <v>43</v>
+      </c>
+      <c r="O12" t="n">
+        <v>10</v>
+      </c>
+      <c r="P12" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>16</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>YmfcAeCo</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0AI1QUJH</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>59</v>
+      </c>
+      <c r="X12" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>23.22222222222222</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>183.7777777777778</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>69.44444444444444</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2422222.222222222</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>76.11111111111111</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>25.125</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>183.625</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>67</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1356250</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>72</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2360000</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>24.9375</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>186.1875</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>66.9375</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1417187.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>72.125</v>
+      </c>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>zkVf7hmm</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45507.33333333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">braun r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bbbank wildpark
+  karlsruhe </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>34302</v>
+      </c>
+      <c r="F13" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>EB3q7jbk</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M13" t="n">
+        <v>51</v>
+      </c>
+      <c r="N13" t="n">
+        <v>49</v>
+      </c>
+      <c r="O13" t="n">
+        <v>15</v>
+      </c>
+      <c r="P13" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="n">
+        <v>12</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>OzPMRhK3</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>tO31cZrF</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>59</v>
+      </c>
+      <c r="X13" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>26.27272727272727</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>184.3636363636364</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>67.81818181818181</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1395454.545454545</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>71.90909090909091</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>22.77777777777778</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>182</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>66</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1697222.222222222</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>72.55555555555556</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>22.78947368421053</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>181.1052631578947</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>64.84210526315789</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1087894.736842105</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>72.84210526315789</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>27.77777777777778</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>181.2222222222222</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>67.44444444444444</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1377777.777777778</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>70.22222222222223</v>
+      </c>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>f5QUJVWh</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45507.33333333334</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heft f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mdcc arena
+  magdeburg </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>30098</v>
+      </c>
+      <c r="F14" t="n">
+        <v>21469</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>YFuz2RLm</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M14" t="n">
+        <v>63</v>
+      </c>
+      <c r="N14" t="n">
+        <v>37</v>
+      </c>
+      <c r="O14" t="n">
+        <v>21</v>
+      </c>
+      <c r="P14" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>6</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3</v>
+      </c>
+      <c r="S14" t="n">
+        <v>11</v>
+      </c>
+      <c r="T14" t="n">
+        <v>8</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>IgZoGKFn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>8E8qmw3d</t>
+        </is>
+      </c>
+      <c r="W14" t="n">
+        <v>59</v>
+      </c>
+      <c r="X14" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>182.3</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>24.93333333333333</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>176.3333333333333</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1375000</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>181.4666666666667</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>64.93333333333334</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>908333.3333333334</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>68.26666666666667</v>
+      </c>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="inlineStr"/>
+      <c r="BM14" t="inlineStr"/>
+      <c r="BN14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>OA1xkBXI</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45506.64583333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burda m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rheinenergiestadion
+  cologne </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M15" t="n">
+        <v>58</v>
+      </c>
+      <c r="N15" t="n">
+        <v>42</v>
+      </c>
+      <c r="O15" t="n">
+        <v>26</v>
+      </c>
+      <c r="P15" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6</v>
+      </c>
+      <c r="S15" t="n">
+        <v>18</v>
+      </c>
+      <c r="T15" t="n">
+        <v>7</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>4fX0k7gg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+      <c r="W15" t="n">
+        <v>59</v>
+      </c>
+      <c r="X15" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="AC15" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>186</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>4680000</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>79</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>2470000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>25.78947368421053</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>184.7894736842105</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.210526315789474</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>68.63157894736842</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2486315.789473684</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>73.05263157894737</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>183.25</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>2124000</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="inlineStr"/>
+      <c r="BM15" t="inlineStr"/>
+      <c r="BN15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
+++ b/data/germany/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN15"/>
+  <dimension ref="A1:BN46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,39 +762,39 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IViLLjPF</t>
+          <t>pzHxyrtm</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45514.33333333334</v>
+        <v>45522.54166666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">hartmann r 
+          <t xml:space="preserve">oldhafer k 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">merkur spiel arena
-  dusseldorf </t>
+          <t xml:space="preserve">stadion am lotter kreuz
+  lotte </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>54600</v>
+        <v>10059</v>
       </c>
       <c r="F2" t="n">
-        <v>36103</v>
+        <v>4637</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ne1oL3y7</t>
+          <t>hjNlCFPB</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -802,39 +802,35 @@
           <t>EB3q7jbk</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.66</v>
-      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N2" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="O2" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="P2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="Q2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>AoL97rX8</t>
+          <t>KW0bzbwJ</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -846,47 +842,31 @@
         <v>59</v>
       </c>
       <c r="X2" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr">
         <is>
           <t>naWckLmC</t>
         </is>
       </c>
-      <c r="AC2" t="n">
-        <v>25.63636363636364</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>182.7272727272727</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2334090.909090909</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>73.90909090909091</v>
-      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>26.27272727272727</v>
+        <v>26.18181818181818</v>
       </c>
       <c r="AJ2" t="n">
-        <v>184.3636363636364</v>
+        <v>183.0909090909091</v>
       </c>
       <c r="AK2" t="n">
         <v>1</v>
@@ -895,46 +875,34 @@
         <v>67.81818181818181</v>
       </c>
       <c r="AM2" t="n">
-        <v>1395454.545454545</v>
+        <v>1413636.363636364</v>
       </c>
       <c r="AN2" t="n">
-        <v>71.90909090909091</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>22.69230769230769</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>186.3846153846154</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>66</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1753846.153846154</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>73.53846153846153</v>
-      </c>
+        <v>71.72727272727273</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="n">
-        <v>23.3125</v>
+        <v>25.21428571428572</v>
       </c>
       <c r="AV2" t="n">
-        <v>181</v>
+        <v>183.7142857142857</v>
       </c>
       <c r="AW2" t="n">
         <v>1</v>
       </c>
       <c r="AX2" t="n">
-        <v>65.25</v>
+        <v>66.21428571428571</v>
       </c>
       <c r="AY2" t="n">
-        <v>1126250</v>
+        <v>1071071.428571429</v>
       </c>
       <c r="AZ2" t="n">
-        <v>72.5625</v>
+        <v>70.92857142857143</v>
       </c>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="inlineStr"/>
@@ -954,94 +922,90 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>tC1Aa08D</t>
+          <t>vXAKoaf5</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45514.33333333334</v>
+        <v>45522.54166666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bauer t 
+          <t xml:space="preserve">stegemann s 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">waldstadion kaiserlinde
-  spiesen elversberg </t>
+          <t xml:space="preserve">rudolf harbig stadion
+  dresden </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>9970</v>
+        <v>32249</v>
       </c>
       <c r="F3" t="n">
-        <v>9502</v>
+        <v>30000</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6in2Eknb</t>
+          <t>zL1YsOi1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="L3" t="n">
-        <v>3.39</v>
-      </c>
+          <t>ne1oL3y7</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O3" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="P3" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
+        <v>5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>8</v>
+      </c>
+      <c r="T3" t="n">
         <v>9</v>
       </c>
-      <c r="S3" t="n">
-        <v>13</v>
-      </c>
-      <c r="T3" t="n">
-        <v>13</v>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>8E8qmw3d</t>
+          <t>4YhTfKrD</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>4fX0k7gg</t>
+          <t>AoL97rX8</t>
         </is>
       </c>
       <c r="W3" t="n">
         <v>59</v>
       </c>
       <c r="X3" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
         <v>20242025</v>
@@ -1049,80 +1013,68 @@
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
-        </is>
-      </c>
-      <c r="AC3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>182.3</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>70.5</v>
-      </c>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>23</v>
+        <v>25.36363636363636</v>
       </c>
       <c r="AJ3" t="n">
-        <v>185.4545454545455</v>
+        <v>183.8181818181818</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.181818181818182</v>
+        <v>1</v>
       </c>
       <c r="AL3" t="n">
-        <v>71.27272727272727</v>
+        <v>69.54545454545455</v>
       </c>
       <c r="AM3" t="n">
-        <v>4545454.545454546</v>
+        <v>2061363.636363636</v>
       </c>
       <c r="AN3" t="n">
-        <v>78.63636363636364</v>
+        <v>73.36363636363636</v>
       </c>
       <c r="AO3" t="n">
-        <v>25.30769230769231</v>
+        <v>26.28571428571428</v>
       </c>
       <c r="AP3" t="n">
-        <v>182.3076923076923</v>
+        <v>180.1428571428571</v>
       </c>
       <c r="AQ3" t="n">
         <v>1</v>
       </c>
       <c r="AR3" t="n">
-        <v>65.23076923076923</v>
+        <v>65.57142857142857</v>
       </c>
       <c r="AS3" t="n">
-        <v>975000</v>
+        <v>853571.4285714285</v>
       </c>
       <c r="AT3" t="n">
-        <v>69.07692307692308</v>
+        <v>67.28571428571429</v>
       </c>
       <c r="AU3" t="n">
-        <v>26.33333333333333</v>
+        <v>21.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>186.5714285714286</v>
+        <v>186.95</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.380952380952381</v>
+        <v>1</v>
       </c>
       <c r="AX3" t="n">
-        <v>69.47619047619048</v>
+        <v>64.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>2787619.047619048</v>
+        <v>1241250</v>
       </c>
       <c r="AZ3" t="n">
-        <v>73.19047619047619</v>
+        <v>75.45</v>
       </c>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="inlineStr"/>
@@ -1142,179 +1094,147 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>YJ3eN30K</t>
+          <t>dCPKovw8</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45514.33333333334</v>
+        <v>45522.54166666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">winter n 
+          <t xml:space="preserve">zwayer f 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">max morlock stadion
-  nuremberg </t>
+          <t xml:space="preserve">hansch arena
+  meppen </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44308</v>
+        <v>13696</v>
       </c>
       <c r="F4" t="n">
-        <v>50000</v>
+        <v>12959</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6FDqshzF</t>
+          <t>rXqBh2xP</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2.12</v>
-      </c>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="N4" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="O4" t="n">
+        <v>7</v>
+      </c>
+      <c r="P4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>12</v>
+      </c>
+      <c r="S4" t="n">
         <v>8</v>
       </c>
-      <c r="P4" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>5</v>
-      </c>
-      <c r="R4" t="n">
-        <v>5</v>
-      </c>
-      <c r="S4" t="n">
-        <v>11</v>
-      </c>
       <c r="T4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>tO31cZrF</t>
+          <t>UqphGQrg</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>txZLBQVC</t>
+          <t>EDRZkDzS</t>
         </is>
       </c>
       <c r="W4" t="n">
         <v>59</v>
       </c>
       <c r="X4" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>CCQGbik8</t>
-        </is>
-      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="AC4" t="n">
-        <v>22.77777777777778</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>182</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.111111111111111</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>66</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1697222.222222222</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>72.55555555555556</v>
-      </c>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>25.625</v>
+        <v>25.25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>189.75</v>
+        <v>182.5</v>
       </c>
       <c r="AK4" t="n">
         <v>1</v>
       </c>
       <c r="AL4" t="n">
-        <v>67.625</v>
+        <v>71.625</v>
       </c>
       <c r="AM4" t="n">
-        <v>1540625</v>
+        <v>2912500</v>
       </c>
       <c r="AN4" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>28.125</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>180</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>67.875</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1209375</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>70</v>
-      </c>
+        <v>74.75</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="n">
-        <v>26.57142857142857</v>
+        <v>26.68421052631579</v>
       </c>
       <c r="AV4" t="n">
-        <v>186.7142857142857</v>
+        <v>186.6315789473684</v>
       </c>
       <c r="AW4" t="n">
         <v>1</v>
       </c>
       <c r="AX4" t="n">
-        <v>68.57142857142857</v>
+        <v>70.57894736842105</v>
       </c>
       <c r="AY4" t="n">
-        <v>1428571.428571429</v>
+        <v>2598947.368421053</v>
       </c>
       <c r="AZ4" t="n">
-        <v>70.57142857142857</v>
+        <v>72.63157894736842</v>
       </c>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
@@ -1334,175 +1254,171 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>h4pSHsOs</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45513.5625</v>
+        <v>45522.4375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">lechner f 
+          <t xml:space="preserve">schroder r 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">fritz walter stadion
-  kaiserslautern </t>
+          <t xml:space="preserve">ostseestadion
+  rostock </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>49500</v>
+        <v>29000</v>
       </c>
       <c r="F5" t="n">
-        <v>41632</v>
+        <v>25600</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>naWckLmC</t>
+          <t>KIHmtCkL</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>CCQGbik8</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2.7</v>
-      </c>
+          <t>2y0u8Wrq</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="N5" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="O5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="P5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4bJLk19p</t>
+          <t>G8THUSaE</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>8E86CPuD</t>
+          <t>YmfcAeCo</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>59</v>
       </c>
       <c r="X5" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>6FDqshzF</t>
-        </is>
-      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>25</v>
+        <v>25.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>184.6363636363636</v>
+        <v>183.875</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
       </c>
       <c r="AF5" t="n">
-        <v>67.63636363636364</v>
+        <v>65.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>1484090.909090909</v>
+        <v>1040625</v>
       </c>
       <c r="AH5" t="n">
-        <v>70.63636363636364</v>
+        <v>69.125</v>
       </c>
       <c r="AI5" t="n">
-        <v>25</v>
+        <v>23.4</v>
       </c>
       <c r="AJ5" t="n">
-        <v>183.1</v>
+        <v>182.8</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AL5" t="n">
-        <v>67</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AM5" t="n">
-        <v>1480000</v>
+        <v>2340000</v>
       </c>
       <c r="AN5" t="n">
-        <v>71.59999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>25.23529411764706</v>
+        <v>23.7</v>
       </c>
       <c r="AP5" t="n">
-        <v>181.4705882352941</v>
+        <v>181.6</v>
       </c>
       <c r="AQ5" t="n">
         <v>1</v>
       </c>
       <c r="AR5" t="n">
-        <v>68.05882352941177</v>
+        <v>64</v>
       </c>
       <c r="AS5" t="n">
-        <v>1691176.470588235</v>
+        <v>997500</v>
       </c>
       <c r="AT5" t="n">
-        <v>71.29411764705883</v>
+        <v>70.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>23.13636363636364</v>
+        <v>23.47368421052632</v>
       </c>
       <c r="AV5" t="n">
-        <v>183.8181818181818</v>
+        <v>186.3684210526316</v>
       </c>
       <c r="AW5" t="n">
-        <v>1</v>
+        <v>1.157894736842105</v>
       </c>
       <c r="AX5" t="n">
-        <v>65.31818181818181</v>
+        <v>68.47368421052632</v>
       </c>
       <c r="AY5" t="n">
-        <v>1430681.818181818</v>
+        <v>1956578.947368421</v>
       </c>
       <c r="AZ5" t="n">
-        <v>73.09090909090909</v>
+        <v>75</v>
       </c>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr"/>
@@ -1522,100 +1438,100 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>StuiCwhJ</t>
+          <t>KSwfVwAO</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45513.5625</v>
+        <v>45522.4375</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">benen l 
+          <t xml:space="preserve">lechner f 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">jahnstadion regensburg
-  regensburg </t>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>15210</v>
+        <v>29546</v>
       </c>
       <c r="F6" t="n">
-        <v>12095</v>
+        <v>6487</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>UiCmEP56</t>
+          <t>WrbkcjCd</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>tbC3EcQn</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.47</v>
-      </c>
+          <t>S0hPB9rA</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="N6" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="O6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="T6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>zyLSrbZQ</t>
+          <t>lC9J1RTa</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>QevvB2nf</t>
+          <t>MDhPV0RQ</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>59</v>
       </c>
       <c r="X6" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="n">
         <v>20242025</v>
       </c>
       <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
@@ -1635,22 +1551,22 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="n">
-        <v>21.5</v>
+        <v>27.14285714285714</v>
       </c>
       <c r="AV6" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="AW6" t="n">
         <v>1</v>
       </c>
       <c r="AX6" t="n">
-        <v>62</v>
+        <v>70.35714285714286</v>
       </c>
       <c r="AY6" t="n">
-        <v>887500</v>
+        <v>1908928.571428571</v>
       </c>
       <c r="AZ6" t="n">
-        <v>70.5</v>
+        <v>73.71428571428571</v>
       </c>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
@@ -1670,106 +1586,98 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vJqPCEPP</t>
+          <t>tvOIPExA</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45508.35416666666</v>
+        <v>45522.4375</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">kampka r 
+          <t xml:space="preserve">brand b 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">merck stadion am bollenfalltor
-  darmstadt </t>
+          <t xml:space="preserve">hardtwaldstadion
+  sandhausen </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17810</v>
+        <v>15414</v>
       </c>
       <c r="F7" t="n">
-        <v>17810</v>
+        <v>9705</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>S0hPB9rA</t>
+          <t>UZxEj1R4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ne1oL3y7</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.49</v>
-      </c>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="N7" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="O7" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="P7" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R7" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="S7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T7" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>MDhPV0RQ</t>
+          <t>rZtwKVAL</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>AoL97rX8</t>
+          <t>4fX0k7gg</t>
         </is>
       </c>
       <c r="W7" t="n">
         <v>59</v>
       </c>
       <c r="X7" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
+      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1779,58 +1687,46 @@
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="n">
-        <v>26.3</v>
+        <v>22.7</v>
       </c>
       <c r="AJ7" t="n">
-        <v>183.3</v>
+        <v>184.6</v>
       </c>
       <c r="AK7" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AL7" t="n">
-        <v>70.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AM7" t="n">
-        <v>2490000</v>
+        <v>3820000</v>
       </c>
       <c r="AN7" t="n">
-        <v>74</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>25.6875</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>186.25</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>68.75</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1679687.5</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>73.1875</v>
-      </c>
+        <v>78.3</v>
+      </c>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
       <c r="AU7" t="n">
-        <v>21.95454545454545</v>
+        <v>26.04761904761905</v>
       </c>
       <c r="AV7" t="n">
-        <v>186.4545454545455</v>
+        <v>187.5714285714286</v>
       </c>
       <c r="AW7" t="n">
-        <v>1</v>
+        <v>1.238095238095238</v>
       </c>
       <c r="AX7" t="n">
-        <v>64.04545454545455</v>
+        <v>68.42857142857143</v>
       </c>
       <c r="AY7" t="n">
-        <v>1346590.909090909</v>
+        <v>2287619.047619048</v>
       </c>
       <c r="AZ7" t="n">
-        <v>72.95454545454545</v>
+        <v>72.23809523809524</v>
       </c>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
@@ -1850,163 +1746,147 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2Hl43AnC</t>
+          <t>jFMCm08e</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45508.35416666666</v>
+        <v>45522.4375</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">hempel r 
+          <t xml:space="preserve">heft f 
   ger </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">sportpark ronhof thomas sommer
-  furth </t>
+          <t xml:space="preserve">jahnstadion regensburg
+  regensburg </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>16626</v>
+        <v>15210</v>
       </c>
       <c r="F8" t="n">
-        <v>12664</v>
+        <v>12581</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CCQGbik8</t>
+          <t>UiCmEP56</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>zedZaSL7</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3.65</v>
-      </c>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="N8" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="O8" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="P8" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7</v>
+      </c>
+      <c r="S8" t="n">
         <v>15</v>
       </c>
-      <c r="Q8" t="n">
-        <v>9</v>
-      </c>
-      <c r="R8" t="n">
-        <v>5</v>
-      </c>
-      <c r="S8" t="n">
-        <v>9</v>
-      </c>
       <c r="T8" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>8E86CPuD</t>
+          <t>zyLSrbZQ</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>pdPRS0me</t>
+          <t>8f6APkLc</t>
         </is>
       </c>
       <c r="W8" t="n">
         <v>59</v>
       </c>
       <c r="X8" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>6FDqshzF</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>183.1</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>67</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1480000</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="n">
-        <v>22.72727272727273</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>182.5454545454545</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>64.59090909090909</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1273863.636363636</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>72.86363636363636</v>
-      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="n">
+        <v>26.88888888888889</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>183.4444444444445</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>70.88888888888889</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>2213888.888888889</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>73.44444444444444</v>
+      </c>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
       <c r="AU8" t="n">
-        <v>25.57142857142857</v>
+        <v>22.875</v>
       </c>
       <c r="AV8" t="n">
-        <v>181.8571428571429</v>
+        <v>183.875</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
       </c>
       <c r="AX8" t="n">
-        <v>66.71428571428571</v>
+        <v>67.25</v>
       </c>
       <c r="AY8" t="n">
-        <v>1175000</v>
+        <v>1814062.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>68.42857142857143</v>
+        <v>75.8125</v>
       </c>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
@@ -2026,94 +1906,90 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SIOxI915</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45508.35416666666</v>
+        <v>45522.4375</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">schroder r 
+          <t xml:space="preserve">nouhoum a 
   ger </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">donaustadion
-  ulm </t>
+          <t xml:space="preserve">friedrich ebert stadium
+  hildesheim </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>19500</v>
+        <v>10000</v>
       </c>
       <c r="F9" t="n">
-        <v>17400</v>
+        <v>5186</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>tbC3EcQn</t>
+          <t>E3xs5mIe</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>naWckLmC</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="L9" t="n">
-        <v>3</v>
-      </c>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="N9" t="n">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="O9" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P9" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>QevvB2nf</t>
+          <t>bJ0lIKrp</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>4bJLk19p</t>
+          <t>8E8qmw3d</t>
         </is>
       </c>
       <c r="W9" t="n">
         <v>59</v>
       </c>
       <c r="X9" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="n">
         <v>20242025</v>
@@ -2127,22 +2003,22 @@
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="n">
-        <v>25</v>
+        <v>24.1</v>
       </c>
       <c r="AJ9" t="n">
-        <v>184.6363636363636</v>
+        <v>184</v>
       </c>
       <c r="AK9" t="n">
         <v>1</v>
       </c>
       <c r="AL9" t="n">
-        <v>67.63636363636364</v>
+        <v>66.3</v>
       </c>
       <c r="AM9" t="n">
-        <v>1484090.909090909</v>
+        <v>1177500</v>
       </c>
       <c r="AN9" t="n">
-        <v>70.63636363636364</v>
+        <v>71.2</v>
       </c>
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr"/>
@@ -2151,22 +2027,22 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
       <c r="AU9" t="n">
-        <v>25.22222222222222</v>
+        <v>26.26315789473684</v>
       </c>
       <c r="AV9" t="n">
-        <v>180.9444444444445</v>
+        <v>181</v>
       </c>
       <c r="AW9" t="n">
         <v>1</v>
       </c>
       <c r="AX9" t="n">
-        <v>67.5</v>
+        <v>65.78947368421052</v>
       </c>
       <c r="AY9" t="n">
-        <v>1468055.555555556</v>
+        <v>959210.5263157894</v>
       </c>
       <c r="AZ9" t="n">
-        <v>71.11111111111111</v>
+        <v>67.52631578947368</v>
       </c>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
@@ -2186,179 +2062,131 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>EeIMLi2t</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45507.64583333334</v>
+        <v>45522.4375</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">speckner m 
   ger </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">veltins arena
-  gelsenkirchen </t>
+          <t xml:space="preserve">stadion am panzenberg
+  bremen </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>62271</v>
+        <v>5000</v>
       </c>
       <c r="F10" t="n">
-        <v>61000</v>
+        <v>3500</v>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
+          <t>tW75B1ei</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>QqLCC3il</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.21</v>
-      </c>
+          <t>G2Op923t</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="N10" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="O10" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="P10" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Q10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S10" t="n">
         <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>txZLBQVC</t>
+          <t>4tvZg2Br</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>SQrxFAMl</t>
+          <t>0AI1QUJH</t>
         </is>
       </c>
       <c r="W10" t="n">
         <v>59</v>
       </c>
       <c r="X10" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>dfNCCCzS</t>
-        </is>
-      </c>
-      <c r="AC10" t="n">
-        <v>26.25</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>187.125</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>69</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1740625</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>25.375</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>183.25</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>66.875</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1287500</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>71.875</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>27.22222222222222</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>190.2222222222222</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>67.94444444444444</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>1294444.444444444</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>70.88888888888889</v>
-      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
       <c r="AU10" t="n">
-        <v>24.57142857142857</v>
+        <v>24.15789473684211</v>
       </c>
       <c r="AV10" t="n">
-        <v>184.9285714285714</v>
+        <v>186.3684210526316</v>
       </c>
       <c r="AW10" t="n">
         <v>1</v>
       </c>
       <c r="AX10" t="n">
-        <v>66.07142857142857</v>
+        <v>66.89473684210526</v>
       </c>
       <c r="AY10" t="n">
-        <v>1302142.857142857</v>
+        <v>1414473.684210526</v>
       </c>
       <c r="AZ10" t="n">
-        <v>71.14285714285714</v>
+        <v>72.31578947368421</v>
       </c>
       <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="inlineStr"/>
@@ -2378,152 +2206,144 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>fiod5WHa</t>
+          <t>AiJ3kset</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45507.33333333334</v>
+        <v>45522.33333333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">bacher m 
+          <t xml:space="preserve">weisbach e 
   ger </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">heinz von heiden arena
-  hannover </t>
+          <t xml:space="preserve">friedrich ludwig jahn sportpark
+  berlin </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>49200</v>
+        <v>19708</v>
       </c>
       <c r="F11" t="n">
-        <v>31800</v>
+        <v>5504</v>
       </c>
       <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>UNr2EUfd</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>24</v>
+      </c>
+      <c r="N11" t="n">
+        <v>76</v>
+      </c>
+      <c r="O11" t="n">
+        <v>5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2</v>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>dfNCCCzS</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>UiCmEP56</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="M11" t="n">
-        <v>58</v>
-      </c>
-      <c r="N11" t="n">
-        <v>42</v>
-      </c>
-      <c r="O11" t="n">
-        <v>16</v>
-      </c>
-      <c r="P11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5</v>
-      </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T11" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>t0ZPdkUl</t>
+          <t>CCww5Qfo</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>zyLSrbZQ</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
       <c r="W11" t="n">
         <v>59</v>
       </c>
       <c r="X11" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>QqLCC3il</t>
-        </is>
-      </c>
+      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>184.3</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2082500</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="n">
-        <v>24.40909090909091</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>183.4545454545455</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>68</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>1812500</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>72.81818181818181</v>
-      </c>
-      <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="inlineStr"/>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="n">
+        <v>24.625</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>185.125</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>4975000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>182.1904761904762</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.476190476190476</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>72.19047619047619</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>4629761.904761905</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>76.95238095238095</v>
+      </c>
       <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr"/>
@@ -2542,29 +2362,29 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>OWxD1lHO</t>
+          <t>6q2yrHgU</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45507.33333333334</v>
+        <v>45522.33333333334</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">haslberger w 
+          <t xml:space="preserve">dankert b 
   ger </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">olympiastadion
-  berlin </t>
+          <t xml:space="preserve">ludwigspark stadion
+  saarbrucken </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>74667</v>
+        <v>16003</v>
       </c>
       <c r="F12" t="n">
-        <v>48591</v>
+        <v>14868</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -2574,139 +2394,115 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2y0u8Wrq</t>
+          <t>fLbhmJ5l</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>G2Op923t</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="L12" t="n">
-        <v>2.1</v>
-      </c>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="N12" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="O12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="T12" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>YmfcAeCo</t>
+          <t>trS1MB7T</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0AI1QUJH</t>
+          <t>tO31cZrF</t>
         </is>
       </c>
       <c r="W12" t="n">
         <v>59</v>
       </c>
       <c r="X12" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="n">
         <v>20242025</v>
       </c>
       <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="n">
-        <v>23.22222222222222</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>183.7777777777778</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.111111111111111</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>69.44444444444444</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2422222.222222222</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>76.11111111111111</v>
-      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="n">
-        <v>25.125</v>
+        <v>26</v>
       </c>
       <c r="AJ12" t="n">
-        <v>183.625</v>
+        <v>182.875</v>
       </c>
       <c r="AK12" t="n">
-        <v>1</v>
+        <v>1.125</v>
       </c>
       <c r="AL12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AM12" t="n">
-        <v>1356250</v>
+        <v>1521875</v>
       </c>
       <c r="AN12" t="n">
-        <v>72</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>23.55</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>184.2</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>69.25</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2360000</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>74.75</v>
-      </c>
+        <v>72.25</v>
+      </c>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
       <c r="AU12" t="n">
-        <v>24.9375</v>
+        <v>26</v>
       </c>
       <c r="AV12" t="n">
-        <v>186.1875</v>
+        <v>178</v>
       </c>
       <c r="AW12" t="n">
-        <v>1</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AX12" t="n">
-        <v>66.9375</v>
+        <v>69.16666666666667</v>
       </c>
       <c r="AY12" t="n">
-        <v>1417187.5</v>
+        <v>1866666.666666667</v>
       </c>
       <c r="AZ12" t="n">
-        <v>72.125</v>
+        <v>70.66666666666667</v>
       </c>
       <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="inlineStr"/>
@@ -2726,29 +2522,29 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>zkVf7hmm</t>
+          <t>fcxqFy2l</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45507.33333333334</v>
+        <v>45521.64583333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">braun r 
+          <t xml:space="preserve">stieler t 
   ger </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">bbbank wildpark
-  karlsruhe </t>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>34302</v>
+        <v>30210</v>
       </c>
       <c r="F13" t="n">
-        <v>25000</v>
+        <v>30210</v>
       </c>
       <c r="G13" t="n">
         <v>3</v>
@@ -2758,147 +2554,147 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>EB3q7jbk</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>6FDqshzF</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1.8</v>
+        <v>2.77</v>
       </c>
       <c r="L13" t="n">
-        <v>1.71</v>
+        <v>2.32</v>
       </c>
       <c r="M13" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="N13" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="O13" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="P13" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>OzPMRhK3</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>tO31cZrF</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="W13" t="n">
         <v>59</v>
       </c>
       <c r="X13" t="n">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="n">
-        <v>20242025</v>
+        <v>2024</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>naWckLmC</t>
+          <t>WG9pOTse</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>CCQGbik8</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="AC13" t="n">
-        <v>26.27272727272727</v>
+        <v>25.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>184.3636363636364</v>
+        <v>184.625</v>
       </c>
       <c r="AE13" t="n">
-        <v>1</v>
+        <v>1.875</v>
       </c>
       <c r="AF13" t="n">
-        <v>67.81818181818181</v>
+        <v>80</v>
       </c>
       <c r="AG13" t="n">
-        <v>1395454.545454545</v>
+        <v>25375000</v>
       </c>
       <c r="AH13" t="n">
-        <v>71.90909090909091</v>
+        <v>83.75</v>
       </c>
       <c r="AI13" t="n">
-        <v>22.77777777777778</v>
+        <v>24.1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>182</v>
+        <v>185.5</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.111111111111111</v>
+        <v>1.3</v>
       </c>
       <c r="AL13" t="n">
-        <v>66</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="AM13" t="n">
-        <v>1697222.222222222</v>
+        <v>9810000</v>
       </c>
       <c r="AN13" t="n">
-        <v>72.55555555555556</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="AO13" t="n">
-        <v>22.78947368421053</v>
+        <v>24.28571428571428</v>
       </c>
       <c r="AP13" t="n">
-        <v>181.1052631578947</v>
+        <v>181.8571428571429</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1</v>
+        <v>2.190476190476191</v>
       </c>
       <c r="AR13" t="n">
-        <v>64.84210526315789</v>
+        <v>82.0952380952381</v>
       </c>
       <c r="AS13" t="n">
-        <v>1087894.736842105</v>
+        <v>50242857.14285714</v>
       </c>
       <c r="AT13" t="n">
-        <v>72.84210526315789</v>
+        <v>85.0952380952381</v>
       </c>
       <c r="AU13" t="n">
-        <v>27.77777777777778</v>
+        <v>23.27777777777778</v>
       </c>
       <c r="AV13" t="n">
-        <v>181.2222222222222</v>
+        <v>183.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.111111111111111</v>
+        <v>1.055555555555556</v>
       </c>
       <c r="AX13" t="n">
-        <v>67.44444444444444</v>
+        <v>72.16666666666667</v>
       </c>
       <c r="AY13" t="n">
-        <v>1377777.777777778</v>
+        <v>6294444.444444444</v>
       </c>
       <c r="AZ13" t="n">
-        <v>70.22222222222223</v>
+        <v>78.05555555555556</v>
       </c>
       <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="inlineStr"/>
@@ -2907,111 +2703,125 @@
       <c r="BE13" t="inlineStr"/>
       <c r="BF13" t="inlineStr"/>
       <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
-      <c r="BI13" t="inlineStr"/>
-      <c r="BJ13" t="inlineStr"/>
-      <c r="BK13" t="inlineStr"/>
-      <c r="BL13" t="inlineStr"/>
-      <c r="BM13" t="inlineStr"/>
-      <c r="BN13" t="inlineStr"/>
+      <c r="BH13" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>191.75</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>289</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>23600000</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>303</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>f5QUJVWh</t>
+          <t>8CpxDyg4</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45507.33333333334</v>
+        <v>45521.54166666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">heft f 
+          <t xml:space="preserve">burda m 
   ger </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">mdcc arena
-  magdeburg </t>
+          <t xml:space="preserve">volksparkstadion
+  hamburg </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>30098</v>
+        <v>57274</v>
       </c>
       <c r="F14" t="n">
-        <v>21469</v>
+        <v>50971</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>YFuz2RLm</t>
+          <t>I1Vk6k3R</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>6in2Eknb</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.72</v>
-      </c>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="N14" t="n">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="O14" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="P14" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
         <v>9</v>
       </c>
-      <c r="Q14" t="n">
-        <v>6</v>
-      </c>
-      <c r="R14" t="n">
-        <v>3</v>
-      </c>
       <c r="S14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>IgZoGKFn</t>
+          <t>AgnJojCs</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>8E8qmw3d</t>
+          <t>IkCftsQm</t>
         </is>
       </c>
       <c r="W14" t="n">
         <v>59</v>
       </c>
       <c r="X14" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="n">
         <v>20242025</v>
       </c>
       <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
@@ -3019,58 +2829,46 @@
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="AJ14" t="n">
-        <v>182.3</v>
+        <v>186.1</v>
       </c>
       <c r="AK14" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>66.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="AM14" t="n">
-        <v>1200000</v>
+        <v>34700000</v>
       </c>
       <c r="AN14" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>24.93333333333333</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>176.3333333333333</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1375000</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>69.59999999999999</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
       <c r="AU14" t="n">
-        <v>25.8</v>
+        <v>23.61904761904762</v>
       </c>
       <c r="AV14" t="n">
-        <v>181.4666666666667</v>
+        <v>183.7142857142857</v>
       </c>
       <c r="AW14" t="n">
-        <v>1</v>
+        <v>1.619047619047619</v>
       </c>
       <c r="AX14" t="n">
-        <v>64.93333333333334</v>
+        <v>76.80952380952381</v>
       </c>
       <c r="AY14" t="n">
-        <v>908333.3333333334</v>
+        <v>21880952.38095238</v>
       </c>
       <c r="AZ14" t="n">
-        <v>68.26666666666667</v>
+        <v>83.0952380952381</v>
       </c>
       <c r="BA14" t="inlineStr"/>
       <c r="BB14" t="inlineStr"/>
@@ -3090,179 +2888,159 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>OA1xkBXI</t>
+          <t>CpiTEcOi</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45506.64583333334</v>
+        <v>45521.54166666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">burda m 
+          <t xml:space="preserve">hartmann r 
   ger </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">rheinenergiestadion
-  cologne </t>
+          <t xml:space="preserve">schuco arena
+  bielefeld </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>50000</v>
+        <v>27332</v>
       </c>
       <c r="F15" t="n">
-        <v>50000</v>
+        <v>26044</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
+          <t>pp38UXK8</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.95</v>
-      </c>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="N15" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="O15" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="P15" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="T15" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>4fX0k7gg</t>
+          <t>KrFXELrR</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>EDRZkDzS</t>
+          <t>t0ZPdkUl</t>
         </is>
       </c>
       <c r="W15" t="n">
         <v>59</v>
       </c>
       <c r="X15" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>88HSzjDr</t>
-        </is>
-      </c>
+      <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="AC15" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>186</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>4680000</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>79</v>
-      </c>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="n">
-        <v>25.7</v>
+        <v>25.5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>183.4</v>
+        <v>184</v>
       </c>
       <c r="AK15" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AL15" t="n">
-        <v>71.2</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AM15" t="n">
-        <v>2470000</v>
+        <v>1932500</v>
       </c>
       <c r="AN15" t="n">
-        <v>73.7</v>
+        <v>72.8</v>
       </c>
       <c r="AO15" t="n">
-        <v>25.78947368421053</v>
+        <v>22.85714285714286</v>
       </c>
       <c r="AP15" t="n">
-        <v>184.7894736842105</v>
+        <v>186.1428571428571</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.210526315789474</v>
+        <v>1</v>
       </c>
       <c r="AR15" t="n">
-        <v>68.63157894736842</v>
+        <v>65.28571428571429</v>
       </c>
       <c r="AS15" t="n">
-        <v>2486315.789473684</v>
+        <v>1321428.571428571</v>
       </c>
       <c r="AT15" t="n">
-        <v>73.05263157894737</v>
+        <v>72.28571428571429</v>
       </c>
       <c r="AU15" t="n">
-        <v>25.25</v>
+        <v>25.09523809523809</v>
       </c>
       <c r="AV15" t="n">
-        <v>183.25</v>
+        <v>184.3333333333333</v>
       </c>
       <c r="AW15" t="n">
-        <v>1</v>
+        <v>1.047619047619048</v>
       </c>
       <c r="AX15" t="n">
-        <v>69.05</v>
+        <v>69.04761904761905</v>
       </c>
       <c r="AY15" t="n">
-        <v>2124000</v>
+        <v>1947619.047619048</v>
       </c>
       <c r="AZ15" t="n">
-        <v>72.75</v>
+        <v>72.95238095238095</v>
       </c>
       <c r="BA15" t="inlineStr"/>
       <c r="BB15" t="inlineStr"/>
@@ -3279,6 +3057,5322 @@
       <c r="BM15" t="inlineStr"/>
       <c r="BN15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>hzyf0b9b</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45521.54166666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bacher m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">new tivoli
+  aachen </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>31026</v>
+      </c>
+      <c r="F16" t="n">
+        <v>29555</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>j3PKcB4E</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>39</v>
+      </c>
+      <c r="N16" t="n">
+        <v>61</v>
+      </c>
+      <c r="O16" t="n">
+        <v>9</v>
+      </c>
+      <c r="P16" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>5</v>
+      </c>
+      <c r="S16" t="n">
+        <v>11</v>
+      </c>
+      <c r="T16" t="n">
+        <v>13</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SfKt2E6n</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="W16" t="n">
+        <v>59</v>
+      </c>
+      <c r="X16" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1760000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="n">
+        <v>24.4375</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>186.3125</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>66.625</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1476562.5</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>71.375</v>
+      </c>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="inlineStr"/>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="inlineStr"/>
+      <c r="BM16" t="inlineStr"/>
+      <c r="BN16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>MZjh9ghT</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45521.4375</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion an der hafenstrasse
+  essen </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>20352</v>
+      </c>
+      <c r="F17" t="n">
+        <v>17000</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>EB0xsr77</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>41</v>
+      </c>
+      <c r="N17" t="n">
+        <v>59</v>
+      </c>
+      <c r="O17" t="n">
+        <v>7</v>
+      </c>
+      <c r="P17" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>9</v>
+      </c>
+      <c r="S17" t="n">
+        <v>9</v>
+      </c>
+      <c r="T17" t="n">
+        <v>9</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>0KMe4S4D</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="W17" t="n">
+        <v>59</v>
+      </c>
+      <c r="X17" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="n">
+        <v>25.45454545454545</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>183.2727272727273</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>2.090909090909091</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>79.81818181818181</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>26636363.63636364</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>83.36363636363636</v>
+      </c>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="n">
+        <v>23.15384615384615</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>184.2307692307692</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.769230769230769</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>76.92307692307692</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>22559615.38461538</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>81.84615384615384</v>
+      </c>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
+      <c r="BI17" t="inlineStr"/>
+      <c r="BJ17" t="inlineStr"/>
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="inlineStr"/>
+      <c r="BM17" t="inlineStr"/>
+      <c r="BN17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>f1nnRRDE</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45521.4375</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reichel t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion an der bremer bruck
+  osnabruck </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>16667</v>
+      </c>
+      <c r="F18" t="n">
+        <v>15500</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>88Xgj1Y5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>49</v>
+      </c>
+      <c r="N18" t="n">
+        <v>51</v>
+      </c>
+      <c r="O18" t="n">
+        <v>8</v>
+      </c>
+      <c r="P18" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6</v>
+      </c>
+      <c r="S18" t="n">
+        <v>6</v>
+      </c>
+      <c r="T18" t="n">
+        <v>8</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>lxrr7DgN</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="W18" t="n">
+        <v>59</v>
+      </c>
+      <c r="X18" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="n">
+        <v>25.88888888888889</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>183.3333333333333</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>75.11111111111111</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>10033333.33333333</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>77.44444444444444</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>22.27272727272727</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>186.4545454545455</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>62.90909090909091</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>863636.3636363636</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>72</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>26.95652173913043</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>182.1304347826087</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.608695652173913</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>74.08695652173913</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>6278260.869565218</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>76.04347826086956</v>
+      </c>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr"/>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="inlineStr"/>
+      <c r="BM18" t="inlineStr"/>
+      <c r="BN18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>tbKZHNz1</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45521.4375</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">braun r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audi sportpark
+  ingolstadt </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>15800</v>
+      </c>
+      <c r="F19" t="n">
+        <v>11655</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ne5QkLtB</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>45</v>
+      </c>
+      <c r="N19" t="n">
+        <v>55</v>
+      </c>
+      <c r="O19" t="n">
+        <v>13</v>
+      </c>
+      <c r="P19" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>10</v>
+      </c>
+      <c r="R19" t="n">
+        <v>4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>19</v>
+      </c>
+      <c r="T19" t="n">
+        <v>14</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>CWcD8UM8</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>4bJLk19p</t>
+        </is>
+      </c>
+      <c r="W19" t="n">
+        <v>59</v>
+      </c>
+      <c r="X19" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>182.95</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1510000</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>70.34999999999999</v>
+      </c>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="inlineStr"/>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="inlineStr"/>
+      <c r="BM19" t="inlineStr"/>
+      <c r="BN19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>vyk5gjdE</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45521.4375</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">benen l 
+  ger </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volksstadion greifswald
+  greifswald </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4990</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4990</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Q1yNyI5t</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>39</v>
+      </c>
+      <c r="N20" t="n">
+        <v>61</v>
+      </c>
+      <c r="O20" t="n">
+        <v>6</v>
+      </c>
+      <c r="P20" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>5</v>
+      </c>
+      <c r="S20" t="n">
+        <v>6</v>
+      </c>
+      <c r="T20" t="n">
+        <v>12</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Wbz1kusU</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="W20" t="n">
+        <v>59</v>
+      </c>
+      <c r="X20" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>185.5555555555555</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>75.44444444444444</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>7833333.333333333</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>77.22222222222223</v>
+      </c>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="n">
+        <v>25.69565217391304</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>184.304347826087</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.391304347826087</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>71.65217391304348</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>4054347.826086957</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>76.30434782608695</v>
+      </c>
+      <c r="BA20" t="inlineStr"/>
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="inlineStr"/>
+      <c r="BG20" t="inlineStr"/>
+      <c r="BH20" t="inlineStr"/>
+      <c r="BI20" t="inlineStr"/>
+      <c r="BJ20" t="inlineStr"/>
+      <c r="BK20" t="inlineStr"/>
+      <c r="BL20" t="inlineStr"/>
+      <c r="BM20" t="inlineStr"/>
+      <c r="BN20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>bF2q76Mr</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45521.4375</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brych f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ostalb arena
+  aalen </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>14500</v>
+      </c>
+      <c r="F21" t="n">
+        <v>10850</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Oh2C15j0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>32</v>
+      </c>
+      <c r="N21" t="n">
+        <v>68</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4</v>
+      </c>
+      <c r="P21" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>8</v>
+      </c>
+      <c r="S21" t="n">
+        <v>17</v>
+      </c>
+      <c r="T21" t="n">
+        <v>16</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>8bJFOfzK</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>txZLBQVC</t>
+        </is>
+      </c>
+      <c r="W21" t="n">
+        <v>59</v>
+      </c>
+      <c r="X21" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="n">
+        <v>25.28571428571428</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>188.5714285714286</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>66.14285714285714</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1089285.714285714</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>70.28571428571429</v>
+      </c>
+      <c r="BA21" t="inlineStr"/>
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="inlineStr"/>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="inlineStr"/>
+      <c r="BJ21" t="inlineStr"/>
+      <c r="BK21" t="inlineStr"/>
+      <c r="BL21" t="inlineStr"/>
+      <c r="BM21" t="inlineStr"/>
+      <c r="BN21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>8QPARz8c</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45521.4375</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">michel f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ms technologie arena
+  villingen schwenningen </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F22" t="n">
+        <v>6800</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>lKLJUxeT</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>33</v>
+      </c>
+      <c r="N22" t="n">
+        <v>67</v>
+      </c>
+      <c r="O22" t="n">
+        <v>6</v>
+      </c>
+      <c r="P22" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>9</v>
+      </c>
+      <c r="S22" t="n">
+        <v>7</v>
+      </c>
+      <c r="T22" t="n">
+        <v>9</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>lli2SfLl</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="W22" t="n">
+        <v>59</v>
+      </c>
+      <c r="X22" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>188.25</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>72.125</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>2837500</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>74.125</v>
+      </c>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>187.1111111111111</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>69.77777777777777</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>2063888.888888889</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>72.61111111111111</v>
+      </c>
+      <c r="BA22" t="inlineStr"/>
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="inlineStr"/>
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="inlineStr"/>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr"/>
+      <c r="BI22" t="inlineStr"/>
+      <c r="BJ22" t="inlineStr"/>
+      <c r="BK22" t="inlineStr"/>
+      <c r="BL22" t="inlineStr"/>
+      <c r="BM22" t="inlineStr"/>
+      <c r="BN22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>0K2qBFNG</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45521.33333333334</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badstubner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">erzgebirgsstadion
+  aue </t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>16485</v>
+      </c>
+      <c r="F23" t="n">
+        <v>14811</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>vsXIDreP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>53</v>
+      </c>
+      <c r="N23" t="n">
+        <v>47</v>
+      </c>
+      <c r="O23" t="n">
+        <v>8</v>
+      </c>
+      <c r="P23" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3</v>
+      </c>
+      <c r="R23" t="n">
+        <v>11</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>9</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>rPfNaCdg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="W23" t="n">
+        <v>59</v>
+      </c>
+      <c r="X23" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="n">
+        <v>24.81818181818182</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>184</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.545454545454545</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>75.27272727272727</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>9627272.727272727</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>79</v>
+      </c>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="n">
+        <v>24.43478260869565</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>185.4347826086957</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.347826086956522</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>73.47826086956522</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>7100000</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>77.95652173913044</v>
+      </c>
+      <c r="BA23" t="inlineStr"/>
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="inlineStr"/>
+      <c r="BG23" t="inlineStr"/>
+      <c r="BH23" t="inlineStr"/>
+      <c r="BI23" t="inlineStr"/>
+      <c r="BJ23" t="inlineStr"/>
+      <c r="BK23" t="inlineStr"/>
+      <c r="BL23" t="inlineStr"/>
+      <c r="BM23" t="inlineStr"/>
+      <c r="BN23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Kj4sifWp</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45521.33333333334</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prigan f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bruchwegstadion
+  mainz </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>7134</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4235</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>WzEYqEyg</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>35</v>
+      </c>
+      <c r="N24" t="n">
+        <v>65</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4</v>
+      </c>
+      <c r="P24" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>pvucOaW7</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>8E86CPuD</t>
+        </is>
+      </c>
+      <c r="W24" t="n">
+        <v>59</v>
+      </c>
+      <c r="X24" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>183.3</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1605000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="n">
+        <v>22.60869565217391</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>183.2173913043478</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>64.08695652173913</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1201086.956521739</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>72.73913043478261</v>
+      </c>
+      <c r="BA24" t="inlineStr"/>
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="inlineStr"/>
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="inlineStr"/>
+      <c r="BG24" t="inlineStr"/>
+      <c r="BH24" t="inlineStr"/>
+      <c r="BI24" t="inlineStr"/>
+      <c r="BJ24" t="inlineStr"/>
+      <c r="BK24" t="inlineStr"/>
+      <c r="BL24" t="inlineStr"/>
+      <c r="BM24" t="inlineStr"/>
+      <c r="BN24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>lONsG15D</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45520.65625</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jablonski s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">donaustadion
+  ulm </t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>19500</v>
+      </c>
+      <c r="F25" t="n">
+        <v>17400</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>tbC3EcQn</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>27</v>
+      </c>
+      <c r="N25" t="n">
+        <v>73</v>
+      </c>
+      <c r="O25" t="n">
+        <v>5</v>
+      </c>
+      <c r="P25" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>5</v>
+      </c>
+      <c r="S25" t="n">
+        <v>11</v>
+      </c>
+      <c r="T25" t="n">
+        <v>11</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>QevvB2nf</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="W25" t="n">
+        <v>59</v>
+      </c>
+      <c r="X25" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="n">
+        <v>25.81818181818182</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>183.5454545454545</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>2.727272727272727</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>81.18181818181819</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>37700000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>85.18181818181819</v>
+      </c>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="n">
+        <v>25.35294117647059</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>184.6470588235294</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>3.176470588235294</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>82.41176470588235</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>55613235.29411764</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>85.52941176470588</v>
+      </c>
+      <c r="BA25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="inlineStr"/>
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="inlineStr"/>
+      <c r="BG25" t="inlineStr"/>
+      <c r="BH25" t="inlineStr"/>
+      <c r="BI25" t="inlineStr"/>
+      <c r="BJ25" t="inlineStr"/>
+      <c r="BK25" t="inlineStr"/>
+      <c r="BL25" t="inlineStr"/>
+      <c r="BM25" t="inlineStr"/>
+      <c r="BN25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>pWQQJq6l</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45520.54166666666</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">siebert d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leuna chemie stadion
+  halle </t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>15057</v>
+      </c>
+      <c r="F26" t="n">
+        <v>14000</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>boX3cIQa</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>34</v>
+      </c>
+      <c r="N26" t="n">
+        <v>66</v>
+      </c>
+      <c r="O26" t="n">
+        <v>9</v>
+      </c>
+      <c r="P26" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>8</v>
+      </c>
+      <c r="S26" t="n">
+        <v>14</v>
+      </c>
+      <c r="T26" t="n">
+        <v>12</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>02hM7hzd</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="W26" t="n">
+        <v>59</v>
+      </c>
+      <c r="X26" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>185.8888888888889</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>70.22222222222223</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>2277777.777777778</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>73.77777777777777</v>
+      </c>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="n">
+        <v>23.94444444444444</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>183.9444444444445</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>68.38888888888889</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1944444.444444444</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="BA26" t="inlineStr"/>
+      <c r="BB26" t="inlineStr"/>
+      <c r="BC26" t="inlineStr"/>
+      <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="inlineStr"/>
+      <c r="BF26" t="inlineStr"/>
+      <c r="BG26" t="inlineStr"/>
+      <c r="BH26" t="inlineStr"/>
+      <c r="BI26" t="inlineStr"/>
+      <c r="BJ26" t="inlineStr"/>
+      <c r="BK26" t="inlineStr"/>
+      <c r="BL26" t="inlineStr"/>
+      <c r="BM26" t="inlineStr"/>
+      <c r="BN26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>hIsO3XFj</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45520.54166666666</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hempel r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brita arena
+  wiesbaden </t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>12566</v>
+      </c>
+      <c r="F27" t="n">
+        <v>12500</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ObxFt3lm</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>35</v>
+      </c>
+      <c r="N27" t="n">
+        <v>65</v>
+      </c>
+      <c r="O27" t="n">
+        <v>8</v>
+      </c>
+      <c r="P27" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6</v>
+      </c>
+      <c r="S27" t="n">
+        <v>19</v>
+      </c>
+      <c r="T27" t="n">
+        <v>18</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>QTAUlvUP</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="W27" t="n">
+        <v>59</v>
+      </c>
+      <c r="X27" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>6100000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>24.53846153846154</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>183.3846153846154</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>63.76923076923077</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>769230.7692307692</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>67.23076923076923</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>71</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>3146250</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="BA27" t="inlineStr"/>
+      <c r="BB27" t="inlineStr"/>
+      <c r="BC27" t="inlineStr"/>
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr"/>
+      <c r="BF27" t="inlineStr"/>
+      <c r="BG27" t="inlineStr"/>
+      <c r="BH27" t="inlineStr"/>
+      <c r="BI27" t="inlineStr"/>
+      <c r="BJ27" t="inlineStr"/>
+      <c r="BK27" t="inlineStr"/>
+      <c r="BL27" t="inlineStr"/>
+      <c r="BM27" t="inlineStr"/>
+      <c r="BN27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>EF8gXauC</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45520.54166666666</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">petersen m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flyeralarm arena
+  wurzburger </t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>13090</v>
+      </c>
+      <c r="F28" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>nVM1YUFj</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>31</v>
+      </c>
+      <c r="N28" t="n">
+        <v>69</v>
+      </c>
+      <c r="O28" t="n">
+        <v>9</v>
+      </c>
+      <c r="P28" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4</v>
+      </c>
+      <c r="R28" t="n">
+        <v>8</v>
+      </c>
+      <c r="S28" t="n">
+        <v>11</v>
+      </c>
+      <c r="T28" t="n">
+        <v>13</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>lEwgk7go</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="W28" t="n">
+        <v>59</v>
+      </c>
+      <c r="X28" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>186.8888888888889</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>73.22222222222223</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>7694444.444444444</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>76.88888888888889</v>
+      </c>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="n">
+        <v>23.94117647058824</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>184.4117647058823</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.529411764705882</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>72.05882352941177</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>7377941.176470588</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>78.58823529411765</v>
+      </c>
+      <c r="BA28" t="inlineStr"/>
+      <c r="BB28" t="inlineStr"/>
+      <c r="BC28" t="inlineStr"/>
+      <c r="BD28" t="inlineStr"/>
+      <c r="BE28" t="inlineStr"/>
+      <c r="BF28" t="inlineStr"/>
+      <c r="BG28" t="inlineStr"/>
+      <c r="BH28" t="inlineStr"/>
+      <c r="BI28" t="inlineStr"/>
+      <c r="BJ28" t="inlineStr"/>
+      <c r="BK28" t="inlineStr"/>
+      <c r="BL28" t="inlineStr"/>
+      <c r="BM28" t="inlineStr"/>
+      <c r="BN28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>MqxqEaN6</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45515.35416666666</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">erbst l 
+  ger </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">preussenstadion
+  munster </t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>12794</v>
+      </c>
+      <c r="F29" t="n">
+        <v>12422</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>zedZaSL7</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M29" t="n">
+        <v>47</v>
+      </c>
+      <c r="N29" t="n">
+        <v>53</v>
+      </c>
+      <c r="O29" t="n">
+        <v>11</v>
+      </c>
+      <c r="P29" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" t="n">
+        <v>13</v>
+      </c>
+      <c r="T29" t="n">
+        <v>11</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>pdPRS0me</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>t0ZPdkUl</t>
+        </is>
+      </c>
+      <c r="W29" t="n">
+        <v>59</v>
+      </c>
+      <c r="X29" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>2082500</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>25.57142857142857</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>181.8571428571429</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>66.71428571428571</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1175000</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>68.42857142857143</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>24.17391304347826</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>183.5652173913043</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>67.56521739130434</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1753260.869565217</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>72.60869565217391</v>
+      </c>
+      <c r="BA29" t="inlineStr"/>
+      <c r="BB29" t="inlineStr"/>
+      <c r="BC29" t="inlineStr"/>
+      <c r="BD29" t="inlineStr"/>
+      <c r="BE29" t="inlineStr"/>
+      <c r="BF29" t="inlineStr"/>
+      <c r="BG29" t="inlineStr"/>
+      <c r="BH29" t="inlineStr"/>
+      <c r="BI29" t="inlineStr"/>
+      <c r="BJ29" t="inlineStr"/>
+      <c r="BK29" t="inlineStr"/>
+      <c r="BL29" t="inlineStr"/>
+      <c r="BM29" t="inlineStr"/>
+      <c r="BN29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>KdD11Mw1</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45515.35416666666</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schwengers p 
+  ger </t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">home deluxe arena
+  paderborn </t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F30" t="n">
+        <v>12972</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>G2Op923t</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>S0hPB9rA</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="M30" t="n">
+        <v>54</v>
+      </c>
+      <c r="N30" t="n">
+        <v>46</v>
+      </c>
+      <c r="O30" t="n">
+        <v>18</v>
+      </c>
+      <c r="P30" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>5</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7</v>
+      </c>
+      <c r="S30" t="n">
+        <v>8</v>
+      </c>
+      <c r="T30" t="n">
+        <v>11</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>0AI1QUJH</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>MDhPV0RQ</t>
+        </is>
+      </c>
+      <c r="W30" t="n">
+        <v>59</v>
+      </c>
+      <c r="X30" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="AC30" t="n">
+        <v>25.125</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>183.625</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>67</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1356250</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>72</v>
+      </c>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="n">
+        <v>25.11111111111111</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>186.1111111111111</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>67.22222222222223</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1555555.555555556</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>72.55555555555556</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>24.27777777777778</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>184.8888888888889</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>68.44444444444444</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1895833.333333333</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>73.66666666666667</v>
+      </c>
+      <c r="BA30" t="inlineStr"/>
+      <c r="BB30" t="inlineStr"/>
+      <c r="BC30" t="inlineStr"/>
+      <c r="BD30" t="inlineStr"/>
+      <c r="BE30" t="inlineStr"/>
+      <c r="BF30" t="inlineStr"/>
+      <c r="BG30" t="inlineStr"/>
+      <c r="BH30" t="inlineStr"/>
+      <c r="BI30" t="inlineStr"/>
+      <c r="BJ30" t="inlineStr"/>
+      <c r="BK30" t="inlineStr"/>
+      <c r="BL30" t="inlineStr"/>
+      <c r="BM30" t="inlineStr"/>
+      <c r="BN30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>QHrzGLhf</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45515.35416666666</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reichel t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eintracht stadion
+  braunschweig </t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>23325</v>
+      </c>
+      <c r="F31" t="n">
+        <v>22791</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>YFuz2RLm</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="L31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M31" t="n">
+        <v>49</v>
+      </c>
+      <c r="N31" t="n">
+        <v>51</v>
+      </c>
+      <c r="O31" t="n">
+        <v>20</v>
+      </c>
+      <c r="P31" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>8</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6</v>
+      </c>
+      <c r="S31" t="n">
+        <v>9</v>
+      </c>
+      <c r="T31" t="n">
+        <v>15</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SQrxFAMl</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>IgZoGKFn</t>
+        </is>
+      </c>
+      <c r="W31" t="n">
+        <v>59</v>
+      </c>
+      <c r="X31" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="n">
+        <v>25.625</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>186.125</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>67.75</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1428125</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="n">
+        <v>25.1875</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>182</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>66.8125</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1287500</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>70.9375</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>24.73684210526316</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>178.7368421052632</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>67.36842105263158</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1485526.315789474</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>70.26315789473684</v>
+      </c>
+      <c r="BA31" t="inlineStr"/>
+      <c r="BB31" t="inlineStr"/>
+      <c r="BC31" t="inlineStr"/>
+      <c r="BD31" t="inlineStr"/>
+      <c r="BE31" t="inlineStr"/>
+      <c r="BF31" t="inlineStr"/>
+      <c r="BG31" t="inlineStr"/>
+      <c r="BH31" t="inlineStr"/>
+      <c r="BI31" t="inlineStr"/>
+      <c r="BJ31" t="inlineStr"/>
+      <c r="BK31" t="inlineStr"/>
+      <c r="BL31" t="inlineStr"/>
+      <c r="BM31" t="inlineStr"/>
+      <c r="BN31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>CW9g3r9l</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45514.64583333334</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gerach t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volksparkstadion
+  hamburg </t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>57274</v>
+      </c>
+      <c r="F32" t="n">
+        <v>57000</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2y0u8Wrq</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="M32" t="n">
+        <v>48</v>
+      </c>
+      <c r="N32" t="n">
+        <v>52</v>
+      </c>
+      <c r="O32" t="n">
+        <v>13</v>
+      </c>
+      <c r="P32" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3</v>
+      </c>
+      <c r="R32" t="n">
+        <v>4</v>
+      </c>
+      <c r="S32" t="n">
+        <v>9</v>
+      </c>
+      <c r="T32" t="n">
+        <v>8</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>YmfcAeCo</t>
+        </is>
+      </c>
+      <c r="W32" t="n">
+        <v>59</v>
+      </c>
+      <c r="X32" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2470000</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>183.3</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>2420000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>25.70588235294118</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>184.5294117647059</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>70.23529411764706</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2645882.352941176</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>73.05882352941177</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>23.56521739130435</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>184.2173913043478</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>68.43478260869566</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1948913.043478261</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>74.39130434782609</v>
+      </c>
+      <c r="BA32" t="inlineStr"/>
+      <c r="BB32" t="inlineStr"/>
+      <c r="BC32" t="inlineStr"/>
+      <c r="BD32" t="inlineStr"/>
+      <c r="BE32" t="inlineStr"/>
+      <c r="BF32" t="inlineStr"/>
+      <c r="BG32" t="inlineStr"/>
+      <c r="BH32" t="inlineStr"/>
+      <c r="BI32" t="inlineStr"/>
+      <c r="BJ32" t="inlineStr"/>
+      <c r="BK32" t="inlineStr"/>
+      <c r="BL32" t="inlineStr"/>
+      <c r="BM32" t="inlineStr"/>
+      <c r="BN32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>IViLLjPF</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45514.33333333334</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">merkur spiel arena
+  dusseldorf </t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>54600</v>
+      </c>
+      <c r="F33" t="n">
+        <v>36103</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ne1oL3y7</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>EB3q7jbk</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M33" t="n">
+        <v>53</v>
+      </c>
+      <c r="N33" t="n">
+        <v>47</v>
+      </c>
+      <c r="O33" t="n">
+        <v>20</v>
+      </c>
+      <c r="P33" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>6</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2</v>
+      </c>
+      <c r="S33" t="n">
+        <v>6</v>
+      </c>
+      <c r="T33" t="n">
+        <v>6</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>AoL97rX8</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>OzPMRhK3</t>
+        </is>
+      </c>
+      <c r="W33" t="n">
+        <v>59</v>
+      </c>
+      <c r="X33" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="AC33" t="n">
+        <v>25.63636363636364</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>182.7272727272727</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>70</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>2334090.909090909</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>73.90909090909091</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>26.27272727272727</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>184.3636363636364</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>67.81818181818181</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1395454.545454545</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>71.90909090909091</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>22.69230769230769</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>186.3846153846154</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>66</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>1753846.153846154</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>73.53846153846153</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>23.3125</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>181</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1126250</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>72.5625</v>
+      </c>
+      <c r="BA33" t="inlineStr"/>
+      <c r="BB33" t="inlineStr"/>
+      <c r="BC33" t="inlineStr"/>
+      <c r="BD33" t="inlineStr"/>
+      <c r="BE33" t="inlineStr"/>
+      <c r="BF33" t="inlineStr"/>
+      <c r="BG33" t="inlineStr"/>
+      <c r="BH33" t="inlineStr"/>
+      <c r="BI33" t="inlineStr"/>
+      <c r="BJ33" t="inlineStr"/>
+      <c r="BK33" t="inlineStr"/>
+      <c r="BL33" t="inlineStr"/>
+      <c r="BM33" t="inlineStr"/>
+      <c r="BN33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>tC1Aa08D</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45514.33333333334</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bauer t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waldstadion kaiserlinde
+  spiesen elversberg </t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>9970</v>
+      </c>
+      <c r="F34" t="n">
+        <v>9502</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="L34" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="M34" t="n">
+        <v>45</v>
+      </c>
+      <c r="N34" t="n">
+        <v>55</v>
+      </c>
+      <c r="O34" t="n">
+        <v>10</v>
+      </c>
+      <c r="P34" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3</v>
+      </c>
+      <c r="R34" t="n">
+        <v>9</v>
+      </c>
+      <c r="S34" t="n">
+        <v>13</v>
+      </c>
+      <c r="T34" t="n">
+        <v>13</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>8E8qmw3d</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>4fX0k7gg</t>
+        </is>
+      </c>
+      <c r="W34" t="n">
+        <v>59</v>
+      </c>
+      <c r="X34" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="AC34" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>182.3</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>185.4545454545455</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>71.27272727272727</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>4545454.545454546</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>78.63636363636364</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>25.30769230769231</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>182.3076923076923</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>65.23076923076923</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>975000</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>69.07692307692308</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>186.5714285714286</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>69.47619047619048</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>2787619.047619048</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>73.19047619047619</v>
+      </c>
+      <c r="BA34" t="inlineStr"/>
+      <c r="BB34" t="inlineStr"/>
+      <c r="BC34" t="inlineStr"/>
+      <c r="BD34" t="inlineStr"/>
+      <c r="BE34" t="inlineStr"/>
+      <c r="BF34" t="inlineStr"/>
+      <c r="BG34" t="inlineStr"/>
+      <c r="BH34" t="inlineStr"/>
+      <c r="BI34" t="inlineStr"/>
+      <c r="BJ34" t="inlineStr"/>
+      <c r="BK34" t="inlineStr"/>
+      <c r="BL34" t="inlineStr"/>
+      <c r="BM34" t="inlineStr"/>
+      <c r="BN34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>YJ3eN30K</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45514.33333333334</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">winter n 
+  ger </t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">max morlock stadion
+  nuremberg </t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>44308</v>
+      </c>
+      <c r="F35" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M35" t="n">
+        <v>51</v>
+      </c>
+      <c r="N35" t="n">
+        <v>49</v>
+      </c>
+      <c r="O35" t="n">
+        <v>8</v>
+      </c>
+      <c r="P35" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>5</v>
+      </c>
+      <c r="R35" t="n">
+        <v>5</v>
+      </c>
+      <c r="S35" t="n">
+        <v>11</v>
+      </c>
+      <c r="T35" t="n">
+        <v>12</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>tO31cZrF</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>txZLBQVC</t>
+        </is>
+      </c>
+      <c r="W35" t="n">
+        <v>59</v>
+      </c>
+      <c r="X35" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="AC35" t="n">
+        <v>22.77777777777778</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>182</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>66</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1697222.222222222</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>72.55555555555556</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>25.625</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>189.75</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>67.625</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1540625</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>28.125</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>180</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>67.875</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1209375</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>70</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>26.57142857142857</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>186.7142857142857</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>68.57142857142857</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1428571.428571429</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>70.57142857142857</v>
+      </c>
+      <c r="BA35" t="inlineStr"/>
+      <c r="BB35" t="inlineStr"/>
+      <c r="BC35" t="inlineStr"/>
+      <c r="BD35" t="inlineStr"/>
+      <c r="BE35" t="inlineStr"/>
+      <c r="BF35" t="inlineStr"/>
+      <c r="BG35" t="inlineStr"/>
+      <c r="BH35" t="inlineStr"/>
+      <c r="BI35" t="inlineStr"/>
+      <c r="BJ35" t="inlineStr"/>
+      <c r="BK35" t="inlineStr"/>
+      <c r="BL35" t="inlineStr"/>
+      <c r="BM35" t="inlineStr"/>
+      <c r="BN35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>StuiCwhJ</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45513.5625</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">benen l 
+  ger </t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jahnstadion regensburg
+  regensburg </t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>15210</v>
+      </c>
+      <c r="F36" t="n">
+        <v>12095</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>UiCmEP56</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>tbC3EcQn</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="M36" t="n">
+        <v>49</v>
+      </c>
+      <c r="N36" t="n">
+        <v>51</v>
+      </c>
+      <c r="O36" t="n">
+        <v>8</v>
+      </c>
+      <c r="P36" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>5</v>
+      </c>
+      <c r="S36" t="n">
+        <v>22</v>
+      </c>
+      <c r="T36" t="n">
+        <v>16</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>zyLSrbZQ</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>QevvB2nf</t>
+        </is>
+      </c>
+      <c r="W36" t="n">
+        <v>59</v>
+      </c>
+      <c r="X36" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr"/>
+      <c r="AR36" t="inlineStr"/>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AU36" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>183</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>62</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>887500</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BA36" t="inlineStr"/>
+      <c r="BB36" t="inlineStr"/>
+      <c r="BC36" t="inlineStr"/>
+      <c r="BD36" t="inlineStr"/>
+      <c r="BE36" t="inlineStr"/>
+      <c r="BF36" t="inlineStr"/>
+      <c r="BG36" t="inlineStr"/>
+      <c r="BH36" t="inlineStr"/>
+      <c r="BI36" t="inlineStr"/>
+      <c r="BJ36" t="inlineStr"/>
+      <c r="BK36" t="inlineStr"/>
+      <c r="BL36" t="inlineStr"/>
+      <c r="BM36" t="inlineStr"/>
+      <c r="BN36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>h4pSHsOs</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45513.5625</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lechner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fritz walter stadion
+  kaiserslautern </t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>49500</v>
+      </c>
+      <c r="F37" t="n">
+        <v>41632</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="L37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M37" t="n">
+        <v>54</v>
+      </c>
+      <c r="N37" t="n">
+        <v>46</v>
+      </c>
+      <c r="O37" t="n">
+        <v>13</v>
+      </c>
+      <c r="P37" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>7</v>
+      </c>
+      <c r="R37" t="n">
+        <v>8</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="n">
+        <v>14</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>4bJLk19p</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>8E86CPuD</t>
+        </is>
+      </c>
+      <c r="W37" t="n">
+        <v>59</v>
+      </c>
+      <c r="X37" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="AC37" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>184.6363636363636</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>67.63636363636364</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1484090.909090909</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>70.63636363636364</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>183.1</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>67</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1480000</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>25.23529411764706</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>181.4705882352941</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>68.05882352941177</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>1691176.470588235</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>71.29411764705883</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>23.13636363636364</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>183.8181818181818</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>65.31818181818181</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1430681.818181818</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>73.09090909090909</v>
+      </c>
+      <c r="BA37" t="inlineStr"/>
+      <c r="BB37" t="inlineStr"/>
+      <c r="BC37" t="inlineStr"/>
+      <c r="BD37" t="inlineStr"/>
+      <c r="BE37" t="inlineStr"/>
+      <c r="BF37" t="inlineStr"/>
+      <c r="BG37" t="inlineStr"/>
+      <c r="BH37" t="inlineStr"/>
+      <c r="BI37" t="inlineStr"/>
+      <c r="BJ37" t="inlineStr"/>
+      <c r="BK37" t="inlineStr"/>
+      <c r="BL37" t="inlineStr"/>
+      <c r="BM37" t="inlineStr"/>
+      <c r="BN37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>SIOxI915</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45508.35416666666</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schroder r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">donaustadion
+  ulm </t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>19500</v>
+      </c>
+      <c r="F38" t="n">
+        <v>17400</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>tbC3EcQn</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L38" t="n">
+        <v>3</v>
+      </c>
+      <c r="M38" t="n">
+        <v>54</v>
+      </c>
+      <c r="N38" t="n">
+        <v>46</v>
+      </c>
+      <c r="O38" t="n">
+        <v>12</v>
+      </c>
+      <c r="P38" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3</v>
+      </c>
+      <c r="R38" t="n">
+        <v>4</v>
+      </c>
+      <c r="S38" t="n">
+        <v>12</v>
+      </c>
+      <c r="T38" t="n">
+        <v>16</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>QevvB2nf</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>4bJLk19p</t>
+        </is>
+      </c>
+      <c r="W38" t="n">
+        <v>59</v>
+      </c>
+      <c r="X38" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>184.6363636363636</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>67.63636363636364</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1484090.909090909</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>70.63636363636364</v>
+      </c>
+      <c r="AO38" t="inlineStr"/>
+      <c r="AP38" t="inlineStr"/>
+      <c r="AQ38" t="inlineStr"/>
+      <c r="AR38" t="inlineStr"/>
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AU38" t="n">
+        <v>25.22222222222222</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>180.9444444444445</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1468055.555555556</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>71.11111111111111</v>
+      </c>
+      <c r="BA38" t="inlineStr"/>
+      <c r="BB38" t="inlineStr"/>
+      <c r="BC38" t="inlineStr"/>
+      <c r="BD38" t="inlineStr"/>
+      <c r="BE38" t="inlineStr"/>
+      <c r="BF38" t="inlineStr"/>
+      <c r="BG38" t="inlineStr"/>
+      <c r="BH38" t="inlineStr"/>
+      <c r="BI38" t="inlineStr"/>
+      <c r="BJ38" t="inlineStr"/>
+      <c r="BK38" t="inlineStr"/>
+      <c r="BL38" t="inlineStr"/>
+      <c r="BM38" t="inlineStr"/>
+      <c r="BN38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>2Hl43AnC</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45508.35416666666</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hempel r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sportpark ronhof thomas sommer
+  furth </t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>16626</v>
+      </c>
+      <c r="F39" t="n">
+        <v>12664</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>zedZaSL7</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L39" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="M39" t="n">
+        <v>47</v>
+      </c>
+      <c r="N39" t="n">
+        <v>53</v>
+      </c>
+      <c r="O39" t="n">
+        <v>22</v>
+      </c>
+      <c r="P39" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>9</v>
+      </c>
+      <c r="R39" t="n">
+        <v>5</v>
+      </c>
+      <c r="S39" t="n">
+        <v>9</v>
+      </c>
+      <c r="T39" t="n">
+        <v>11</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>8E86CPuD</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>pdPRS0me</t>
+        </is>
+      </c>
+      <c r="W39" t="n">
+        <v>59</v>
+      </c>
+      <c r="X39" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>183.1</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>67</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1480000</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="n">
+        <v>22.72727272727273</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>182.5454545454545</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>64.59090909090909</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1273863.636363636</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>72.86363636363636</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>25.57142857142857</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>181.8571428571429</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>66.71428571428571</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1175000</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>68.42857142857143</v>
+      </c>
+      <c r="BA39" t="inlineStr"/>
+      <c r="BB39" t="inlineStr"/>
+      <c r="BC39" t="inlineStr"/>
+      <c r="BD39" t="inlineStr"/>
+      <c r="BE39" t="inlineStr"/>
+      <c r="BF39" t="inlineStr"/>
+      <c r="BG39" t="inlineStr"/>
+      <c r="BH39" t="inlineStr"/>
+      <c r="BI39" t="inlineStr"/>
+      <c r="BJ39" t="inlineStr"/>
+      <c r="BK39" t="inlineStr"/>
+      <c r="BL39" t="inlineStr"/>
+      <c r="BM39" t="inlineStr"/>
+      <c r="BN39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>vJqPCEPP</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45508.35416666666</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kampka r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">merck stadion am bollenfalltor
+  darmstadt </t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>17810</v>
+      </c>
+      <c r="F40" t="n">
+        <v>17810</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>S0hPB9rA</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>ne1oL3y7</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M40" t="n">
+        <v>47</v>
+      </c>
+      <c r="N40" t="n">
+        <v>53</v>
+      </c>
+      <c r="O40" t="n">
+        <v>11</v>
+      </c>
+      <c r="P40" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>6</v>
+      </c>
+      <c r="R40" t="n">
+        <v>4</v>
+      </c>
+      <c r="S40" t="n">
+        <v>16</v>
+      </c>
+      <c r="T40" t="n">
+        <v>7</v>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>MDhPV0RQ</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>AoL97rX8</t>
+        </is>
+      </c>
+      <c r="W40" t="n">
+        <v>59</v>
+      </c>
+      <c r="X40" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>183.3</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>2490000</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>74</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>25.6875</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>186.25</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>1679687.5</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>73.1875</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>21.95454545454545</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>186.4545454545455</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>64.04545454545455</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>1346590.909090909</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>72.95454545454545</v>
+      </c>
+      <c r="BA40" t="inlineStr"/>
+      <c r="BB40" t="inlineStr"/>
+      <c r="BC40" t="inlineStr"/>
+      <c r="BD40" t="inlineStr"/>
+      <c r="BE40" t="inlineStr"/>
+      <c r="BF40" t="inlineStr"/>
+      <c r="BG40" t="inlineStr"/>
+      <c r="BH40" t="inlineStr"/>
+      <c r="BI40" t="inlineStr"/>
+      <c r="BJ40" t="inlineStr"/>
+      <c r="BK40" t="inlineStr"/>
+      <c r="BL40" t="inlineStr"/>
+      <c r="BM40" t="inlineStr"/>
+      <c r="BN40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>EeIMLi2t</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45507.64583333334</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stieler t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">veltins arena
+  gelsenkirchen </t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>62271</v>
+      </c>
+      <c r="F41" t="n">
+        <v>61000</v>
+      </c>
+      <c r="G41" t="n">
+        <v>5</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M41" t="n">
+        <v>52</v>
+      </c>
+      <c r="N41" t="n">
+        <v>48</v>
+      </c>
+      <c r="O41" t="n">
+        <v>14</v>
+      </c>
+      <c r="P41" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>8</v>
+      </c>
+      <c r="R41" t="n">
+        <v>5</v>
+      </c>
+      <c r="S41" t="n">
+        <v>13</v>
+      </c>
+      <c r="T41" t="n">
+        <v>11</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>txZLBQVC</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>SQrxFAMl</t>
+        </is>
+      </c>
+      <c r="W41" t="n">
+        <v>59</v>
+      </c>
+      <c r="X41" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="AC41" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>187.125</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>69</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1740625</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>183.25</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>66.875</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1287500</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>27.22222222222222</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>190.2222222222222</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>67.94444444444444</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>1294444.444444444</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>70.88888888888889</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>24.57142857142857</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>184.9285714285714</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>66.07142857142857</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1302142.857142857</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>71.14285714285714</v>
+      </c>
+      <c r="BA41" t="inlineStr"/>
+      <c r="BB41" t="inlineStr"/>
+      <c r="BC41" t="inlineStr"/>
+      <c r="BD41" t="inlineStr"/>
+      <c r="BE41" t="inlineStr"/>
+      <c r="BF41" t="inlineStr"/>
+      <c r="BG41" t="inlineStr"/>
+      <c r="BH41" t="inlineStr"/>
+      <c r="BI41" t="inlineStr"/>
+      <c r="BJ41" t="inlineStr"/>
+      <c r="BK41" t="inlineStr"/>
+      <c r="BL41" t="inlineStr"/>
+      <c r="BM41" t="inlineStr"/>
+      <c r="BN41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>fiod5WHa</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>45507.33333333334</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bacher m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heinz von heiden arena
+  hannover </t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>49200</v>
+      </c>
+      <c r="F42" t="n">
+        <v>31800</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>UiCmEP56</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>2</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="M42" t="n">
+        <v>58</v>
+      </c>
+      <c r="N42" t="n">
+        <v>42</v>
+      </c>
+      <c r="O42" t="n">
+        <v>16</v>
+      </c>
+      <c r="P42" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>5</v>
+      </c>
+      <c r="R42" t="n">
+        <v>3</v>
+      </c>
+      <c r="S42" t="n">
+        <v>12</v>
+      </c>
+      <c r="T42" t="n">
+        <v>17</v>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>t0ZPdkUl</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>zyLSrbZQ</t>
+        </is>
+      </c>
+      <c r="W42" t="n">
+        <v>59</v>
+      </c>
+      <c r="X42" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>2082500</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="n">
+        <v>24.40909090909091</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>183.4545454545455</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>68</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>1812500</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>72.81818181818181</v>
+      </c>
+      <c r="AU42" t="inlineStr"/>
+      <c r="AV42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr"/>
+      <c r="AX42" t="inlineStr"/>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr"/>
+      <c r="BA42" t="inlineStr"/>
+      <c r="BB42" t="inlineStr"/>
+      <c r="BC42" t="inlineStr"/>
+      <c r="BD42" t="inlineStr"/>
+      <c r="BE42" t="inlineStr"/>
+      <c r="BF42" t="inlineStr"/>
+      <c r="BG42" t="inlineStr"/>
+      <c r="BH42" t="inlineStr"/>
+      <c r="BI42" t="inlineStr"/>
+      <c r="BJ42" t="inlineStr"/>
+      <c r="BK42" t="inlineStr"/>
+      <c r="BL42" t="inlineStr"/>
+      <c r="BM42" t="inlineStr"/>
+      <c r="BN42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>OWxD1lHO</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>45507.33333333334</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">haslberger w 
+  ger </t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">olympiastadion
+  berlin </t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>74667</v>
+      </c>
+      <c r="F43" t="n">
+        <v>48591</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2y0u8Wrq</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>G2Op923t</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L43" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M43" t="n">
+        <v>57</v>
+      </c>
+      <c r="N43" t="n">
+        <v>43</v>
+      </c>
+      <c r="O43" t="n">
+        <v>10</v>
+      </c>
+      <c r="P43" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3</v>
+      </c>
+      <c r="R43" t="n">
+        <v>5</v>
+      </c>
+      <c r="S43" t="n">
+        <v>16</v>
+      </c>
+      <c r="T43" t="n">
+        <v>7</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>YmfcAeCo</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>0AI1QUJH</t>
+        </is>
+      </c>
+      <c r="W43" t="n">
+        <v>59</v>
+      </c>
+      <c r="X43" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="n">
+        <v>23.22222222222222</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>183.7777777777778</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>69.44444444444444</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>2422222.222222222</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>76.11111111111111</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>25.125</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>183.625</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>67</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>1356250</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>72</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>2360000</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>24.9375</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>186.1875</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>66.9375</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>1417187.5</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>72.125</v>
+      </c>
+      <c r="BA43" t="inlineStr"/>
+      <c r="BB43" t="inlineStr"/>
+      <c r="BC43" t="inlineStr"/>
+      <c r="BD43" t="inlineStr"/>
+      <c r="BE43" t="inlineStr"/>
+      <c r="BF43" t="inlineStr"/>
+      <c r="BG43" t="inlineStr"/>
+      <c r="BH43" t="inlineStr"/>
+      <c r="BI43" t="inlineStr"/>
+      <c r="BJ43" t="inlineStr"/>
+      <c r="BK43" t="inlineStr"/>
+      <c r="BL43" t="inlineStr"/>
+      <c r="BM43" t="inlineStr"/>
+      <c r="BN43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>zkVf7hmm</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>45507.33333333334</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">braun r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bbbank wildpark
+  karlsruhe </t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>34302</v>
+      </c>
+      <c r="F44" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G44" t="n">
+        <v>3</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>EB3q7jbk</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M44" t="n">
+        <v>51</v>
+      </c>
+      <c r="N44" t="n">
+        <v>49</v>
+      </c>
+      <c r="O44" t="n">
+        <v>15</v>
+      </c>
+      <c r="P44" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>5</v>
+      </c>
+      <c r="R44" t="n">
+        <v>5</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="n">
+        <v>12</v>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>OzPMRhK3</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>tO31cZrF</t>
+        </is>
+      </c>
+      <c r="W44" t="n">
+        <v>59</v>
+      </c>
+      <c r="X44" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="AC44" t="n">
+        <v>26.27272727272727</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>184.3636363636364</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>67.81818181818181</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>1395454.545454545</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>71.90909090909091</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>22.77777777777778</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>182</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>66</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>1697222.222222222</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>72.55555555555556</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>22.78947368421053</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>181.1052631578947</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>64.84210526315789</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>1087894.736842105</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>72.84210526315789</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>27.77777777777778</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>181.2222222222222</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>67.44444444444444</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>1377777.777777778</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>70.22222222222223</v>
+      </c>
+      <c r="BA44" t="inlineStr"/>
+      <c r="BB44" t="inlineStr"/>
+      <c r="BC44" t="inlineStr"/>
+      <c r="BD44" t="inlineStr"/>
+      <c r="BE44" t="inlineStr"/>
+      <c r="BF44" t="inlineStr"/>
+      <c r="BG44" t="inlineStr"/>
+      <c r="BH44" t="inlineStr"/>
+      <c r="BI44" t="inlineStr"/>
+      <c r="BJ44" t="inlineStr"/>
+      <c r="BK44" t="inlineStr"/>
+      <c r="BL44" t="inlineStr"/>
+      <c r="BM44" t="inlineStr"/>
+      <c r="BN44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>f5QUJVWh</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>45507.33333333334</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heft f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mdcc arena
+  magdeburg </t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>30098</v>
+      </c>
+      <c r="F45" t="n">
+        <v>21469</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>YFuz2RLm</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M45" t="n">
+        <v>63</v>
+      </c>
+      <c r="N45" t="n">
+        <v>37</v>
+      </c>
+      <c r="O45" t="n">
+        <v>21</v>
+      </c>
+      <c r="P45" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>6</v>
+      </c>
+      <c r="R45" t="n">
+        <v>3</v>
+      </c>
+      <c r="S45" t="n">
+        <v>11</v>
+      </c>
+      <c r="T45" t="n">
+        <v>8</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>IgZoGKFn</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>8E8qmw3d</t>
+        </is>
+      </c>
+      <c r="W45" t="n">
+        <v>59</v>
+      </c>
+      <c r="X45" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>182.3</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>24.93333333333333</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>176.3333333333333</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>1375000</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>181.4666666666667</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>64.93333333333334</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>908333.3333333334</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>68.26666666666667</v>
+      </c>
+      <c r="BA45" t="inlineStr"/>
+      <c r="BB45" t="inlineStr"/>
+      <c r="BC45" t="inlineStr"/>
+      <c r="BD45" t="inlineStr"/>
+      <c r="BE45" t="inlineStr"/>
+      <c r="BF45" t="inlineStr"/>
+      <c r="BG45" t="inlineStr"/>
+      <c r="BH45" t="inlineStr"/>
+      <c r="BI45" t="inlineStr"/>
+      <c r="BJ45" t="inlineStr"/>
+      <c r="BK45" t="inlineStr"/>
+      <c r="BL45" t="inlineStr"/>
+      <c r="BM45" t="inlineStr"/>
+      <c r="BN45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>OA1xkBXI</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>45506.64583333334</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burda m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rheinenergiestadion
+  cologne </t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F46" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M46" t="n">
+        <v>58</v>
+      </c>
+      <c r="N46" t="n">
+        <v>42</v>
+      </c>
+      <c r="O46" t="n">
+        <v>26</v>
+      </c>
+      <c r="P46" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>4</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6</v>
+      </c>
+      <c r="S46" t="n">
+        <v>18</v>
+      </c>
+      <c r="T46" t="n">
+        <v>7</v>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>4fX0k7gg</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+      <c r="W46" t="n">
+        <v>59</v>
+      </c>
+      <c r="X46" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="AC46" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>186</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>4680000</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>79</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>2470000</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>25.78947368421053</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>184.7894736842105</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>1.210526315789474</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>68.63157894736842</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>2486315.789473684</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>73.05263157894737</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>183.25</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>2124000</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="BA46" t="inlineStr"/>
+      <c r="BB46" t="inlineStr"/>
+      <c r="BC46" t="inlineStr"/>
+      <c r="BD46" t="inlineStr"/>
+      <c r="BE46" t="inlineStr"/>
+      <c r="BF46" t="inlineStr"/>
+      <c r="BG46" t="inlineStr"/>
+      <c r="BH46" t="inlineStr"/>
+      <c r="BI46" t="inlineStr"/>
+      <c r="BJ46" t="inlineStr"/>
+      <c r="BK46" t="inlineStr"/>
+      <c r="BL46" t="inlineStr"/>
+      <c r="BM46" t="inlineStr"/>
+      <c r="BN46" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
+++ b/data/germany/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN15"/>
+  <dimension ref="A1:BN50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,179 +762,173 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IViLLjPF</t>
+          <t>pAXo2Kvn</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45514.33333333334</v>
+        <v>45523.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">hartmann r 
+          <t xml:space="preserve">exner f 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">merkur spiel arena
-  dusseldorf </t>
+          <t xml:space="preserve">eintracht stadion
+  braunschweig </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>54600</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36103</v>
-      </c>
+        <v>23325</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ne1oL3y7</t>
+          <t>QqLCC3il</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>EB3q7jbk</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.66</v>
-      </c>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N2" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="O2" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="P2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Q2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T2" t="n">
         <v>6</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>AoL97rX8</t>
+          <t>SQrxFAMl</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>OzPMRhK3</t>
+          <t>UgdQz0fK</t>
         </is>
       </c>
       <c r="W2" t="n">
         <v>59</v>
       </c>
       <c r="X2" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
         <v>20242025</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
+          <t>dfNCCCzS</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>naWckLmC</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="AC2" t="n">
-        <v>25.63636363636364</v>
+        <v>26.375</v>
       </c>
       <c r="AD2" t="n">
-        <v>182.7272727272727</v>
+        <v>185.625</v>
       </c>
       <c r="AE2" t="n">
-        <v>1</v>
+        <v>1.125</v>
       </c>
       <c r="AF2" t="n">
-        <v>70</v>
+        <v>67.625</v>
       </c>
       <c r="AG2" t="n">
-        <v>2334090.909090909</v>
+        <v>1325000</v>
       </c>
       <c r="AH2" t="n">
-        <v>73.90909090909091</v>
+        <v>70.625</v>
       </c>
       <c r="AI2" t="n">
-        <v>26.27272727272727</v>
+        <v>23.77777777777778</v>
       </c>
       <c r="AJ2" t="n">
-        <v>184.3636363636364</v>
+        <v>184.3333333333333</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AL2" t="n">
-        <v>67.81818181818181</v>
+        <v>76.88888888888889</v>
       </c>
       <c r="AM2" t="n">
-        <v>1395454.545454545</v>
+        <v>14777777.77777778</v>
       </c>
       <c r="AN2" t="n">
-        <v>71.90909090909091</v>
+        <v>82</v>
       </c>
       <c r="AO2" t="n">
-        <v>22.69230769230769</v>
+        <v>24.4</v>
       </c>
       <c r="AP2" t="n">
-        <v>186.3846153846154</v>
+        <v>181.5333333333333</v>
       </c>
       <c r="AQ2" t="n">
         <v>1</v>
       </c>
       <c r="AR2" t="n">
-        <v>66</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="AS2" t="n">
-        <v>1753846.153846154</v>
+        <v>1386666.666666667</v>
       </c>
       <c r="AT2" t="n">
-        <v>73.53846153846153</v>
+        <v>71.73333333333333</v>
       </c>
       <c r="AU2" t="n">
-        <v>23.3125</v>
+        <v>20.31578947368421</v>
       </c>
       <c r="AV2" t="n">
-        <v>181</v>
+        <v>185.3684210526316</v>
       </c>
       <c r="AW2" t="n">
-        <v>1</v>
+        <v>1.315789473684211</v>
       </c>
       <c r="AX2" t="n">
-        <v>65.25</v>
+        <v>70.31578947368421</v>
       </c>
       <c r="AY2" t="n">
-        <v>1126250</v>
+        <v>6257894.736842105</v>
       </c>
       <c r="AZ2" t="n">
-        <v>72.5625</v>
+        <v>80.94736842105263</v>
       </c>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="inlineStr"/>
@@ -954,94 +948,88 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>tC1Aa08D</t>
+          <t>EkP2bxvB</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45514.33333333334</v>
+        <v>45523.54166666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bauer t 
+          <t xml:space="preserve">storks s 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">waldstadion kaiserlinde
-  spiesen elversberg </t>
+          <t xml:space="preserve">stadion oberwerth
+  koblenz </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>9970</v>
-      </c>
-      <c r="F3" t="n">
-        <v>9502</v>
-      </c>
+        <v>9500</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>p8wBsqZt</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>24</v>
+      </c>
+      <c r="N3" t="n">
+        <v>76</v>
+      </c>
+      <c r="O3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P3" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
         <v>2</v>
       </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6in2Eknb</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="L3" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="M3" t="n">
-        <v>45</v>
-      </c>
-      <c r="N3" t="n">
-        <v>55</v>
-      </c>
-      <c r="O3" t="n">
-        <v>10</v>
-      </c>
-      <c r="P3" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
+        <v>19</v>
+      </c>
+      <c r="T3" t="n">
         <v>9</v>
       </c>
-      <c r="S3" t="n">
-        <v>13</v>
-      </c>
-      <c r="T3" t="n">
-        <v>13</v>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>8E8qmw3d</t>
+          <t>rFNN7oyi</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>4fX0k7gg</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="W3" t="n">
         <v>59</v>
       </c>
       <c r="X3" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
         <v>20242025</v>
@@ -1049,80 +1037,56 @@
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
-        </is>
-      </c>
-      <c r="AC3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>182.3</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>70.5</v>
-      </c>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>23</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="AJ3" t="n">
-        <v>185.4545454545455</v>
+        <v>185.8888888888889</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.181818181818182</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AL3" t="n">
-        <v>71.27272727272727</v>
+        <v>76</v>
       </c>
       <c r="AM3" t="n">
-        <v>4545454.545454546</v>
+        <v>12611111.11111111</v>
       </c>
       <c r="AN3" t="n">
-        <v>78.63636363636364</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>25.30769230769231</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>182.3076923076923</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>65.23076923076923</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>975000</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>69.07692307692308</v>
-      </c>
+        <v>80.55555555555556</v>
+      </c>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="n">
-        <v>26.33333333333333</v>
+        <v>22.08333333333333</v>
       </c>
       <c r="AV3" t="n">
-        <v>186.5714285714286</v>
+        <v>186.3333333333333</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.380952380952381</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AX3" t="n">
-        <v>69.47619047619048</v>
+        <v>71.75</v>
       </c>
       <c r="AY3" t="n">
-        <v>2787619.047619048</v>
+        <v>6483333.333333333</v>
       </c>
       <c r="AZ3" t="n">
-        <v>73.19047619047619</v>
+        <v>79.16666666666667</v>
       </c>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="inlineStr"/>
@@ -1142,179 +1106,129 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>YJ3eN30K</t>
+          <t>Sff03OL7</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45514.33333333334</v>
+        <v>45523.54166666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">winter n 
+          <t xml:space="preserve">alt p 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">max morlock stadion
-  nuremberg </t>
+          <t xml:space="preserve">bieberer berg stadion
+  offenbach am main </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44308</v>
-      </c>
-      <c r="F4" t="n">
-        <v>50000</v>
-      </c>
+        <v>20500</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6FDqshzF</t>
+          <t>YJURlaIO</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2.12</v>
-      </c>
+          <t>YFuz2RLm</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N4" t="n">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="O4" t="n">
         <v>8</v>
       </c>
       <c r="P4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="T4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>tO31cZrF</t>
+          <t>GWkh67yH</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>txZLBQVC</t>
+          <t>IgZoGKFn</t>
         </is>
       </c>
       <c r="W4" t="n">
         <v>59</v>
       </c>
       <c r="X4" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>CCQGbik8</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="AC4" t="n">
-        <v>22.77777777777778</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>182</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.111111111111111</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>66</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1697222.222222222</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>72.55555555555556</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>25.625</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>189.75</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>67.625</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1540625</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>28.125</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>180</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>67.875</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1209375</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>70</v>
-      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="n">
-        <v>26.57142857142857</v>
+        <v>25.31578947368421</v>
       </c>
       <c r="AV4" t="n">
-        <v>186.7142857142857</v>
+        <v>178.578947368421</v>
       </c>
       <c r="AW4" t="n">
         <v>1</v>
       </c>
       <c r="AX4" t="n">
-        <v>68.57142857142857</v>
+        <v>66.68421052631579</v>
       </c>
       <c r="AY4" t="n">
-        <v>1428571.428571429</v>
+        <v>1192105.263157895</v>
       </c>
       <c r="AZ4" t="n">
-        <v>70.57142857142857</v>
+        <v>69.10526315789474</v>
       </c>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
@@ -1334,94 +1248,88 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>h4pSHsOs</t>
+          <t>06NAdG8N</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45513.5625</v>
+        <v>45523.54166666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">lechner f 
+          <t xml:space="preserve">osmers h 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">fritz walter stadion
-  kaiserslautern </t>
+          <t xml:space="preserve">stadion der freundschaft
+  cottbus </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>49500</v>
-      </c>
-      <c r="F5" t="n">
-        <v>41632</v>
-      </c>
+        <v>22450</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>naWckLmC</t>
+          <t>6g44VD52</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>CCQGbik8</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2.7</v>
-      </c>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="N5" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="O5" t="n">
+        <v>8</v>
+      </c>
+      <c r="P5" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>9</v>
+      </c>
+      <c r="S5" t="n">
         <v>13</v>
       </c>
-      <c r="P5" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>7</v>
-      </c>
-      <c r="R5" t="n">
-        <v>8</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
       <c r="T5" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4bJLk19p</t>
+          <t>tnTvQd1l</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>8E86CPuD</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>59</v>
       </c>
       <c r="X5" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
         <v>20242025</v>
@@ -1429,80 +1337,56 @@
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>6FDqshzF</t>
-        </is>
-      </c>
-      <c r="AC5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>184.6363636363636</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>67.63636363636364</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1484090.909090909</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>70.63636363636364</v>
-      </c>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>25</v>
+        <v>25.45454545454545</v>
       </c>
       <c r="AJ5" t="n">
-        <v>183.1</v>
+        <v>184.2727272727273</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
+        <v>1.181818181818182</v>
       </c>
       <c r="AL5" t="n">
-        <v>67</v>
+        <v>73.27272727272727</v>
       </c>
       <c r="AM5" t="n">
-        <v>1480000</v>
+        <v>5290909.090909091</v>
       </c>
       <c r="AN5" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>25.23529411764706</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>181.4705882352941</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>68.05882352941177</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1691176.470588235</v>
-      </c>
-      <c r="AT5" t="n">
+        <v>76.90909090909091</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="n">
+        <v>25.58823529411765</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>183.0588235294118</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.235294117647059</v>
+      </c>
+      <c r="AX5" t="n">
         <v>71.29411764705883</v>
       </c>
-      <c r="AU5" t="n">
-        <v>23.13636363636364</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>183.8181818181818</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>65.31818181818181</v>
-      </c>
       <c r="AY5" t="n">
-        <v>1430681.818181818</v>
+        <v>3341176.470588235</v>
       </c>
       <c r="AZ5" t="n">
-        <v>73.09090909090909</v>
+        <v>76</v>
       </c>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr"/>
@@ -1522,112 +1406,124 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>StuiCwhJ</t>
+          <t>pzHxyrtm</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45513.5625</v>
+        <v>45522.54166666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">benen l 
+          <t xml:space="preserve">oldhafer k 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">jahnstadion regensburg
-  regensburg </t>
+          <t xml:space="preserve">stadion am lotter kreuz
+  lotte </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>15210</v>
+        <v>10059</v>
       </c>
       <c r="F6" t="n">
-        <v>12095</v>
+        <v>4637</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>UiCmEP56</t>
+          <t>hjNlCFPB</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>tbC3EcQn</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.47</v>
-      </c>
+          <t>EB3q7jbk</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N6" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O6" t="n">
         <v>8</v>
       </c>
       <c r="P6" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S6" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="T6" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>zyLSrbZQ</t>
+          <t>KW0bzbwJ</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>QevvB2nf</t>
+          <t>OzPMRhK3</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>59</v>
       </c>
       <c r="X6" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="n">
         <v>20242025</v>
       </c>
       <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
+      <c r="AI6" t="n">
+        <v>26.18181818181818</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>183.0909090909091</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>67.81818181818181</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1413636.363636364</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>71.72727272727273</v>
+      </c>
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
@@ -1635,22 +1531,22 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="n">
-        <v>21.5</v>
+        <v>25.21428571428572</v>
       </c>
       <c r="AV6" t="n">
-        <v>183</v>
+        <v>183.7142857142857</v>
       </c>
       <c r="AW6" t="n">
         <v>1</v>
       </c>
       <c r="AX6" t="n">
-        <v>62</v>
+        <v>66.21428571428571</v>
       </c>
       <c r="AY6" t="n">
-        <v>887500</v>
+        <v>1071071.428571429</v>
       </c>
       <c r="AZ6" t="n">
-        <v>70.5</v>
+        <v>70.92857142857143</v>
       </c>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
@@ -1670,39 +1566,39 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vJqPCEPP</t>
+          <t>vXAKoaf5</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45508.35416666666</v>
+        <v>45522.54166666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">kampka r 
+          <t xml:space="preserve">stegemann s 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">merck stadion am bollenfalltor
-  darmstadt </t>
+          <t xml:space="preserve">rudolf harbig stadion
+  dresden </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17810</v>
+        <v>32249</v>
       </c>
       <c r="F7" t="n">
-        <v>17810</v>
+        <v>30000</v>
       </c>
       <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="n">
-        <v>2</v>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>S0hPB9rA</t>
+          <t>zL1YsOi1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1710,39 +1606,35 @@
           <t>ne1oL3y7</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.49</v>
-      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O7" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="P7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="T7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>MDhPV0RQ</t>
+          <t>4YhTfKrD</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1754,19 +1646,15 @@
         <v>59</v>
       </c>
       <c r="X7" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
+      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr">
         <is>
           <t>WG9pOTse</t>
@@ -1779,58 +1667,58 @@
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="n">
-        <v>26.3</v>
+        <v>25.36363636363636</v>
       </c>
       <c r="AJ7" t="n">
-        <v>183.3</v>
+        <v>183.8181818181818</v>
       </c>
       <c r="AK7" t="n">
         <v>1</v>
       </c>
       <c r="AL7" t="n">
-        <v>70.90000000000001</v>
+        <v>69.54545454545455</v>
       </c>
       <c r="AM7" t="n">
-        <v>2490000</v>
+        <v>2061363.636363636</v>
       </c>
       <c r="AN7" t="n">
-        <v>74</v>
+        <v>73.36363636363636</v>
       </c>
       <c r="AO7" t="n">
-        <v>25.6875</v>
+        <v>26.28571428571428</v>
       </c>
       <c r="AP7" t="n">
-        <v>186.25</v>
+        <v>180.1428571428571</v>
       </c>
       <c r="AQ7" t="n">
         <v>1</v>
       </c>
       <c r="AR7" t="n">
-        <v>68.75</v>
+        <v>65.57142857142857</v>
       </c>
       <c r="AS7" t="n">
-        <v>1679687.5</v>
+        <v>853571.4285714285</v>
       </c>
       <c r="AT7" t="n">
-        <v>73.1875</v>
+        <v>67.28571428571429</v>
       </c>
       <c r="AU7" t="n">
-        <v>21.95454545454545</v>
+        <v>21.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>186.4545454545455</v>
+        <v>186.95</v>
       </c>
       <c r="AW7" t="n">
         <v>1</v>
       </c>
       <c r="AX7" t="n">
-        <v>64.04545454545455</v>
+        <v>64.8</v>
       </c>
       <c r="AY7" t="n">
-        <v>1346590.909090909</v>
+        <v>1241250</v>
       </c>
       <c r="AZ7" t="n">
-        <v>72.95454545454545</v>
+        <v>75.45</v>
       </c>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
@@ -1850,163 +1738,147 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2Hl43AnC</t>
+          <t>dCPKovw8</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45508.35416666666</v>
+        <v>45522.54166666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">hempel r 
+          <t xml:space="preserve">zwayer f 
   ger </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">sportpark ronhof thomas sommer
-  furth </t>
+          <t xml:space="preserve">hansch arena
+  meppen </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>16626</v>
+        <v>13696</v>
       </c>
       <c r="F8" t="n">
-        <v>12664</v>
+        <v>12959</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CCQGbik8</t>
+          <t>rXqBh2xP</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>zedZaSL7</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3.65</v>
-      </c>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="N8" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="O8" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="P8" t="n">
         <v>15</v>
       </c>
       <c r="Q8" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>8E86CPuD</t>
+          <t>UqphGQrg</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>pdPRS0me</t>
+          <t>EDRZkDzS</t>
         </is>
       </c>
       <c r="W8" t="n">
         <v>59</v>
       </c>
       <c r="X8" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>6FDqshzF</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>183.1</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>67</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1480000</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="n">
-        <v>22.72727272727273</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>182.5454545454545</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>64.59090909090909</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1273863.636363636</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>72.86363636363636</v>
-      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>71.625</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>2912500</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
       <c r="AU8" t="n">
-        <v>25.57142857142857</v>
+        <v>26.68421052631579</v>
       </c>
       <c r="AV8" t="n">
-        <v>181.8571428571429</v>
+        <v>186.6315789473684</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
       </c>
       <c r="AX8" t="n">
-        <v>66.71428571428571</v>
+        <v>70.57894736842105</v>
       </c>
       <c r="AY8" t="n">
-        <v>1175000</v>
+        <v>2598947.368421053</v>
       </c>
       <c r="AZ8" t="n">
-        <v>68.42857142857143</v>
+        <v>72.63157894736842</v>
       </c>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
@@ -2026,124 +1898,112 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SIOxI915</t>
+          <t>KSwfVwAO</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45508.35416666666</v>
+        <v>45522.4375</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">schroder r 
+          <t xml:space="preserve">lechner f 
   ger </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">donaustadion
-  ulm </t>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>19500</v>
+        <v>29546</v>
       </c>
       <c r="F9" t="n">
-        <v>17400</v>
+        <v>6487</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>tbC3EcQn</t>
+          <t>WrbkcjCd</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>naWckLmC</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="L9" t="n">
+          <t>S0hPB9rA</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>31</v>
+      </c>
+      <c r="N9" t="n">
+        <v>69</v>
+      </c>
+      <c r="O9" t="n">
+        <v>10</v>
+      </c>
+      <c r="P9" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R9" t="n">
         <v>3</v>
-      </c>
-      <c r="M9" t="n">
-        <v>54</v>
-      </c>
-      <c r="N9" t="n">
-        <v>46</v>
-      </c>
-      <c r="O9" t="n">
-        <v>12</v>
-      </c>
-      <c r="P9" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>4</v>
       </c>
       <c r="S9" t="n">
         <v>12</v>
       </c>
       <c r="T9" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>QevvB2nf</t>
+          <t>lC9J1RTa</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>4bJLk19p</t>
+          <t>MDhPV0RQ</t>
         </is>
       </c>
       <c r="W9" t="n">
         <v>59</v>
       </c>
       <c r="X9" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="n">
         <v>20242025</v>
       </c>
       <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>184.6363636363636</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>67.63636363636364</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1484090.909090909</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>70.63636363636364</v>
-      </c>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr"/>
@@ -2151,22 +2011,22 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
       <c r="AU9" t="n">
-        <v>25.22222222222222</v>
+        <v>27.14285714285714</v>
       </c>
       <c r="AV9" t="n">
-        <v>180.9444444444445</v>
+        <v>189</v>
       </c>
       <c r="AW9" t="n">
         <v>1</v>
       </c>
       <c r="AX9" t="n">
-        <v>67.5</v>
+        <v>70.35714285714286</v>
       </c>
       <c r="AY9" t="n">
-        <v>1468055.555555556</v>
+        <v>1908928.571428571</v>
       </c>
       <c r="AZ9" t="n">
-        <v>71.11111111111111</v>
+        <v>73.71428571428571</v>
       </c>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
@@ -2186,179 +2046,147 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>EeIMLi2t</t>
+          <t>tvOIPExA</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45507.64583333334</v>
+        <v>45522.4375</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">brand b 
   ger </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">veltins arena
-  gelsenkirchen </t>
+          <t xml:space="preserve">hardtwaldstadion
+  sandhausen </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>62271</v>
+        <v>15414</v>
       </c>
       <c r="F10" t="n">
-        <v>61000</v>
+        <v>9705</v>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
+          <t>UZxEj1R4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>QqLCC3il</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.21</v>
-      </c>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="O10" t="n">
+        <v>16</v>
+      </c>
+      <c r="P10" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>7</v>
+      </c>
+      <c r="R10" t="n">
         <v>14</v>
       </c>
-      <c r="P10" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>8</v>
-      </c>
-      <c r="R10" t="n">
-        <v>5</v>
-      </c>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="T10" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>txZLBQVC</t>
+          <t>rZtwKVAL</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>SQrxFAMl</t>
+          <t>4fX0k7gg</t>
         </is>
       </c>
       <c r="W10" t="n">
         <v>59</v>
       </c>
       <c r="X10" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
+      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>dfNCCCzS</t>
-        </is>
-      </c>
-      <c r="AC10" t="n">
-        <v>26.25</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>187.125</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>69</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1740625</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>71.5</v>
-      </c>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="n">
-        <v>25.375</v>
+        <v>22.7</v>
       </c>
       <c r="AJ10" t="n">
-        <v>183.25</v>
+        <v>184.6</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.125</v>
+        <v>1.2</v>
       </c>
       <c r="AL10" t="n">
-        <v>66.875</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AM10" t="n">
-        <v>1287500</v>
+        <v>3820000</v>
       </c>
       <c r="AN10" t="n">
-        <v>71.875</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>27.22222222222222</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>190.2222222222222</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>67.94444444444444</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>1294444.444444444</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>70.88888888888889</v>
-      </c>
+        <v>78.3</v>
+      </c>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
       <c r="AU10" t="n">
-        <v>24.57142857142857</v>
+        <v>26.04761904761905</v>
       </c>
       <c r="AV10" t="n">
-        <v>184.9285714285714</v>
+        <v>187.5714285714286</v>
       </c>
       <c r="AW10" t="n">
-        <v>1</v>
+        <v>1.238095238095238</v>
       </c>
       <c r="AX10" t="n">
-        <v>66.07142857142857</v>
+        <v>68.42857142857143</v>
       </c>
       <c r="AY10" t="n">
-        <v>1302142.857142857</v>
+        <v>2287619.047619048</v>
       </c>
       <c r="AZ10" t="n">
-        <v>71.14285714285714</v>
+        <v>72.23809523809524</v>
       </c>
       <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="inlineStr"/>
@@ -2378,152 +2206,144 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>fiod5WHa</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45507.33333333334</v>
+        <v>45522.4375</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">bacher m 
+          <t xml:space="preserve">nouhoum a 
   ger </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">heinz von heiden arena
-  hannover </t>
+          <t xml:space="preserve">friedrich ebert stadium
+  hildesheim </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>49200</v>
+        <v>10000</v>
       </c>
       <c r="F11" t="n">
-        <v>31800</v>
+        <v>5186</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>dfNCCCzS</t>
+          <t>E3xs5mIe</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>UiCmEP56</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.51</v>
-      </c>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="N11" t="n">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="O11" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="P11" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T11" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>t0ZPdkUl</t>
+          <t>bJ0lIKrp</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>zyLSrbZQ</t>
+          <t>8E8qmw3d</t>
         </is>
       </c>
       <c r="W11" t="n">
         <v>59</v>
       </c>
       <c r="X11" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>QqLCC3il</t>
-        </is>
-      </c>
+      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>184.3</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2082500</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="n">
-        <v>24.40909090909091</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>183.4545454545455</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>68</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>1812500</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>72.81818181818181</v>
-      </c>
-      <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="inlineStr"/>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>184</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1177500</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="n">
+        <v>26.26315789473684</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>181</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>65.78947368421052</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>959210.5263157894</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>67.52631578947368</v>
+      </c>
       <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr"/>
@@ -2542,171 +2362,171 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>OWxD1lHO</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45507.33333333334</v>
+        <v>45522.4375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">haslberger w 
+          <t xml:space="preserve">schroder r 
   ger </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">olympiastadion
-  berlin </t>
+          <t xml:space="preserve">ostseestadion
+  rostock </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>74667</v>
+        <v>29000</v>
       </c>
       <c r="F12" t="n">
-        <v>48591</v>
+        <v>25600</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>KIHmtCkL</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>2y0u8Wrq</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>G2Op923t</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="L12" t="n">
-        <v>2.1</v>
-      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="N12" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="O12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q12" t="n">
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
+          <t>G8THUSaE</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
           <t>YmfcAeCo</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0AI1QUJH</t>
         </is>
       </c>
       <c r="W12" t="n">
         <v>59</v>
       </c>
       <c r="X12" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
-        <v>23.22222222222222</v>
+        <v>25.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>183.7777777777778</v>
+        <v>183.875</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.111111111111111</v>
+        <v>1</v>
       </c>
       <c r="AF12" t="n">
-        <v>69.44444444444444</v>
+        <v>65.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>2422222.222222222</v>
+        <v>1040625</v>
       </c>
       <c r="AH12" t="n">
-        <v>76.11111111111111</v>
+        <v>69.125</v>
       </c>
       <c r="AI12" t="n">
-        <v>25.125</v>
+        <v>23.4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>183.625</v>
+        <v>182.8</v>
       </c>
       <c r="AK12" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AL12" t="n">
-        <v>67</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AM12" t="n">
-        <v>1356250</v>
+        <v>2340000</v>
       </c>
       <c r="AN12" t="n">
-        <v>72</v>
+        <v>75.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>23.55</v>
+        <v>23.7</v>
       </c>
       <c r="AP12" t="n">
-        <v>184.2</v>
+        <v>181.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR12" t="n">
-        <v>69.25</v>
+        <v>64</v>
       </c>
       <c r="AS12" t="n">
-        <v>2360000</v>
+        <v>997500</v>
       </c>
       <c r="AT12" t="n">
-        <v>74.75</v>
+        <v>70.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>24.9375</v>
+        <v>23.47368421052632</v>
       </c>
       <c r="AV12" t="n">
-        <v>186.1875</v>
+        <v>186.3684210526316</v>
       </c>
       <c r="AW12" t="n">
-        <v>1</v>
+        <v>1.157894736842105</v>
       </c>
       <c r="AX12" t="n">
-        <v>66.9375</v>
+        <v>68.47368421052632</v>
       </c>
       <c r="AY12" t="n">
-        <v>1417187.5</v>
+        <v>1956578.947368421</v>
       </c>
       <c r="AZ12" t="n">
-        <v>72.125</v>
+        <v>75</v>
       </c>
       <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="inlineStr"/>
@@ -2726,179 +2546,131 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>zkVf7hmm</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45507.33333333334</v>
+        <v>45522.4375</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">braun r 
+          <t xml:space="preserve">speckner m 
   ger </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">bbbank wildpark
-  karlsruhe </t>
+          <t xml:space="preserve">stadion am panzenberg
+  bremen </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>34302</v>
+        <v>5000</v>
       </c>
       <c r="F13" t="n">
-        <v>25000</v>
+        <v>3500</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>tW75B1ei</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>G2Op923t</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>37</v>
+      </c>
+      <c r="N13" t="n">
+        <v>63</v>
+      </c>
+      <c r="O13" t="n">
+        <v>7</v>
+      </c>
+      <c r="P13" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q13" t="n">
         <v>2</v>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>EB3q7jbk</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>6FDqshzF</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="M13" t="n">
-        <v>51</v>
-      </c>
-      <c r="N13" t="n">
-        <v>49</v>
-      </c>
-      <c r="O13" t="n">
-        <v>15</v>
-      </c>
-      <c r="P13" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>5</v>
-      </c>
       <c r="R13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>OzPMRhK3</t>
+          <t>4tvZg2Br</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>tO31cZrF</t>
+          <t>0AI1QUJH</t>
         </is>
       </c>
       <c r="W13" t="n">
         <v>59</v>
       </c>
       <c r="X13" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>naWckLmC</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>CCQGbik8</t>
-        </is>
-      </c>
-      <c r="AC13" t="n">
-        <v>26.27272727272727</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>184.3636363636364</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>67.81818181818181</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1395454.545454545</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>71.90909090909091</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>22.77777777777778</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>182</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.111111111111111</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>66</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1697222.222222222</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>72.55555555555556</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>22.78947368421053</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>181.1052631578947</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>64.84210526315789</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>1087894.736842105</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>72.84210526315789</v>
-      </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
       <c r="AU13" t="n">
-        <v>27.77777777777778</v>
+        <v>24.15789473684211</v>
       </c>
       <c r="AV13" t="n">
-        <v>181.2222222222222</v>
+        <v>186.3684210526316</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.111111111111111</v>
+        <v>1</v>
       </c>
       <c r="AX13" t="n">
-        <v>67.44444444444444</v>
+        <v>66.89473684210526</v>
       </c>
       <c r="AY13" t="n">
-        <v>1377777.777777778</v>
+        <v>1414473.684210526</v>
       </c>
       <c r="AZ13" t="n">
-        <v>70.22222222222223</v>
+        <v>72.31578947368421</v>
       </c>
       <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="inlineStr"/>
@@ -2918,11 +2690,11 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>f5QUJVWh</t>
+          <t>jFMCm08e</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45507.33333333334</v>
+        <v>45522.4375</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2932,86 +2704,86 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">mdcc arena
-  magdeburg </t>
+          <t xml:space="preserve">jahnstadion regensburg
+  regensburg </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>30098</v>
+        <v>15210</v>
       </c>
       <c r="F14" t="n">
-        <v>21469</v>
+        <v>12581</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>YFuz2RLm</t>
+          <t>UiCmEP56</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>6in2Eknb</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.72</v>
-      </c>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="N14" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="O14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P14" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="Q14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S14" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T14" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>IgZoGKFn</t>
+          <t>zyLSrbZQ</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>8E8qmw3d</t>
+          <t>8f6APkLc</t>
         </is>
       </c>
       <c r="W14" t="n">
         <v>59</v>
       </c>
       <c r="X14" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="n">
         <v>20242025</v>
       </c>
       <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
@@ -3019,58 +2791,46 @@
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="n">
-        <v>24.9</v>
+        <v>26.88888888888889</v>
       </c>
       <c r="AJ14" t="n">
-        <v>182.3</v>
+        <v>183.4444444444445</v>
       </c>
       <c r="AK14" t="n">
         <v>1</v>
       </c>
       <c r="AL14" t="n">
-        <v>66.90000000000001</v>
+        <v>70.88888888888889</v>
       </c>
       <c r="AM14" t="n">
-        <v>1200000</v>
+        <v>2213888.888888889</v>
       </c>
       <c r="AN14" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>24.93333333333333</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>176.3333333333333</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1375000</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>69.59999999999999</v>
-      </c>
+        <v>73.44444444444444</v>
+      </c>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
       <c r="AU14" t="n">
-        <v>25.8</v>
+        <v>22.875</v>
       </c>
       <c r="AV14" t="n">
-        <v>181.4666666666667</v>
+        <v>183.875</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
       </c>
       <c r="AX14" t="n">
-        <v>64.93333333333334</v>
+        <v>67.25</v>
       </c>
       <c r="AY14" t="n">
-        <v>908333.3333333334</v>
+        <v>1814062.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>68.26666666666667</v>
+        <v>75.8125</v>
       </c>
       <c r="BA14" t="inlineStr"/>
       <c r="BB14" t="inlineStr"/>
@@ -3090,29 +2850,29 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>OA1xkBXI</t>
+          <t>6q2yrHgU</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45506.64583333334</v>
+        <v>45522.33333333334</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">burda m 
+          <t xml:space="preserve">dankert b 
   ger </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">rheinenergiestadion
-  cologne </t>
+          <t xml:space="preserve">ludwigspark stadion
+  saarbrucken </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>50000</v>
+        <v>16003</v>
       </c>
       <c r="F15" t="n">
-        <v>50000</v>
+        <v>14868</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -3122,147 +2882,115 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
+          <t>fLbhmJ5l</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.95</v>
-      </c>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="N15" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="O15" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="P15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q15" t="n">
         <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T15" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>4fX0k7gg</t>
+          <t>trS1MB7T</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>EDRZkDzS</t>
+          <t>tO31cZrF</t>
         </is>
       </c>
       <c r="W15" t="n">
         <v>59</v>
       </c>
       <c r="X15" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>88HSzjDr</t>
-        </is>
-      </c>
+      <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="AC15" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>186</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>4680000</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>79</v>
-      </c>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="n">
-        <v>25.7</v>
+        <v>26</v>
       </c>
       <c r="AJ15" t="n">
-        <v>183.4</v>
+        <v>182.875</v>
       </c>
       <c r="AK15" t="n">
-        <v>1</v>
+        <v>1.125</v>
       </c>
       <c r="AL15" t="n">
-        <v>71.2</v>
+        <v>68</v>
       </c>
       <c r="AM15" t="n">
-        <v>2470000</v>
+        <v>1521875</v>
       </c>
       <c r="AN15" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>25.78947368421053</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>184.7894736842105</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.210526315789474</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>68.63157894736842</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2486315.789473684</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>73.05263157894737</v>
-      </c>
+        <v>72.25</v>
+      </c>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
       <c r="AU15" t="n">
-        <v>25.25</v>
+        <v>26</v>
       </c>
       <c r="AV15" t="n">
-        <v>183.25</v>
+        <v>178</v>
       </c>
       <c r="AW15" t="n">
-        <v>1</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AX15" t="n">
-        <v>69.05</v>
+        <v>69.16666666666667</v>
       </c>
       <c r="AY15" t="n">
-        <v>2124000</v>
+        <v>1866666.666666667</v>
       </c>
       <c r="AZ15" t="n">
-        <v>72.75</v>
+        <v>70.66666666666667</v>
       </c>
       <c r="BA15" t="inlineStr"/>
       <c r="BB15" t="inlineStr"/>
@@ -3279,6 +3007,6016 @@
       <c r="BM15" t="inlineStr"/>
       <c r="BN15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AiJ3kset</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45522.33333333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weisbach e 
+  ger </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">friedrich ludwig jahn sportpark
+  berlin </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>19708</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5504</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>UNr2EUfd</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>24</v>
+      </c>
+      <c r="N16" t="n">
+        <v>76</v>
+      </c>
+      <c r="O16" t="n">
+        <v>5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="n">
+        <v>6</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>CCww5Qfo</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="W16" t="n">
+        <v>59</v>
+      </c>
+      <c r="X16" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="n">
+        <v>24.625</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>185.125</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>4975000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>182.1904761904762</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.476190476190476</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>72.19047619047619</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>4629761.904761905</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>76.95238095238095</v>
+      </c>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="inlineStr"/>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="inlineStr"/>
+      <c r="BM16" t="inlineStr"/>
+      <c r="BN16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>fcxqFy2l</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stieler t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>30210</v>
+      </c>
+      <c r="F17" t="n">
+        <v>30210</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M17" t="n">
+        <v>38</v>
+      </c>
+      <c r="N17" t="n">
+        <v>62</v>
+      </c>
+      <c r="O17" t="n">
+        <v>12</v>
+      </c>
+      <c r="P17" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="n">
+        <v>20</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="W17" t="n">
+        <v>59</v>
+      </c>
+      <c r="X17" t="n">
+        <v>594</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>184.625</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>80</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>25375000</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>83.75</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>9810000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>181.8571428571429</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>2.190476190476191</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>82.0952380952381</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>50242857.14285714</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>85.0952380952381</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>23.27777777777778</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.055555555555556</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>72.16666666666667</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>6294444.444444444</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>78.05555555555556</v>
+      </c>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>191.75</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>289</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>23600000</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>8CpxDyg4</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45521.54166666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burda m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volksparkstadion
+  hamburg </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>57274</v>
+      </c>
+      <c r="F18" t="n">
+        <v>50971</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>I1Vk6k3R</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>20</v>
+      </c>
+      <c r="N18" t="n">
+        <v>80</v>
+      </c>
+      <c r="O18" t="n">
+        <v>7</v>
+      </c>
+      <c r="P18" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>9</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="n">
+        <v>5</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>AgnJojCs</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="W18" t="n">
+        <v>59</v>
+      </c>
+      <c r="X18" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>186.1</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>81</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>34700000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>84</v>
+      </c>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="n">
+        <v>23.61904761904762</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>183.7142857142857</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.619047619047619</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>76.80952380952381</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>21880952.38095238</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>83.0952380952381</v>
+      </c>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr"/>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="inlineStr"/>
+      <c r="BM18" t="inlineStr"/>
+      <c r="BN18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>CpiTEcOi</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45521.54166666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schuco arena
+  bielefeld </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>27332</v>
+      </c>
+      <c r="F19" t="n">
+        <v>26044</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>pp38UXK8</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>44</v>
+      </c>
+      <c r="N19" t="n">
+        <v>56</v>
+      </c>
+      <c r="O19" t="n">
+        <v>12</v>
+      </c>
+      <c r="P19" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>6</v>
+      </c>
+      <c r="R19" t="n">
+        <v>5</v>
+      </c>
+      <c r="S19" t="n">
+        <v>21</v>
+      </c>
+      <c r="T19" t="n">
+        <v>24</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>KrFXELrR</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>t0ZPdkUl</t>
+        </is>
+      </c>
+      <c r="W19" t="n">
+        <v>59</v>
+      </c>
+      <c r="X19" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>184</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1932500</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>186.1428571428571</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>65.28571428571429</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1321428.571428571</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>72.28571428571429</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>25.09523809523809</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>184.3333333333333</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>69.04761904761905</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1947619.047619048</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>72.95238095238095</v>
+      </c>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="inlineStr"/>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="inlineStr"/>
+      <c r="BM19" t="inlineStr"/>
+      <c r="BN19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>hzyf0b9b</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45521.54166666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bacher m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">new tivoli
+  aachen </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>31026</v>
+      </c>
+      <c r="F20" t="n">
+        <v>29555</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>j3PKcB4E</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>39</v>
+      </c>
+      <c r="N20" t="n">
+        <v>61</v>
+      </c>
+      <c r="O20" t="n">
+        <v>9</v>
+      </c>
+      <c r="P20" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>6</v>
+      </c>
+      <c r="R20" t="n">
+        <v>5</v>
+      </c>
+      <c r="S20" t="n">
+        <v>11</v>
+      </c>
+      <c r="T20" t="n">
+        <v>13</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SfKt2E6n</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="W20" t="n">
+        <v>59</v>
+      </c>
+      <c r="X20" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1760000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="n">
+        <v>24.4375</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>186.3125</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>66.625</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1476562.5</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>71.375</v>
+      </c>
+      <c r="BA20" t="inlineStr"/>
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="inlineStr"/>
+      <c r="BG20" t="inlineStr"/>
+      <c r="BH20" t="inlineStr"/>
+      <c r="BI20" t="inlineStr"/>
+      <c r="BJ20" t="inlineStr"/>
+      <c r="BK20" t="inlineStr"/>
+      <c r="BL20" t="inlineStr"/>
+      <c r="BM20" t="inlineStr"/>
+      <c r="BN20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>f1nnRRDE</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45521.4375</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reichel t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion an der bremer bruck
+  osnabruck </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>16667</v>
+      </c>
+      <c r="F21" t="n">
+        <v>15500</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>88Xgj1Y5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>49</v>
+      </c>
+      <c r="N21" t="n">
+        <v>51</v>
+      </c>
+      <c r="O21" t="n">
+        <v>8</v>
+      </c>
+      <c r="P21" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6</v>
+      </c>
+      <c r="S21" t="n">
+        <v>6</v>
+      </c>
+      <c r="T21" t="n">
+        <v>8</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>lxrr7DgN</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="W21" t="n">
+        <v>59</v>
+      </c>
+      <c r="X21" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="n">
+        <v>25.88888888888889</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>183.3333333333333</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>75.11111111111111</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>10033333.33333333</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>77.44444444444444</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>22.27272727272727</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>186.4545454545455</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>62.90909090909091</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>863636.3636363636</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>72</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>26.95652173913043</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>182.1304347826087</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.608695652173913</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>74.08695652173913</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>6278260.869565218</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>76.04347826086956</v>
+      </c>
+      <c r="BA21" t="inlineStr"/>
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="inlineStr"/>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="inlineStr"/>
+      <c r="BJ21" t="inlineStr"/>
+      <c r="BK21" t="inlineStr"/>
+      <c r="BL21" t="inlineStr"/>
+      <c r="BM21" t="inlineStr"/>
+      <c r="BN21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>MZjh9ghT</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45521.4375</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion an der hafenstrasse
+  essen </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>20352</v>
+      </c>
+      <c r="F22" t="n">
+        <v>17000</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>EB0xsr77</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>41</v>
+      </c>
+      <c r="N22" t="n">
+        <v>59</v>
+      </c>
+      <c r="O22" t="n">
+        <v>7</v>
+      </c>
+      <c r="P22" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>9</v>
+      </c>
+      <c r="S22" t="n">
+        <v>9</v>
+      </c>
+      <c r="T22" t="n">
+        <v>9</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>0KMe4S4D</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="W22" t="n">
+        <v>59</v>
+      </c>
+      <c r="X22" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="n">
+        <v>25.45454545454545</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>183.2727272727273</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>2.090909090909091</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>79.81818181818181</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>26636363.63636364</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>83.36363636363636</v>
+      </c>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="n">
+        <v>23.15384615384615</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>184.2307692307692</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.769230769230769</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>76.92307692307692</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>22559615.38461538</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>81.84615384615384</v>
+      </c>
+      <c r="BA22" t="inlineStr"/>
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="inlineStr"/>
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="inlineStr"/>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr"/>
+      <c r="BI22" t="inlineStr"/>
+      <c r="BJ22" t="inlineStr"/>
+      <c r="BK22" t="inlineStr"/>
+      <c r="BL22" t="inlineStr"/>
+      <c r="BM22" t="inlineStr"/>
+      <c r="BN22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>tbKZHNz1</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45521.4375</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">braun r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audi sportpark
+  ingolstadt </t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>15800</v>
+      </c>
+      <c r="F23" t="n">
+        <v>11655</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ne5QkLtB</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>45</v>
+      </c>
+      <c r="N23" t="n">
+        <v>55</v>
+      </c>
+      <c r="O23" t="n">
+        <v>13</v>
+      </c>
+      <c r="P23" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>10</v>
+      </c>
+      <c r="R23" t="n">
+        <v>4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>19</v>
+      </c>
+      <c r="T23" t="n">
+        <v>14</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>CWcD8UM8</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>4bJLk19p</t>
+        </is>
+      </c>
+      <c r="W23" t="n">
+        <v>59</v>
+      </c>
+      <c r="X23" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>182.95</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1510000</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>70.34999999999999</v>
+      </c>
+      <c r="BA23" t="inlineStr"/>
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="inlineStr"/>
+      <c r="BG23" t="inlineStr"/>
+      <c r="BH23" t="inlineStr"/>
+      <c r="BI23" t="inlineStr"/>
+      <c r="BJ23" t="inlineStr"/>
+      <c r="BK23" t="inlineStr"/>
+      <c r="BL23" t="inlineStr"/>
+      <c r="BM23" t="inlineStr"/>
+      <c r="BN23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>vyk5gjdE</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45521.4375</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">benen l 
+  ger </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volksstadion greifswald
+  greifswald </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4990</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4990</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Q1yNyI5t</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>39</v>
+      </c>
+      <c r="N24" t="n">
+        <v>61</v>
+      </c>
+      <c r="O24" t="n">
+        <v>6</v>
+      </c>
+      <c r="P24" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>5</v>
+      </c>
+      <c r="S24" t="n">
+        <v>6</v>
+      </c>
+      <c r="T24" t="n">
+        <v>12</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Wbz1kusU</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="W24" t="n">
+        <v>59</v>
+      </c>
+      <c r="X24" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>185.5555555555555</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>75.44444444444444</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>7833333.333333333</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>77.22222222222223</v>
+      </c>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="n">
+        <v>25.69565217391304</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>184.304347826087</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.391304347826087</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>71.65217391304348</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>4054347.826086957</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>76.30434782608695</v>
+      </c>
+      <c r="BA24" t="inlineStr"/>
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="inlineStr"/>
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="inlineStr"/>
+      <c r="BG24" t="inlineStr"/>
+      <c r="BH24" t="inlineStr"/>
+      <c r="BI24" t="inlineStr"/>
+      <c r="BJ24" t="inlineStr"/>
+      <c r="BK24" t="inlineStr"/>
+      <c r="BL24" t="inlineStr"/>
+      <c r="BM24" t="inlineStr"/>
+      <c r="BN24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>bF2q76Mr</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45521.4375</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brych f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ostalb arena
+  aalen </t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>14500</v>
+      </c>
+      <c r="F25" t="n">
+        <v>10850</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Oh2C15j0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>32</v>
+      </c>
+      <c r="N25" t="n">
+        <v>68</v>
+      </c>
+      <c r="O25" t="n">
+        <v>4</v>
+      </c>
+      <c r="P25" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>8</v>
+      </c>
+      <c r="S25" t="n">
+        <v>17</v>
+      </c>
+      <c r="T25" t="n">
+        <v>16</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>8bJFOfzK</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>txZLBQVC</t>
+        </is>
+      </c>
+      <c r="W25" t="n">
+        <v>59</v>
+      </c>
+      <c r="X25" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="n">
+        <v>25.28571428571428</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>188.5714285714286</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>66.14285714285714</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1089285.714285714</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>70.28571428571429</v>
+      </c>
+      <c r="BA25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="inlineStr"/>
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="inlineStr"/>
+      <c r="BG25" t="inlineStr"/>
+      <c r="BH25" t="inlineStr"/>
+      <c r="BI25" t="inlineStr"/>
+      <c r="BJ25" t="inlineStr"/>
+      <c r="BK25" t="inlineStr"/>
+      <c r="BL25" t="inlineStr"/>
+      <c r="BM25" t="inlineStr"/>
+      <c r="BN25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>8QPARz8c</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45521.4375</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">michel f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ms technologie arena
+  villingen schwenningen </t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F26" t="n">
+        <v>6800</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>lKLJUxeT</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>33</v>
+      </c>
+      <c r="N26" t="n">
+        <v>67</v>
+      </c>
+      <c r="O26" t="n">
+        <v>6</v>
+      </c>
+      <c r="P26" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>9</v>
+      </c>
+      <c r="S26" t="n">
+        <v>7</v>
+      </c>
+      <c r="T26" t="n">
+        <v>9</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>lli2SfLl</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="W26" t="n">
+        <v>59</v>
+      </c>
+      <c r="X26" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>188.25</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>72.125</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>2837500</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>74.125</v>
+      </c>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>187.1111111111111</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>69.77777777777777</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>2063888.888888889</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>72.61111111111111</v>
+      </c>
+      <c r="BA26" t="inlineStr"/>
+      <c r="BB26" t="inlineStr"/>
+      <c r="BC26" t="inlineStr"/>
+      <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="inlineStr"/>
+      <c r="BF26" t="inlineStr"/>
+      <c r="BG26" t="inlineStr"/>
+      <c r="BH26" t="inlineStr"/>
+      <c r="BI26" t="inlineStr"/>
+      <c r="BJ26" t="inlineStr"/>
+      <c r="BK26" t="inlineStr"/>
+      <c r="BL26" t="inlineStr"/>
+      <c r="BM26" t="inlineStr"/>
+      <c r="BN26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>0K2qBFNG</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45521.33333333334</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badstubner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">erzgebirgsstadion
+  aue </t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>16485</v>
+      </c>
+      <c r="F27" t="n">
+        <v>14811</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>vsXIDreP</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>53</v>
+      </c>
+      <c r="N27" t="n">
+        <v>47</v>
+      </c>
+      <c r="O27" t="n">
+        <v>8</v>
+      </c>
+      <c r="P27" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>11</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3</v>
+      </c>
+      <c r="T27" t="n">
+        <v>9</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>rPfNaCdg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="W27" t="n">
+        <v>59</v>
+      </c>
+      <c r="X27" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="n">
+        <v>24.81818181818182</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>184</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.545454545454545</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>75.27272727272727</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>9627272.727272727</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>79</v>
+      </c>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="n">
+        <v>24.43478260869565</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>185.4347826086957</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.347826086956522</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>73.47826086956522</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>7100000</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>77.95652173913044</v>
+      </c>
+      <c r="BA27" t="inlineStr"/>
+      <c r="BB27" t="inlineStr"/>
+      <c r="BC27" t="inlineStr"/>
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr"/>
+      <c r="BF27" t="inlineStr"/>
+      <c r="BG27" t="inlineStr"/>
+      <c r="BH27" t="inlineStr"/>
+      <c r="BI27" t="inlineStr"/>
+      <c r="BJ27" t="inlineStr"/>
+      <c r="BK27" t="inlineStr"/>
+      <c r="BL27" t="inlineStr"/>
+      <c r="BM27" t="inlineStr"/>
+      <c r="BN27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Kj4sifWp</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45521.33333333334</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prigan f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bruchwegstadion
+  mainz </t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>7134</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4235</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>WzEYqEyg</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>35</v>
+      </c>
+      <c r="N28" t="n">
+        <v>65</v>
+      </c>
+      <c r="O28" t="n">
+        <v>4</v>
+      </c>
+      <c r="P28" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>pvucOaW7</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>8E86CPuD</t>
+        </is>
+      </c>
+      <c r="W28" t="n">
+        <v>59</v>
+      </c>
+      <c r="X28" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>183.3</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1605000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="n">
+        <v>22.60869565217391</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>183.2173913043478</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>64.08695652173913</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1201086.956521739</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>72.73913043478261</v>
+      </c>
+      <c r="BA28" t="inlineStr"/>
+      <c r="BB28" t="inlineStr"/>
+      <c r="BC28" t="inlineStr"/>
+      <c r="BD28" t="inlineStr"/>
+      <c r="BE28" t="inlineStr"/>
+      <c r="BF28" t="inlineStr"/>
+      <c r="BG28" t="inlineStr"/>
+      <c r="BH28" t="inlineStr"/>
+      <c r="BI28" t="inlineStr"/>
+      <c r="BJ28" t="inlineStr"/>
+      <c r="BK28" t="inlineStr"/>
+      <c r="BL28" t="inlineStr"/>
+      <c r="BM28" t="inlineStr"/>
+      <c r="BN28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>lONsG15D</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45520.65625</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jablonski s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">donaustadion
+  ulm </t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>19500</v>
+      </c>
+      <c r="F29" t="n">
+        <v>17400</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>tbC3EcQn</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>27</v>
+      </c>
+      <c r="N29" t="n">
+        <v>73</v>
+      </c>
+      <c r="O29" t="n">
+        <v>5</v>
+      </c>
+      <c r="P29" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>5</v>
+      </c>
+      <c r="S29" t="n">
+        <v>11</v>
+      </c>
+      <c r="T29" t="n">
+        <v>11</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>QevvB2nf</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="W29" t="n">
+        <v>59</v>
+      </c>
+      <c r="X29" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="n">
+        <v>25.81818181818182</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>183.5454545454545</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>2.727272727272727</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>81.18181818181819</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>37700000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>85.18181818181819</v>
+      </c>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="n">
+        <v>25.35294117647059</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>184.6470588235294</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>3.176470588235294</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>82.41176470588235</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>55613235.29411764</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>85.52941176470588</v>
+      </c>
+      <c r="BA29" t="inlineStr"/>
+      <c r="BB29" t="inlineStr"/>
+      <c r="BC29" t="inlineStr"/>
+      <c r="BD29" t="inlineStr"/>
+      <c r="BE29" t="inlineStr"/>
+      <c r="BF29" t="inlineStr"/>
+      <c r="BG29" t="inlineStr"/>
+      <c r="BH29" t="inlineStr"/>
+      <c r="BI29" t="inlineStr"/>
+      <c r="BJ29" t="inlineStr"/>
+      <c r="BK29" t="inlineStr"/>
+      <c r="BL29" t="inlineStr"/>
+      <c r="BM29" t="inlineStr"/>
+      <c r="BN29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>pWQQJq6l</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45520.54166666666</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">siebert d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leuna chemie stadion
+  halle </t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>15057</v>
+      </c>
+      <c r="F30" t="n">
+        <v>14000</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>boX3cIQa</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>34</v>
+      </c>
+      <c r="N30" t="n">
+        <v>66</v>
+      </c>
+      <c r="O30" t="n">
+        <v>9</v>
+      </c>
+      <c r="P30" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3</v>
+      </c>
+      <c r="R30" t="n">
+        <v>8</v>
+      </c>
+      <c r="S30" t="n">
+        <v>14</v>
+      </c>
+      <c r="T30" t="n">
+        <v>12</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>02hM7hzd</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="W30" t="n">
+        <v>59</v>
+      </c>
+      <c r="X30" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>185.8888888888889</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>70.22222222222223</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>2277777.777777778</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>73.77777777777777</v>
+      </c>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AU30" t="n">
+        <v>23.94444444444444</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>183.9444444444445</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>68.38888888888889</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1944444.444444444</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="BA30" t="inlineStr"/>
+      <c r="BB30" t="inlineStr"/>
+      <c r="BC30" t="inlineStr"/>
+      <c r="BD30" t="inlineStr"/>
+      <c r="BE30" t="inlineStr"/>
+      <c r="BF30" t="inlineStr"/>
+      <c r="BG30" t="inlineStr"/>
+      <c r="BH30" t="inlineStr"/>
+      <c r="BI30" t="inlineStr"/>
+      <c r="BJ30" t="inlineStr"/>
+      <c r="BK30" t="inlineStr"/>
+      <c r="BL30" t="inlineStr"/>
+      <c r="BM30" t="inlineStr"/>
+      <c r="BN30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>hIsO3XFj</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45520.54166666666</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hempel r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brita arena
+  wiesbaden </t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>12566</v>
+      </c>
+      <c r="F31" t="n">
+        <v>12500</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ObxFt3lm</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>35</v>
+      </c>
+      <c r="N31" t="n">
+        <v>65</v>
+      </c>
+      <c r="O31" t="n">
+        <v>8</v>
+      </c>
+      <c r="P31" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6</v>
+      </c>
+      <c r="S31" t="n">
+        <v>19</v>
+      </c>
+      <c r="T31" t="n">
+        <v>18</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>QTAUlvUP</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="W31" t="n">
+        <v>59</v>
+      </c>
+      <c r="X31" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>6100000</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>24.53846153846154</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>183.3846153846154</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>63.76923076923077</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>769230.7692307692</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>67.23076923076923</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>71</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>3146250</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="BA31" t="inlineStr"/>
+      <c r="BB31" t="inlineStr"/>
+      <c r="BC31" t="inlineStr"/>
+      <c r="BD31" t="inlineStr"/>
+      <c r="BE31" t="inlineStr"/>
+      <c r="BF31" t="inlineStr"/>
+      <c r="BG31" t="inlineStr"/>
+      <c r="BH31" t="inlineStr"/>
+      <c r="BI31" t="inlineStr"/>
+      <c r="BJ31" t="inlineStr"/>
+      <c r="BK31" t="inlineStr"/>
+      <c r="BL31" t="inlineStr"/>
+      <c r="BM31" t="inlineStr"/>
+      <c r="BN31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>EF8gXauC</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45520.54166666666</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">petersen m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flyeralarm arena
+  wurzburger </t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>13090</v>
+      </c>
+      <c r="F32" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>nVM1YUFj</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="n">
+        <v>31</v>
+      </c>
+      <c r="N32" t="n">
+        <v>69</v>
+      </c>
+      <c r="O32" t="n">
+        <v>9</v>
+      </c>
+      <c r="P32" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>4</v>
+      </c>
+      <c r="R32" t="n">
+        <v>8</v>
+      </c>
+      <c r="S32" t="n">
+        <v>11</v>
+      </c>
+      <c r="T32" t="n">
+        <v>13</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>lEwgk7go</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="W32" t="n">
+        <v>59</v>
+      </c>
+      <c r="X32" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>186.8888888888889</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>73.22222222222223</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>7694444.444444444</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>76.88888888888889</v>
+      </c>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AU32" t="n">
+        <v>23.94117647058824</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>184.4117647058823</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.529411764705882</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>72.05882352941177</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>7377941.176470588</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>78.58823529411765</v>
+      </c>
+      <c r="BA32" t="inlineStr"/>
+      <c r="BB32" t="inlineStr"/>
+      <c r="BC32" t="inlineStr"/>
+      <c r="BD32" t="inlineStr"/>
+      <c r="BE32" t="inlineStr"/>
+      <c r="BF32" t="inlineStr"/>
+      <c r="BG32" t="inlineStr"/>
+      <c r="BH32" t="inlineStr"/>
+      <c r="BI32" t="inlineStr"/>
+      <c r="BJ32" t="inlineStr"/>
+      <c r="BK32" t="inlineStr"/>
+      <c r="BL32" t="inlineStr"/>
+      <c r="BM32" t="inlineStr"/>
+      <c r="BN32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>QHrzGLhf</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45515.35416666666</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reichel t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eintracht stadion
+  braunschweig </t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>23325</v>
+      </c>
+      <c r="F33" t="n">
+        <v>22791</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>YFuz2RLm</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="L33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M33" t="n">
+        <v>49</v>
+      </c>
+      <c r="N33" t="n">
+        <v>51</v>
+      </c>
+      <c r="O33" t="n">
+        <v>20</v>
+      </c>
+      <c r="P33" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>8</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6</v>
+      </c>
+      <c r="S33" t="n">
+        <v>9</v>
+      </c>
+      <c r="T33" t="n">
+        <v>15</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SQrxFAMl</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>IgZoGKFn</t>
+        </is>
+      </c>
+      <c r="W33" t="n">
+        <v>59</v>
+      </c>
+      <c r="X33" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="n">
+        <v>25.625</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>186.125</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>67.75</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1428125</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="n">
+        <v>25.1875</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>182</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>66.8125</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>1287500</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>70.9375</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>24.73684210526316</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>178.7368421052632</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>67.36842105263158</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1485526.315789474</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>70.26315789473684</v>
+      </c>
+      <c r="BA33" t="inlineStr"/>
+      <c r="BB33" t="inlineStr"/>
+      <c r="BC33" t="inlineStr"/>
+      <c r="BD33" t="inlineStr"/>
+      <c r="BE33" t="inlineStr"/>
+      <c r="BF33" t="inlineStr"/>
+      <c r="BG33" t="inlineStr"/>
+      <c r="BH33" t="inlineStr"/>
+      <c r="BI33" t="inlineStr"/>
+      <c r="BJ33" t="inlineStr"/>
+      <c r="BK33" t="inlineStr"/>
+      <c r="BL33" t="inlineStr"/>
+      <c r="BM33" t="inlineStr"/>
+      <c r="BN33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>MqxqEaN6</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45515.35416666666</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">erbst l 
+  ger </t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">preussenstadion
+  munster </t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>12794</v>
+      </c>
+      <c r="F34" t="n">
+        <v>12422</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>zedZaSL7</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M34" t="n">
+        <v>47</v>
+      </c>
+      <c r="N34" t="n">
+        <v>53</v>
+      </c>
+      <c r="O34" t="n">
+        <v>11</v>
+      </c>
+      <c r="P34" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="n">
+        <v>13</v>
+      </c>
+      <c r="T34" t="n">
+        <v>11</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>pdPRS0me</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>t0ZPdkUl</t>
+        </is>
+      </c>
+      <c r="W34" t="n">
+        <v>59</v>
+      </c>
+      <c r="X34" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>2082500</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>25.57142857142857</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>181.8571428571429</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>66.71428571428571</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1175000</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>68.42857142857143</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>24.17391304347826</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>183.5652173913043</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>67.56521739130434</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1753260.869565217</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>72.60869565217391</v>
+      </c>
+      <c r="BA34" t="inlineStr"/>
+      <c r="BB34" t="inlineStr"/>
+      <c r="BC34" t="inlineStr"/>
+      <c r="BD34" t="inlineStr"/>
+      <c r="BE34" t="inlineStr"/>
+      <c r="BF34" t="inlineStr"/>
+      <c r="BG34" t="inlineStr"/>
+      <c r="BH34" t="inlineStr"/>
+      <c r="BI34" t="inlineStr"/>
+      <c r="BJ34" t="inlineStr"/>
+      <c r="BK34" t="inlineStr"/>
+      <c r="BL34" t="inlineStr"/>
+      <c r="BM34" t="inlineStr"/>
+      <c r="BN34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>KdD11Mw1</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45515.35416666666</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schwengers p 
+  ger </t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">home deluxe arena
+  paderborn </t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F35" t="n">
+        <v>12972</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>G2Op923t</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>S0hPB9rA</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="M35" t="n">
+        <v>54</v>
+      </c>
+      <c r="N35" t="n">
+        <v>46</v>
+      </c>
+      <c r="O35" t="n">
+        <v>18</v>
+      </c>
+      <c r="P35" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>5</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7</v>
+      </c>
+      <c r="S35" t="n">
+        <v>8</v>
+      </c>
+      <c r="T35" t="n">
+        <v>11</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>0AI1QUJH</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>MDhPV0RQ</t>
+        </is>
+      </c>
+      <c r="W35" t="n">
+        <v>59</v>
+      </c>
+      <c r="X35" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="AC35" t="n">
+        <v>25.125</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>183.625</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>67</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1356250</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>72</v>
+      </c>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="n">
+        <v>25.11111111111111</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>186.1111111111111</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>67.22222222222223</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1555555.555555556</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>72.55555555555556</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>24.27777777777778</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>184.8888888888889</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>68.44444444444444</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1895833.333333333</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>73.66666666666667</v>
+      </c>
+      <c r="BA35" t="inlineStr"/>
+      <c r="BB35" t="inlineStr"/>
+      <c r="BC35" t="inlineStr"/>
+      <c r="BD35" t="inlineStr"/>
+      <c r="BE35" t="inlineStr"/>
+      <c r="BF35" t="inlineStr"/>
+      <c r="BG35" t="inlineStr"/>
+      <c r="BH35" t="inlineStr"/>
+      <c r="BI35" t="inlineStr"/>
+      <c r="BJ35" t="inlineStr"/>
+      <c r="BK35" t="inlineStr"/>
+      <c r="BL35" t="inlineStr"/>
+      <c r="BM35" t="inlineStr"/>
+      <c r="BN35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>CW9g3r9l</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45514.64583333334</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gerach t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volksparkstadion
+  hamburg </t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>57274</v>
+      </c>
+      <c r="F36" t="n">
+        <v>57000</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2y0u8Wrq</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="M36" t="n">
+        <v>48</v>
+      </c>
+      <c r="N36" t="n">
+        <v>52</v>
+      </c>
+      <c r="O36" t="n">
+        <v>13</v>
+      </c>
+      <c r="P36" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3</v>
+      </c>
+      <c r="R36" t="n">
+        <v>4</v>
+      </c>
+      <c r="S36" t="n">
+        <v>9</v>
+      </c>
+      <c r="T36" t="n">
+        <v>8</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>YmfcAeCo</t>
+        </is>
+      </c>
+      <c r="W36" t="n">
+        <v>59</v>
+      </c>
+      <c r="X36" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>2470000</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>183.3</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>2420000</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>25.70588235294118</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>184.5294117647059</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>70.23529411764706</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>2645882.352941176</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>73.05882352941177</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>23.56521739130435</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>184.2173913043478</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>68.43478260869566</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>1948913.043478261</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>74.39130434782609</v>
+      </c>
+      <c r="BA36" t="inlineStr"/>
+      <c r="BB36" t="inlineStr"/>
+      <c r="BC36" t="inlineStr"/>
+      <c r="BD36" t="inlineStr"/>
+      <c r="BE36" t="inlineStr"/>
+      <c r="BF36" t="inlineStr"/>
+      <c r="BG36" t="inlineStr"/>
+      <c r="BH36" t="inlineStr"/>
+      <c r="BI36" t="inlineStr"/>
+      <c r="BJ36" t="inlineStr"/>
+      <c r="BK36" t="inlineStr"/>
+      <c r="BL36" t="inlineStr"/>
+      <c r="BM36" t="inlineStr"/>
+      <c r="BN36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>IViLLjPF</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45514.33333333334</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">merkur spiel arena
+  dusseldorf </t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>54600</v>
+      </c>
+      <c r="F37" t="n">
+        <v>36103</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ne1oL3y7</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>EB3q7jbk</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M37" t="n">
+        <v>53</v>
+      </c>
+      <c r="N37" t="n">
+        <v>47</v>
+      </c>
+      <c r="O37" t="n">
+        <v>20</v>
+      </c>
+      <c r="P37" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>6</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2</v>
+      </c>
+      <c r="S37" t="n">
+        <v>6</v>
+      </c>
+      <c r="T37" t="n">
+        <v>6</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>AoL97rX8</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>OzPMRhK3</t>
+        </is>
+      </c>
+      <c r="W37" t="n">
+        <v>59</v>
+      </c>
+      <c r="X37" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="AC37" t="n">
+        <v>25.63636363636364</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>182.7272727272727</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>70</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>2334090.909090909</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>73.90909090909091</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>26.27272727272727</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>184.3636363636364</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>67.81818181818181</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1395454.545454545</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>71.90909090909091</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>22.69230769230769</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>186.3846153846154</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>66</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>1753846.153846154</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>73.53846153846153</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>23.3125</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>181</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1126250</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>72.5625</v>
+      </c>
+      <c r="BA37" t="inlineStr"/>
+      <c r="BB37" t="inlineStr"/>
+      <c r="BC37" t="inlineStr"/>
+      <c r="BD37" t="inlineStr"/>
+      <c r="BE37" t="inlineStr"/>
+      <c r="BF37" t="inlineStr"/>
+      <c r="BG37" t="inlineStr"/>
+      <c r="BH37" t="inlineStr"/>
+      <c r="BI37" t="inlineStr"/>
+      <c r="BJ37" t="inlineStr"/>
+      <c r="BK37" t="inlineStr"/>
+      <c r="BL37" t="inlineStr"/>
+      <c r="BM37" t="inlineStr"/>
+      <c r="BN37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>tC1Aa08D</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45514.33333333334</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bauer t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waldstadion kaiserlinde
+  spiesen elversberg </t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>9970</v>
+      </c>
+      <c r="F38" t="n">
+        <v>9502</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="L38" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="M38" t="n">
+        <v>45</v>
+      </c>
+      <c r="N38" t="n">
+        <v>55</v>
+      </c>
+      <c r="O38" t="n">
+        <v>10</v>
+      </c>
+      <c r="P38" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3</v>
+      </c>
+      <c r="R38" t="n">
+        <v>9</v>
+      </c>
+      <c r="S38" t="n">
+        <v>13</v>
+      </c>
+      <c r="T38" t="n">
+        <v>13</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>8E8qmw3d</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>4fX0k7gg</t>
+        </is>
+      </c>
+      <c r="W38" t="n">
+        <v>59</v>
+      </c>
+      <c r="X38" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="AC38" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>182.3</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>185.4545454545455</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>71.27272727272727</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>4545454.545454546</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>78.63636363636364</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>25.30769230769231</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>182.3076923076923</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>65.23076923076923</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>975000</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>69.07692307692308</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>186.5714285714286</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>69.47619047619048</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>2787619.047619048</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>73.19047619047619</v>
+      </c>
+      <c r="BA38" t="inlineStr"/>
+      <c r="BB38" t="inlineStr"/>
+      <c r="BC38" t="inlineStr"/>
+      <c r="BD38" t="inlineStr"/>
+      <c r="BE38" t="inlineStr"/>
+      <c r="BF38" t="inlineStr"/>
+      <c r="BG38" t="inlineStr"/>
+      <c r="BH38" t="inlineStr"/>
+      <c r="BI38" t="inlineStr"/>
+      <c r="BJ38" t="inlineStr"/>
+      <c r="BK38" t="inlineStr"/>
+      <c r="BL38" t="inlineStr"/>
+      <c r="BM38" t="inlineStr"/>
+      <c r="BN38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>YJ3eN30K</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45514.33333333334</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">winter n 
+  ger </t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">max morlock stadion
+  nuremberg </t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>44308</v>
+      </c>
+      <c r="F39" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L39" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M39" t="n">
+        <v>51</v>
+      </c>
+      <c r="N39" t="n">
+        <v>49</v>
+      </c>
+      <c r="O39" t="n">
+        <v>8</v>
+      </c>
+      <c r="P39" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>5</v>
+      </c>
+      <c r="R39" t="n">
+        <v>5</v>
+      </c>
+      <c r="S39" t="n">
+        <v>11</v>
+      </c>
+      <c r="T39" t="n">
+        <v>12</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>tO31cZrF</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>txZLBQVC</t>
+        </is>
+      </c>
+      <c r="W39" t="n">
+        <v>59</v>
+      </c>
+      <c r="X39" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="AC39" t="n">
+        <v>22.77777777777778</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>182</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>66</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1697222.222222222</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>72.55555555555556</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>25.625</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>189.75</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>67.625</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1540625</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>28.125</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>180</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>67.875</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1209375</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>70</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>26.57142857142857</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>186.7142857142857</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>68.57142857142857</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1428571.428571429</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>70.57142857142857</v>
+      </c>
+      <c r="BA39" t="inlineStr"/>
+      <c r="BB39" t="inlineStr"/>
+      <c r="BC39" t="inlineStr"/>
+      <c r="BD39" t="inlineStr"/>
+      <c r="BE39" t="inlineStr"/>
+      <c r="BF39" t="inlineStr"/>
+      <c r="BG39" t="inlineStr"/>
+      <c r="BH39" t="inlineStr"/>
+      <c r="BI39" t="inlineStr"/>
+      <c r="BJ39" t="inlineStr"/>
+      <c r="BK39" t="inlineStr"/>
+      <c r="BL39" t="inlineStr"/>
+      <c r="BM39" t="inlineStr"/>
+      <c r="BN39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>StuiCwhJ</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45513.5625</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">benen l 
+  ger </t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jahnstadion regensburg
+  regensburg </t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>15210</v>
+      </c>
+      <c r="F40" t="n">
+        <v>12095</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>UiCmEP56</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>tbC3EcQn</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="M40" t="n">
+        <v>49</v>
+      </c>
+      <c r="N40" t="n">
+        <v>51</v>
+      </c>
+      <c r="O40" t="n">
+        <v>8</v>
+      </c>
+      <c r="P40" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R40" t="n">
+        <v>5</v>
+      </c>
+      <c r="S40" t="n">
+        <v>22</v>
+      </c>
+      <c r="T40" t="n">
+        <v>16</v>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>zyLSrbZQ</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>QevvB2nf</t>
+        </is>
+      </c>
+      <c r="W40" t="n">
+        <v>59</v>
+      </c>
+      <c r="X40" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr"/>
+      <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="inlineStr"/>
+      <c r="AP40" t="inlineStr"/>
+      <c r="AQ40" t="inlineStr"/>
+      <c r="AR40" t="inlineStr"/>
+      <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AU40" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>183</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>62</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>887500</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BA40" t="inlineStr"/>
+      <c r="BB40" t="inlineStr"/>
+      <c r="BC40" t="inlineStr"/>
+      <c r="BD40" t="inlineStr"/>
+      <c r="BE40" t="inlineStr"/>
+      <c r="BF40" t="inlineStr"/>
+      <c r="BG40" t="inlineStr"/>
+      <c r="BH40" t="inlineStr"/>
+      <c r="BI40" t="inlineStr"/>
+      <c r="BJ40" t="inlineStr"/>
+      <c r="BK40" t="inlineStr"/>
+      <c r="BL40" t="inlineStr"/>
+      <c r="BM40" t="inlineStr"/>
+      <c r="BN40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>h4pSHsOs</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45513.5625</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lechner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fritz walter stadion
+  kaiserslautern </t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>49500</v>
+      </c>
+      <c r="F41" t="n">
+        <v>41632</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="L41" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M41" t="n">
+        <v>54</v>
+      </c>
+      <c r="N41" t="n">
+        <v>46</v>
+      </c>
+      <c r="O41" t="n">
+        <v>13</v>
+      </c>
+      <c r="P41" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>7</v>
+      </c>
+      <c r="R41" t="n">
+        <v>8</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="n">
+        <v>14</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>4bJLk19p</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>8E86CPuD</t>
+        </is>
+      </c>
+      <c r="W41" t="n">
+        <v>59</v>
+      </c>
+      <c r="X41" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="AC41" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>184.6363636363636</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>67.63636363636364</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1484090.909090909</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>70.63636363636364</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>183.1</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>67</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1480000</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>25.23529411764706</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>181.4705882352941</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>68.05882352941177</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>1691176.470588235</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>71.29411764705883</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>23.13636363636364</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>183.8181818181818</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>65.31818181818181</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1430681.818181818</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>73.09090909090909</v>
+      </c>
+      <c r="BA41" t="inlineStr"/>
+      <c r="BB41" t="inlineStr"/>
+      <c r="BC41" t="inlineStr"/>
+      <c r="BD41" t="inlineStr"/>
+      <c r="BE41" t="inlineStr"/>
+      <c r="BF41" t="inlineStr"/>
+      <c r="BG41" t="inlineStr"/>
+      <c r="BH41" t="inlineStr"/>
+      <c r="BI41" t="inlineStr"/>
+      <c r="BJ41" t="inlineStr"/>
+      <c r="BK41" t="inlineStr"/>
+      <c r="BL41" t="inlineStr"/>
+      <c r="BM41" t="inlineStr"/>
+      <c r="BN41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>2Hl43AnC</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>45508.35416666666</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hempel r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sportpark ronhof thomas sommer
+  furth </t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>16626</v>
+      </c>
+      <c r="F42" t="n">
+        <v>12664</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>zedZaSL7</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L42" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="M42" t="n">
+        <v>47</v>
+      </c>
+      <c r="N42" t="n">
+        <v>53</v>
+      </c>
+      <c r="O42" t="n">
+        <v>22</v>
+      </c>
+      <c r="P42" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>9</v>
+      </c>
+      <c r="R42" t="n">
+        <v>5</v>
+      </c>
+      <c r="S42" t="n">
+        <v>9</v>
+      </c>
+      <c r="T42" t="n">
+        <v>11</v>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>8E86CPuD</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>pdPRS0me</t>
+        </is>
+      </c>
+      <c r="W42" t="n">
+        <v>59</v>
+      </c>
+      <c r="X42" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>183.1</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>67</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1480000</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="n">
+        <v>22.72727272727273</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>182.5454545454545</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>64.59090909090909</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>1273863.636363636</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>72.86363636363636</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>25.57142857142857</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>181.8571428571429</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>66.71428571428571</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>1175000</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>68.42857142857143</v>
+      </c>
+      <c r="BA42" t="inlineStr"/>
+      <c r="BB42" t="inlineStr"/>
+      <c r="BC42" t="inlineStr"/>
+      <c r="BD42" t="inlineStr"/>
+      <c r="BE42" t="inlineStr"/>
+      <c r="BF42" t="inlineStr"/>
+      <c r="BG42" t="inlineStr"/>
+      <c r="BH42" t="inlineStr"/>
+      <c r="BI42" t="inlineStr"/>
+      <c r="BJ42" t="inlineStr"/>
+      <c r="BK42" t="inlineStr"/>
+      <c r="BL42" t="inlineStr"/>
+      <c r="BM42" t="inlineStr"/>
+      <c r="BN42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>SIOxI915</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>45508.35416666666</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schroder r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">donaustadion
+  ulm </t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>19500</v>
+      </c>
+      <c r="F43" t="n">
+        <v>17400</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>tbC3EcQn</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L43" t="n">
+        <v>3</v>
+      </c>
+      <c r="M43" t="n">
+        <v>54</v>
+      </c>
+      <c r="N43" t="n">
+        <v>46</v>
+      </c>
+      <c r="O43" t="n">
+        <v>12</v>
+      </c>
+      <c r="P43" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3</v>
+      </c>
+      <c r="R43" t="n">
+        <v>4</v>
+      </c>
+      <c r="S43" t="n">
+        <v>12</v>
+      </c>
+      <c r="T43" t="n">
+        <v>16</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>QevvB2nf</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>4bJLk19p</t>
+        </is>
+      </c>
+      <c r="W43" t="n">
+        <v>59</v>
+      </c>
+      <c r="X43" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>184.6363636363636</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>67.63636363636364</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>1484090.909090909</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>70.63636363636364</v>
+      </c>
+      <c r="AO43" t="inlineStr"/>
+      <c r="AP43" t="inlineStr"/>
+      <c r="AQ43" t="inlineStr"/>
+      <c r="AR43" t="inlineStr"/>
+      <c r="AS43" t="inlineStr"/>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AU43" t="n">
+        <v>25.22222222222222</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>180.9444444444445</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>1468055.555555556</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>71.11111111111111</v>
+      </c>
+      <c r="BA43" t="inlineStr"/>
+      <c r="BB43" t="inlineStr"/>
+      <c r="BC43" t="inlineStr"/>
+      <c r="BD43" t="inlineStr"/>
+      <c r="BE43" t="inlineStr"/>
+      <c r="BF43" t="inlineStr"/>
+      <c r="BG43" t="inlineStr"/>
+      <c r="BH43" t="inlineStr"/>
+      <c r="BI43" t="inlineStr"/>
+      <c r="BJ43" t="inlineStr"/>
+      <c r="BK43" t="inlineStr"/>
+      <c r="BL43" t="inlineStr"/>
+      <c r="BM43" t="inlineStr"/>
+      <c r="BN43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>vJqPCEPP</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>45508.35416666666</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kampka r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">merck stadion am bollenfalltor
+  darmstadt </t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>17810</v>
+      </c>
+      <c r="F44" t="n">
+        <v>17810</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>S0hPB9rA</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>ne1oL3y7</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M44" t="n">
+        <v>47</v>
+      </c>
+      <c r="N44" t="n">
+        <v>53</v>
+      </c>
+      <c r="O44" t="n">
+        <v>11</v>
+      </c>
+      <c r="P44" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>6</v>
+      </c>
+      <c r="R44" t="n">
+        <v>4</v>
+      </c>
+      <c r="S44" t="n">
+        <v>16</v>
+      </c>
+      <c r="T44" t="n">
+        <v>7</v>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>MDhPV0RQ</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>AoL97rX8</t>
+        </is>
+      </c>
+      <c r="W44" t="n">
+        <v>59</v>
+      </c>
+      <c r="X44" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>183.3</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>2490000</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>74</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>25.6875</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>186.25</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>1679687.5</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>73.1875</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>21.95454545454545</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>186.4545454545455</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>64.04545454545455</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>1346590.909090909</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>72.95454545454545</v>
+      </c>
+      <c r="BA44" t="inlineStr"/>
+      <c r="BB44" t="inlineStr"/>
+      <c r="BC44" t="inlineStr"/>
+      <c r="BD44" t="inlineStr"/>
+      <c r="BE44" t="inlineStr"/>
+      <c r="BF44" t="inlineStr"/>
+      <c r="BG44" t="inlineStr"/>
+      <c r="BH44" t="inlineStr"/>
+      <c r="BI44" t="inlineStr"/>
+      <c r="BJ44" t="inlineStr"/>
+      <c r="BK44" t="inlineStr"/>
+      <c r="BL44" t="inlineStr"/>
+      <c r="BM44" t="inlineStr"/>
+      <c r="BN44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>EeIMLi2t</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>45507.64583333334</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stieler t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">veltins arena
+  gelsenkirchen </t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>62271</v>
+      </c>
+      <c r="F45" t="n">
+        <v>61000</v>
+      </c>
+      <c r="G45" t="n">
+        <v>5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M45" t="n">
+        <v>52</v>
+      </c>
+      <c r="N45" t="n">
+        <v>48</v>
+      </c>
+      <c r="O45" t="n">
+        <v>14</v>
+      </c>
+      <c r="P45" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>8</v>
+      </c>
+      <c r="R45" t="n">
+        <v>5</v>
+      </c>
+      <c r="S45" t="n">
+        <v>13</v>
+      </c>
+      <c r="T45" t="n">
+        <v>11</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>txZLBQVC</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>SQrxFAMl</t>
+        </is>
+      </c>
+      <c r="W45" t="n">
+        <v>59</v>
+      </c>
+      <c r="X45" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="AC45" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>187.125</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>69</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>1740625</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>183.25</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>66.875</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>1287500</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>27.22222222222222</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>190.2222222222222</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>67.94444444444444</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>1294444.444444444</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>70.88888888888889</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>24.57142857142857</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>184.9285714285714</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>66.07142857142857</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>1302142.857142857</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>71.14285714285714</v>
+      </c>
+      <c r="BA45" t="inlineStr"/>
+      <c r="BB45" t="inlineStr"/>
+      <c r="BC45" t="inlineStr"/>
+      <c r="BD45" t="inlineStr"/>
+      <c r="BE45" t="inlineStr"/>
+      <c r="BF45" t="inlineStr"/>
+      <c r="BG45" t="inlineStr"/>
+      <c r="BH45" t="inlineStr"/>
+      <c r="BI45" t="inlineStr"/>
+      <c r="BJ45" t="inlineStr"/>
+      <c r="BK45" t="inlineStr"/>
+      <c r="BL45" t="inlineStr"/>
+      <c r="BM45" t="inlineStr"/>
+      <c r="BN45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>OWxD1lHO</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>45507.33333333334</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">haslberger w 
+  ger </t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">olympiastadion
+  berlin </t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>74667</v>
+      </c>
+      <c r="F46" t="n">
+        <v>48591</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2y0u8Wrq</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>G2Op923t</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L46" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M46" t="n">
+        <v>57</v>
+      </c>
+      <c r="N46" t="n">
+        <v>43</v>
+      </c>
+      <c r="O46" t="n">
+        <v>10</v>
+      </c>
+      <c r="P46" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>3</v>
+      </c>
+      <c r="R46" t="n">
+        <v>5</v>
+      </c>
+      <c r="S46" t="n">
+        <v>16</v>
+      </c>
+      <c r="T46" t="n">
+        <v>7</v>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>YmfcAeCo</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>0AI1QUJH</t>
+        </is>
+      </c>
+      <c r="W46" t="n">
+        <v>59</v>
+      </c>
+      <c r="X46" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="n">
+        <v>23.22222222222222</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>183.7777777777778</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>69.44444444444444</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>2422222.222222222</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>76.11111111111111</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>25.125</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>183.625</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>67</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>1356250</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>72</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>2360000</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>24.9375</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>186.1875</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>66.9375</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>1417187.5</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>72.125</v>
+      </c>
+      <c r="BA46" t="inlineStr"/>
+      <c r="BB46" t="inlineStr"/>
+      <c r="BC46" t="inlineStr"/>
+      <c r="BD46" t="inlineStr"/>
+      <c r="BE46" t="inlineStr"/>
+      <c r="BF46" t="inlineStr"/>
+      <c r="BG46" t="inlineStr"/>
+      <c r="BH46" t="inlineStr"/>
+      <c r="BI46" t="inlineStr"/>
+      <c r="BJ46" t="inlineStr"/>
+      <c r="BK46" t="inlineStr"/>
+      <c r="BL46" t="inlineStr"/>
+      <c r="BM46" t="inlineStr"/>
+      <c r="BN46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>zkVf7hmm</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>45507.33333333334</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">braun r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bbbank wildpark
+  karlsruhe </t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>34302</v>
+      </c>
+      <c r="F47" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3</v>
+      </c>
+      <c r="H47" t="n">
+        <v>2</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>EB3q7jbk</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M47" t="n">
+        <v>51</v>
+      </c>
+      <c r="N47" t="n">
+        <v>49</v>
+      </c>
+      <c r="O47" t="n">
+        <v>15</v>
+      </c>
+      <c r="P47" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>5</v>
+      </c>
+      <c r="R47" t="n">
+        <v>5</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="n">
+        <v>12</v>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>OzPMRhK3</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>tO31cZrF</t>
+        </is>
+      </c>
+      <c r="W47" t="n">
+        <v>59</v>
+      </c>
+      <c r="X47" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="AC47" t="n">
+        <v>26.27272727272727</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>184.3636363636364</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>67.81818181818181</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>1395454.545454545</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>71.90909090909091</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>22.77777777777778</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>182</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>66</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>1697222.222222222</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>72.55555555555556</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>22.78947368421053</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>181.1052631578947</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>64.84210526315789</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>1087894.736842105</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>72.84210526315789</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>27.77777777777778</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>181.2222222222222</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>67.44444444444444</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>1377777.777777778</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>70.22222222222223</v>
+      </c>
+      <c r="BA47" t="inlineStr"/>
+      <c r="BB47" t="inlineStr"/>
+      <c r="BC47" t="inlineStr"/>
+      <c r="BD47" t="inlineStr"/>
+      <c r="BE47" t="inlineStr"/>
+      <c r="BF47" t="inlineStr"/>
+      <c r="BG47" t="inlineStr"/>
+      <c r="BH47" t="inlineStr"/>
+      <c r="BI47" t="inlineStr"/>
+      <c r="BJ47" t="inlineStr"/>
+      <c r="BK47" t="inlineStr"/>
+      <c r="BL47" t="inlineStr"/>
+      <c r="BM47" t="inlineStr"/>
+      <c r="BN47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>f5QUJVWh</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>45507.33333333334</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heft f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mdcc arena
+  magdeburg </t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>30098</v>
+      </c>
+      <c r="F48" t="n">
+        <v>21469</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>YFuz2RLm</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M48" t="n">
+        <v>63</v>
+      </c>
+      <c r="N48" t="n">
+        <v>37</v>
+      </c>
+      <c r="O48" t="n">
+        <v>21</v>
+      </c>
+      <c r="P48" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>6</v>
+      </c>
+      <c r="R48" t="n">
+        <v>3</v>
+      </c>
+      <c r="S48" t="n">
+        <v>11</v>
+      </c>
+      <c r="T48" t="n">
+        <v>8</v>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>IgZoGKFn</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>8E8qmw3d</t>
+        </is>
+      </c>
+      <c r="W48" t="n">
+        <v>59</v>
+      </c>
+      <c r="X48" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>182.3</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>24.93333333333333</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>176.3333333333333</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>1375000</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>181.4666666666667</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>64.93333333333334</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>908333.3333333334</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>68.26666666666667</v>
+      </c>
+      <c r="BA48" t="inlineStr"/>
+      <c r="BB48" t="inlineStr"/>
+      <c r="BC48" t="inlineStr"/>
+      <c r="BD48" t="inlineStr"/>
+      <c r="BE48" t="inlineStr"/>
+      <c r="BF48" t="inlineStr"/>
+      <c r="BG48" t="inlineStr"/>
+      <c r="BH48" t="inlineStr"/>
+      <c r="BI48" t="inlineStr"/>
+      <c r="BJ48" t="inlineStr"/>
+      <c r="BK48" t="inlineStr"/>
+      <c r="BL48" t="inlineStr"/>
+      <c r="BM48" t="inlineStr"/>
+      <c r="BN48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>fiod5WHa</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>45507.33333333334</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bacher m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heinz von heiden arena
+  hannover </t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>49200</v>
+      </c>
+      <c r="F49" t="n">
+        <v>31800</v>
+      </c>
+      <c r="G49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>UiCmEP56</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>2</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="M49" t="n">
+        <v>58</v>
+      </c>
+      <c r="N49" t="n">
+        <v>42</v>
+      </c>
+      <c r="O49" t="n">
+        <v>16</v>
+      </c>
+      <c r="P49" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>5</v>
+      </c>
+      <c r="R49" t="n">
+        <v>3</v>
+      </c>
+      <c r="S49" t="n">
+        <v>12</v>
+      </c>
+      <c r="T49" t="n">
+        <v>17</v>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>t0ZPdkUl</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>zyLSrbZQ</t>
+        </is>
+      </c>
+      <c r="W49" t="n">
+        <v>59</v>
+      </c>
+      <c r="X49" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>2082500</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="inlineStr"/>
+      <c r="AK49" t="inlineStr"/>
+      <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="inlineStr"/>
+      <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="n">
+        <v>24.40909090909091</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>183.4545454545455</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>68</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>1812500</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>72.81818181818181</v>
+      </c>
+      <c r="AU49" t="inlineStr"/>
+      <c r="AV49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr"/>
+      <c r="AX49" t="inlineStr"/>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr"/>
+      <c r="BA49" t="inlineStr"/>
+      <c r="BB49" t="inlineStr"/>
+      <c r="BC49" t="inlineStr"/>
+      <c r="BD49" t="inlineStr"/>
+      <c r="BE49" t="inlineStr"/>
+      <c r="BF49" t="inlineStr"/>
+      <c r="BG49" t="inlineStr"/>
+      <c r="BH49" t="inlineStr"/>
+      <c r="BI49" t="inlineStr"/>
+      <c r="BJ49" t="inlineStr"/>
+      <c r="BK49" t="inlineStr"/>
+      <c r="BL49" t="inlineStr"/>
+      <c r="BM49" t="inlineStr"/>
+      <c r="BN49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>OA1xkBXI</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>45506.64583333334</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burda m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rheinenergiestadion
+  cologne </t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F50" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M50" t="n">
+        <v>58</v>
+      </c>
+      <c r="N50" t="n">
+        <v>42</v>
+      </c>
+      <c r="O50" t="n">
+        <v>26</v>
+      </c>
+      <c r="P50" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>4</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6</v>
+      </c>
+      <c r="S50" t="n">
+        <v>18</v>
+      </c>
+      <c r="T50" t="n">
+        <v>7</v>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>4fX0k7gg</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+      <c r="W50" t="n">
+        <v>59</v>
+      </c>
+      <c r="X50" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="AC50" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>186</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>4680000</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>79</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>2470000</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>25.78947368421053</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>184.7894736842105</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>1.210526315789474</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>68.63157894736842</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>2486315.789473684</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>73.05263157894737</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>183.25</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>2124000</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="BA50" t="inlineStr"/>
+      <c r="BB50" t="inlineStr"/>
+      <c r="BC50" t="inlineStr"/>
+      <c r="BD50" t="inlineStr"/>
+      <c r="BE50" t="inlineStr"/>
+      <c r="BF50" t="inlineStr"/>
+      <c r="BG50" t="inlineStr"/>
+      <c r="BH50" t="inlineStr"/>
+      <c r="BI50" t="inlineStr"/>
+      <c r="BJ50" t="inlineStr"/>
+      <c r="BK50" t="inlineStr"/>
+      <c r="BL50" t="inlineStr"/>
+      <c r="BM50" t="inlineStr"/>
+      <c r="BN50" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
+++ b/data/germany/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN111"/>
+  <dimension ref="A1:BN110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4776,7 +4776,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>tOBGu6Xo</t>
+          <t>rF6aucw3</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -4784,52 +4784,52 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">lechner f 
+          <t xml:space="preserve">bauer t 
   ger </t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">home deluxe arena
-  paderborn </t>
+          <t xml:space="preserve">eintracht stadion
+  braunschweig </t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>15000</v>
+        <v>23325</v>
       </c>
       <c r="F22" t="n">
-        <v>11985</v>
+        <v>19908</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>G2Op923t</t>
+          <t>QqLCC3il</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>tbC3EcQn</t>
+          <t>EB3q7jbk</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1.58</v>
+        <v>0.68</v>
       </c>
       <c r="L22" t="n">
-        <v>0.64</v>
+        <v>1.23</v>
       </c>
       <c r="M22" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="N22" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="O22" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="P22" t="n">
         <v>11</v>
@@ -4841,19 +4841,19 @@
         <v>3</v>
       </c>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T22" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0AI1QUJH</t>
+          <t>SQrxFAMl</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>QevvB2nf</t>
+          <t>OzPMRhK3</t>
         </is>
       </c>
       <c r="W22" t="n">
@@ -4868,56 +4868,88 @@
       <c r="Z22" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
       <c r="AC22" t="n">
-        <v>25.375</v>
+        <v>27.33333333333333</v>
       </c>
       <c r="AD22" t="n">
-        <v>183.625</v>
+        <v>185.5555555555555</v>
       </c>
       <c r="AE22" t="n">
-        <v>1</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AF22" t="n">
-        <v>67</v>
+        <v>68.88888888888889</v>
       </c>
       <c r="AG22" t="n">
-        <v>1368750</v>
+        <v>1561111.111111111</v>
       </c>
       <c r="AH22" t="n">
-        <v>72.375</v>
-      </c>
-      <c r="AI22" t="inlineStr"/>
-      <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr"/>
-      <c r="AN22" t="inlineStr"/>
+        <v>71</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>26.27272727272727</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>184.3636363636364</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>67.81818181818181</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1395454.545454545</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>71.90909090909091</v>
+      </c>
       <c r="AO22" t="n">
-        <v>24.44444444444444</v>
+        <v>24.93333333333333</v>
       </c>
       <c r="AP22" t="n">
-        <v>185.7777777777778</v>
+        <v>184.5333333333333</v>
       </c>
       <c r="AQ22" t="n">
         <v>1</v>
       </c>
       <c r="AR22" t="n">
-        <v>67.5</v>
+        <v>67.06666666666666</v>
       </c>
       <c r="AS22" t="n">
-        <v>1652777.777777778</v>
+        <v>1465000</v>
       </c>
       <c r="AT22" t="n">
-        <v>72.72222222222223</v>
-      </c>
-      <c r="AU22" t="inlineStr"/>
-      <c r="AV22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr"/>
-      <c r="AX22" t="inlineStr"/>
-      <c r="AY22" t="inlineStr"/>
-      <c r="AZ22" t="inlineStr"/>
+        <v>71.33333333333333</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>24.21052631578947</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>183.421052631579</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>66.31578947368421</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1262894.736842105</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>71.84210526315789</v>
+      </c>
       <c r="BA22" t="inlineStr"/>
       <c r="BB22" t="inlineStr"/>
       <c r="BC22" t="inlineStr"/>
@@ -5128,7 +5160,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>rF6aucw3</t>
+          <t>tOBGu6Xo</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -5136,52 +5168,52 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">bauer t 
+          <t xml:space="preserve">lechner f 
   ger </t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">eintracht stadion
-  braunschweig </t>
+          <t xml:space="preserve">home deluxe arena
+  paderborn </t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>23325</v>
+        <v>15000</v>
       </c>
       <c r="F24" t="n">
-        <v>19908</v>
+        <v>11985</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>QqLCC3il</t>
+          <t>G2Op923t</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>EB3q7jbk</t>
+          <t>tbC3EcQn</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>0.68</v>
+        <v>1.58</v>
       </c>
       <c r="L24" t="n">
-        <v>1.23</v>
+        <v>0.64</v>
       </c>
       <c r="M24" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="N24" t="n">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="O24" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="P24" t="n">
         <v>11</v>
@@ -5193,19 +5225,19 @@
         <v>3</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>SQrxFAMl</t>
+          <t>0AI1QUJH</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>OzPMRhK3</t>
+          <t>QevvB2nf</t>
         </is>
       </c>
       <c r="W24" t="n">
@@ -5220,88 +5252,56 @@
       <c r="Z24" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>dfNCCCzS</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>naWckLmC</t>
-        </is>
-      </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
-        <v>27.33333333333333</v>
+        <v>25.375</v>
       </c>
       <c r="AD24" t="n">
-        <v>185.5555555555555</v>
+        <v>183.625</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.111111111111111</v>
+        <v>1</v>
       </c>
       <c r="AF24" t="n">
-        <v>68.88888888888889</v>
+        <v>67</v>
       </c>
       <c r="AG24" t="n">
-        <v>1561111.111111111</v>
+        <v>1368750</v>
       </c>
       <c r="AH24" t="n">
-        <v>71</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>26.27272727272727</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>184.3636363636364</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>67.81818181818181</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1395454.545454545</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>71.90909090909091</v>
-      </c>
+        <v>72.375</v>
+      </c>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
       <c r="AO24" t="n">
-        <v>24.93333333333333</v>
+        <v>24.44444444444444</v>
       </c>
       <c r="AP24" t="n">
-        <v>184.5333333333333</v>
+        <v>185.7777777777778</v>
       </c>
       <c r="AQ24" t="n">
         <v>1</v>
       </c>
       <c r="AR24" t="n">
-        <v>67.06666666666666</v>
+        <v>67.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>1465000</v>
+        <v>1652777.777777778</v>
       </c>
       <c r="AT24" t="n">
-        <v>71.33333333333333</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>24.21052631578947</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>183.421052631579</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>66.31578947368421</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1262894.736842105</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>71.84210526315789</v>
-      </c>
+        <v>72.72222222222223</v>
+      </c>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr"/>
       <c r="BA24" t="inlineStr"/>
       <c r="BB24" t="inlineStr"/>
       <c r="BC24" t="inlineStr"/>
@@ -5944,7 +5944,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>U3QUqY85</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -5952,76 +5952,76 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">storks s 
+          <t xml:space="preserve">gerach t 
   ger </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">vonovia ruhrstadion
-  bochum </t>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>26000</v>
+        <v>60449</v>
       </c>
       <c r="F28" t="n">
-        <v>26000</v>
+        <v>59000</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>1.07</v>
+        <v>5.21</v>
       </c>
       <c r="L28" t="n">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="M28" t="n">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="N28" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="O28" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="P28" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="R28" t="n">
+        <v>7</v>
+      </c>
+      <c r="S28" t="n">
         <v>6</v>
       </c>
-      <c r="S28" t="n">
-        <v>9</v>
-      </c>
       <c r="T28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>8f6APkLc</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
       <c r="W28" t="n">
@@ -6038,127 +6038,127 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="AC28" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>185.2</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>8610000</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="AI28" t="n">
         <v>27.44444444444444</v>
       </c>
-      <c r="AD28" t="n">
-        <v>185.3333333333333</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>72</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>2758333.333333333</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>74</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>25.90909090909091</v>
-      </c>
       <c r="AJ28" t="n">
-        <v>184.8181818181818</v>
+        <v>183.7777777777778</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.636363636363636</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AL28" t="n">
-        <v>76.18181818181819</v>
+        <v>74.88888888888889</v>
       </c>
       <c r="AM28" t="n">
-        <v>10145454.54545454</v>
+        <v>6322222.222222222</v>
       </c>
       <c r="AN28" t="n">
-        <v>77.90909090909091</v>
+        <v>76.66666666666667</v>
       </c>
       <c r="AO28" t="n">
-        <v>22.77272727272727</v>
+        <v>22.89473684210526</v>
       </c>
       <c r="AP28" t="n">
-        <v>183.9545454545455</v>
+        <v>184.3684210526316</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1</v>
+        <v>1.368421052631579</v>
       </c>
       <c r="AR28" t="n">
-        <v>68.54545454545455</v>
+        <v>73.47368421052632</v>
       </c>
       <c r="AS28" t="n">
-        <v>2476136.363636364</v>
+        <v>8531578.947368421</v>
       </c>
       <c r="AT28" t="n">
-        <v>76.45454545454545</v>
+        <v>79.26315789473684</v>
       </c>
       <c r="AU28" t="n">
-        <v>24.33333333333333</v>
+        <v>25.7</v>
       </c>
       <c r="AV28" t="n">
-        <v>182.6666666666667</v>
+        <v>184.15</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AX28" t="n">
-        <v>73.58333333333333</v>
+        <v>72.05</v>
       </c>
       <c r="AY28" t="n">
-        <v>6058333.333333333</v>
+        <v>3926250</v>
       </c>
       <c r="AZ28" t="n">
-        <v>77.625</v>
+        <v>76.25</v>
       </c>
       <c r="BA28" t="n">
-        <v>27</v>
+        <v>21.5</v>
       </c>
       <c r="BB28" t="n">
-        <v>185.4</v>
+        <v>187</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.2</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="BD28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BE28" t="n">
-        <v>355</v>
+        <v>423</v>
       </c>
       <c r="BF28" t="n">
-        <v>11050000</v>
+        <v>32525000</v>
       </c>
       <c r="BG28" t="n">
-        <v>368</v>
+        <v>473</v>
       </c>
       <c r="BH28" t="n">
-        <v>19.33333333333333</v>
+        <v>24</v>
       </c>
       <c r="BI28" t="n">
-        <v>181.3333333333333</v>
+        <v>190</v>
       </c>
       <c r="BJ28" t="n">
         <v>1</v>
       </c>
       <c r="BK28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL28" t="n">
-        <v>194</v>
+        <v>75</v>
       </c>
       <c r="BM28" t="n">
-        <v>4625000</v>
+        <v>7000000</v>
       </c>
       <c r="BN28" t="n">
-        <v>230</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29">
@@ -6384,7 +6384,7 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>61DvZGfm</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -6392,76 +6392,76 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">gerach t 
+          <t xml:space="preserve">storks s 
   ger </t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">mhparena
-  stuttgart </t>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>60449</v>
+        <v>26000</v>
       </c>
       <c r="F30" t="n">
-        <v>59000</v>
+        <v>26000</v>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>5.21</v>
+        <v>1.07</v>
       </c>
       <c r="L30" t="n">
-        <v>2.25</v>
+        <v>2.84</v>
       </c>
       <c r="M30" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="N30" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="O30" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="P30" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6</v>
+      </c>
+      <c r="S30" t="n">
         <v>9</v>
       </c>
-      <c r="Q30" t="n">
-        <v>13</v>
-      </c>
-      <c r="R30" t="n">
-        <v>7</v>
-      </c>
-      <c r="S30" t="n">
-        <v>6</v>
-      </c>
       <c r="T30" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>GzfvcwRj</t>
+          <t>8f6APkLc</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
       <c r="W30" t="n">
@@ -6478,127 +6478,127 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>0Ija0Ej9</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>WG9pOTse</t>
         </is>
       </c>
       <c r="AC30" t="n">
-        <v>23.9</v>
+        <v>27.44444444444444</v>
       </c>
       <c r="AD30" t="n">
-        <v>185.2</v>
+        <v>185.3333333333333</v>
       </c>
       <c r="AE30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>72</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2758333.333333333</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>74</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>25.90909090909091</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>184.8181818181818</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.636363636363636</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>76.18181818181819</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>10145454.54545454</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>77.90909090909091</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>22.77272727272727</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>183.9545454545455</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>68.54545454545455</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>2476136.363636364</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>76.45454545454545</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>73.58333333333333</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>6058333.333333333</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>77.625</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>185.4</v>
+      </c>
+      <c r="BC30" t="n">
         <v>1.2</v>
       </c>
-      <c r="AF30" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>8610000</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>77.7</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>27.44444444444444</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>183.7777777777778</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>74.88888888888889</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>6322222.222222222</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>76.66666666666667</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>22.89473684210526</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>184.3684210526316</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>1.368421052631579</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>73.47368421052632</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>8531578.947368421</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>79.26315789473684</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>184.15</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>72.05</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>3926250</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>76.25</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>187</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>1.166666666666667</v>
-      </c>
       <c r="BD30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BE30" t="n">
-        <v>423</v>
+        <v>355</v>
       </c>
       <c r="BF30" t="n">
-        <v>32525000</v>
+        <v>11050000</v>
       </c>
       <c r="BG30" t="n">
-        <v>473</v>
+        <v>368</v>
       </c>
       <c r="BH30" t="n">
-        <v>24</v>
+        <v>19.33333333333333</v>
       </c>
       <c r="BI30" t="n">
-        <v>190</v>
+        <v>181.3333333333333</v>
       </c>
       <c r="BJ30" t="n">
         <v>1</v>
       </c>
       <c r="BK30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL30" t="n">
-        <v>75</v>
+        <v>194</v>
       </c>
       <c r="BM30" t="n">
-        <v>7000000</v>
+        <v>4625000</v>
       </c>
       <c r="BN30" t="n">
-        <v>79</v>
+        <v>230</v>
       </c>
     </row>
     <row r="31">
@@ -6824,7 +6824,7 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>fgQ4JFGq</t>
+          <t>A33XyOWA</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -6832,76 +6832,76 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">brych d  f 
+          <t xml:space="preserve">benen l 
   ger </t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">max morlock stadion
-  nuremberg </t>
+          <t xml:space="preserve">waldstadion kaiserlinde
+  spiesen elversberg </t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>50000</v>
+        <v>9970</v>
       </c>
       <c r="F32" t="n">
-        <v>31581</v>
+        <v>9443</v>
       </c>
       <c r="G32" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" t="n">
         <v>0</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>S0hPB9rA</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M32" t="n">
+        <v>50</v>
+      </c>
+      <c r="N32" t="n">
+        <v>50</v>
+      </c>
+      <c r="O32" t="n">
+        <v>17</v>
+      </c>
+      <c r="P32" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q32" t="n">
         <v>4</v>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>6FDqshzF</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>YFuz2RLm</t>
-        </is>
-      </c>
-      <c r="K32" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="L32" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="M32" t="n">
-        <v>42</v>
-      </c>
-      <c r="N32" t="n">
-        <v>58</v>
-      </c>
-      <c r="O32" t="n">
-        <v>7</v>
-      </c>
-      <c r="P32" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>3</v>
-      </c>
       <c r="R32" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T32" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>tO31cZrF</t>
+          <t>8E8qmw3d</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>IgZoGKFn</t>
+          <t>MDhPV0RQ</t>
         </is>
       </c>
       <c r="W32" t="n">
@@ -6916,83 +6916,71 @@
       <c r="Z32" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>CCQGbik8</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
       <c r="AC32" t="n">
-        <v>23.25</v>
+        <v>23.81818181818182</v>
       </c>
       <c r="AD32" t="n">
-        <v>183.5</v>
+        <v>182.5454545454545</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.125</v>
+        <v>1</v>
       </c>
       <c r="AF32" t="n">
-        <v>67.75</v>
+        <v>66.09090909090909</v>
       </c>
       <c r="AG32" t="n">
-        <v>2181250</v>
+        <v>1179545.454545455</v>
       </c>
       <c r="AH32" t="n">
-        <v>74.125</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>24.875</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>180.125</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>68</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1450000</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>71.125</v>
-      </c>
+        <v>71.81818181818181</v>
+      </c>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
       <c r="AO32" t="n">
-        <v>22</v>
+        <v>25.64705882352941</v>
       </c>
       <c r="AP32" t="n">
-        <v>177.6</v>
+        <v>185.0588235294118</v>
       </c>
       <c r="AQ32" t="n">
         <v>1</v>
       </c>
       <c r="AR32" t="n">
-        <v>68</v>
+        <v>67.05882352941177</v>
       </c>
       <c r="AS32" t="n">
-        <v>2230000</v>
+        <v>1364705.882352941</v>
       </c>
       <c r="AT32" t="n">
-        <v>75</v>
+        <v>70.35294117647059</v>
       </c>
       <c r="AU32" t="n">
-        <v>25.05882352941176</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="AV32" t="n">
-        <v>178.8235294117647</v>
+        <v>184.75</v>
       </c>
       <c r="AW32" t="n">
         <v>1</v>
       </c>
       <c r="AX32" t="n">
-        <v>66.76470588235294</v>
+        <v>68.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>1272058.823529412</v>
+        <v>1918750</v>
       </c>
       <c r="AZ32" t="n">
-        <v>69</v>
+        <v>74.16666666666667</v>
       </c>
       <c r="BA32" t="inlineStr"/>
       <c r="BB32" t="inlineStr"/>
@@ -7188,7 +7176,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>A33XyOWA</t>
+          <t>fgQ4JFGq</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -7196,76 +7184,76 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">benen l 
+          <t xml:space="preserve">brych d  f 
   ger </t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">waldstadion kaiserlinde
-  spiesen elversberg </t>
+          <t xml:space="preserve">max morlock stadion
+  nuremberg </t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>9970</v>
+        <v>50000</v>
       </c>
       <c r="F34" t="n">
-        <v>9443</v>
+        <v>31581</v>
       </c>
       <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
         <v>4</v>
       </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>6in2Eknb</t>
+          <t>6FDqshzF</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>S0hPB9rA</t>
+          <t>YFuz2RLm</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>2.31</v>
+        <v>1.42</v>
       </c>
       <c r="L34" t="n">
-        <v>1.56</v>
+        <v>2.63</v>
       </c>
       <c r="M34" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N34" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="O34" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="P34" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T34" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>8E8qmw3d</t>
+          <t>tO31cZrF</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>MDhPV0RQ</t>
+          <t>IgZoGKFn</t>
         </is>
       </c>
       <c r="W34" t="n">
@@ -7280,71 +7268,83 @@
       <c r="Z34" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA34" t="inlineStr"/>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
-        <v>23.81818181818182</v>
+        <v>23.25</v>
       </c>
       <c r="AD34" t="n">
-        <v>182.5454545454545</v>
+        <v>183.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>1</v>
+        <v>1.125</v>
       </c>
       <c r="AF34" t="n">
-        <v>66.09090909090909</v>
+        <v>67.75</v>
       </c>
       <c r="AG34" t="n">
-        <v>1179545.454545455</v>
+        <v>2181250</v>
       </c>
       <c r="AH34" t="n">
-        <v>71.81818181818181</v>
-      </c>
-      <c r="AI34" t="inlineStr"/>
-      <c r="AJ34" t="inlineStr"/>
-      <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="inlineStr"/>
-      <c r="AN34" t="inlineStr"/>
+        <v>74.125</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>24.875</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>180.125</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>68</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1450000</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>71.125</v>
+      </c>
       <c r="AO34" t="n">
-        <v>25.64705882352941</v>
+        <v>22</v>
       </c>
       <c r="AP34" t="n">
-        <v>185.0588235294118</v>
+        <v>177.6</v>
       </c>
       <c r="AQ34" t="n">
         <v>1</v>
       </c>
       <c r="AR34" t="n">
-        <v>67.05882352941177</v>
+        <v>68</v>
       </c>
       <c r="AS34" t="n">
-        <v>1364705.882352941</v>
+        <v>2230000</v>
       </c>
       <c r="AT34" t="n">
-        <v>70.35294117647059</v>
+        <v>75</v>
       </c>
       <c r="AU34" t="n">
-        <v>23.83333333333333</v>
+        <v>25.05882352941176</v>
       </c>
       <c r="AV34" t="n">
-        <v>184.75</v>
+        <v>178.8235294117647</v>
       </c>
       <c r="AW34" t="n">
         <v>1</v>
       </c>
       <c r="AX34" t="n">
-        <v>68.5</v>
+        <v>66.76470588235294</v>
       </c>
       <c r="AY34" t="n">
-        <v>1918750</v>
+        <v>1272058.823529412</v>
       </c>
       <c r="AZ34" t="n">
-        <v>74.16666666666667</v>
+        <v>69</v>
       </c>
       <c r="BA34" t="inlineStr"/>
       <c r="BB34" t="inlineStr"/>
@@ -8700,7 +8700,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>vL89UK7m</t>
+          <t>n7mhuxM5</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -8708,76 +8708,76 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">burda m 
+          <t xml:space="preserve">weisbach e 
   ger </t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">merck stadion am bollenfalltor
-  darmstadt </t>
+          <t xml:space="preserve">donaustadion
+  ulm </t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>17810</v>
+        <v>19500</v>
       </c>
       <c r="F42" t="n">
-        <v>17600</v>
+        <v>13226</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>S0hPB9rA</t>
+          <t>tbC3EcQn</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>6FDqshzF</t>
+          <t>ne1oL3y7</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>1.31</v>
+        <v>1.66</v>
       </c>
       <c r="L42" t="n">
-        <v>0.37</v>
+        <v>3.87</v>
       </c>
       <c r="M42" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="N42" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="O42" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P42" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>8</v>
+      </c>
+      <c r="R42" t="n">
         <v>5</v>
       </c>
-      <c r="Q42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R42" t="n">
-        <v>4</v>
-      </c>
       <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="n">
         <v>13</v>
       </c>
-      <c r="T42" t="n">
-        <v>11</v>
-      </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>MDhPV0RQ</t>
+          <t>QevvB2nf</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>tO31cZrF</t>
+          <t>AoL97rX8</t>
         </is>
       </c>
       <c r="W42" t="n">
@@ -8792,14 +8792,10 @@
       <c r="Z42" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
+      <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>CCQGbik8</t>
+          <t>WG9pOTse</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr"/>
@@ -8809,58 +8805,46 @@
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="n">
-        <v>23.25</v>
+        <v>26.18181818181818</v>
       </c>
       <c r="AJ42" t="n">
-        <v>183.5</v>
+        <v>184.6363636363636</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.125</v>
+        <v>1</v>
       </c>
       <c r="AL42" t="n">
-        <v>67.75</v>
+        <v>70.45454545454545</v>
       </c>
       <c r="AM42" t="n">
-        <v>2181250</v>
+        <v>2181818.181818182</v>
       </c>
       <c r="AN42" t="n">
-        <v>74.125</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>25.52631578947368</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>187.1052631578947</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>68.31578947368421</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>1584210.526315789</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>73.05263157894737</v>
-      </c>
+        <v>73.18181818181819</v>
+      </c>
+      <c r="AO42" t="inlineStr"/>
+      <c r="AP42" t="inlineStr"/>
+      <c r="AQ42" t="inlineStr"/>
+      <c r="AR42" t="inlineStr"/>
+      <c r="AS42" t="inlineStr"/>
+      <c r="AT42" t="inlineStr"/>
       <c r="AU42" t="n">
-        <v>25</v>
+        <v>22.28571428571428</v>
       </c>
       <c r="AV42" t="n">
-        <v>175.8</v>
+        <v>185.7142857142857</v>
       </c>
       <c r="AW42" t="n">
         <v>1</v>
       </c>
       <c r="AX42" t="n">
-        <v>68.3</v>
+        <v>65.80952380952381</v>
       </c>
       <c r="AY42" t="n">
-        <v>1635000</v>
+        <v>1441666.666666667</v>
       </c>
       <c r="AZ42" t="n">
-        <v>70.40000000000001</v>
+        <v>75.23809523809524</v>
       </c>
       <c r="BA42" t="inlineStr"/>
       <c r="BB42" t="inlineStr"/>
@@ -9068,7 +9052,7 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>n7mhuxM5</t>
+          <t>vL89UK7m</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -9076,76 +9060,76 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">weisbach e 
+          <t xml:space="preserve">burda m 
   ger </t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">donaustadion
-  ulm </t>
+          <t xml:space="preserve">merck stadion am bollenfalltor
+  darmstadt </t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>19500</v>
+        <v>17810</v>
       </c>
       <c r="F44" t="n">
-        <v>13226</v>
+        <v>17600</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>tbC3EcQn</t>
+          <t>S0hPB9rA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>ne1oL3y7</t>
+          <t>6FDqshzF</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>1.66</v>
+        <v>1.31</v>
       </c>
       <c r="L44" t="n">
-        <v>3.87</v>
+        <v>0.37</v>
       </c>
       <c r="M44" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="N44" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="O44" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P44" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Q44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T44" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>QevvB2nf</t>
+          <t>MDhPV0RQ</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>AoL97rX8</t>
+          <t>tO31cZrF</t>
         </is>
       </c>
       <c r="W44" t="n">
@@ -9160,10 +9144,14 @@
       <c r="Z44" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
+          <t>CCQGbik8</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr"/>
@@ -9173,46 +9161,58 @@
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="n">
-        <v>26.18181818181818</v>
+        <v>23.25</v>
       </c>
       <c r="AJ44" t="n">
-        <v>184.6363636363636</v>
+        <v>183.5</v>
       </c>
       <c r="AK44" t="n">
-        <v>1</v>
+        <v>1.125</v>
       </c>
       <c r="AL44" t="n">
-        <v>70.45454545454545</v>
+        <v>67.75</v>
       </c>
       <c r="AM44" t="n">
-        <v>2181818.181818182</v>
+        <v>2181250</v>
       </c>
       <c r="AN44" t="n">
-        <v>73.18181818181819</v>
-      </c>
-      <c r="AO44" t="inlineStr"/>
-      <c r="AP44" t="inlineStr"/>
-      <c r="AQ44" t="inlineStr"/>
-      <c r="AR44" t="inlineStr"/>
-      <c r="AS44" t="inlineStr"/>
-      <c r="AT44" t="inlineStr"/>
+        <v>74.125</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>25.52631578947368</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>187.1052631578947</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>68.31578947368421</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>1584210.526315789</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>73.05263157894737</v>
+      </c>
       <c r="AU44" t="n">
-        <v>22.28571428571428</v>
+        <v>25</v>
       </c>
       <c r="AV44" t="n">
-        <v>185.7142857142857</v>
+        <v>175.8</v>
       </c>
       <c r="AW44" t="n">
         <v>1</v>
       </c>
       <c r="AX44" t="n">
-        <v>65.80952380952381</v>
+        <v>68.3</v>
       </c>
       <c r="AY44" t="n">
-        <v>1441666.666666667</v>
+        <v>1635000</v>
       </c>
       <c r="AZ44" t="n">
-        <v>75.23809523809524</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="BA44" t="inlineStr"/>
       <c r="BB44" t="inlineStr"/>
@@ -10894,7 +10894,7 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>S2GROGyP</t>
+          <t>IReyqKMt</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
@@ -10902,76 +10902,76 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">braun r 
+          <t xml:space="preserve">hempel r 
   ger </t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">sportpark ronhof thomas sommer
-  furth </t>
+          <t xml:space="preserve">olympiastadion
+  berlin </t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>16626</v>
+        <v>74667</v>
       </c>
       <c r="F53" t="n">
-        <v>10261</v>
+        <v>42355</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>CCQGbik8</t>
+          <t>2y0u8Wrq</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>G2Op923t</t>
+          <t>UiCmEP56</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>0.95</v>
+        <v>0.51</v>
       </c>
       <c r="L53" t="n">
-        <v>1.95</v>
+        <v>1.39</v>
       </c>
       <c r="M53" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="N53" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="O53" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P53" t="n">
         <v>13</v>
       </c>
       <c r="Q53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S53" t="n">
         <v>12</v>
       </c>
       <c r="T53" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>8E86CPuD</t>
+          <t>YmfcAeCo</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>0AI1QUJH</t>
+          <t>zyLSrbZQ</t>
         </is>
       </c>
       <c r="W53" t="n">
@@ -10986,84 +10986,56 @@
       <c r="Z53" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>6FDqshzF</t>
-        </is>
-      </c>
+      <c r="AA53" t="inlineStr"/>
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="n">
-        <v>25</v>
+        <v>22.90909090909091</v>
       </c>
       <c r="AD53" t="n">
-        <v>183.1</v>
+        <v>181.9090909090909</v>
       </c>
       <c r="AE53" t="n">
-        <v>1</v>
+        <v>1.181818181818182</v>
       </c>
       <c r="AF53" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AG53" t="n">
-        <v>1480000</v>
+        <v>2354545.454545455</v>
       </c>
       <c r="AH53" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>183.375</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>66.625</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>1384375</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>72.625</v>
-      </c>
+        <v>76.09090909090909</v>
+      </c>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="inlineStr"/>
+      <c r="AK53" t="inlineStr"/>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr"/>
       <c r="AO53" t="n">
-        <v>23.1</v>
+        <v>24.28571428571428</v>
       </c>
       <c r="AP53" t="n">
-        <v>183.4</v>
+        <v>183.7619047619048</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1</v>
+        <v>1.19047619047619</v>
       </c>
       <c r="AR53" t="n">
-        <v>65.84999999999999</v>
+        <v>69.76190476190476</v>
       </c>
       <c r="AS53" t="n">
-        <v>1551250</v>
+        <v>2355952.380952381</v>
       </c>
       <c r="AT53" t="n">
-        <v>73.45</v>
-      </c>
-      <c r="AU53" t="n">
-        <v>25.75</v>
-      </c>
-      <c r="AV53" t="n">
-        <v>186.5</v>
-      </c>
-      <c r="AW53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX53" t="n">
-        <v>67.6875</v>
-      </c>
-      <c r="AY53" t="n">
-        <v>1481250</v>
-      </c>
-      <c r="AZ53" t="n">
-        <v>71.9375</v>
-      </c>
+        <v>75.14285714285714</v>
+      </c>
+      <c r="AU53" t="inlineStr"/>
+      <c r="AV53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr"/>
+      <c r="AX53" t="inlineStr"/>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr"/>
       <c r="BA53" t="inlineStr"/>
       <c r="BB53" t="inlineStr"/>
       <c r="BC53" t="inlineStr"/>
@@ -11082,7 +11054,7 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>IReyqKMt</t>
+          <t>S2GROGyP</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -11090,76 +11062,76 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">hempel r 
+          <t xml:space="preserve">braun r 
   ger </t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">olympiastadion
-  berlin </t>
+          <t xml:space="preserve">sportpark ronhof thomas sommer
+  furth </t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>74667</v>
+        <v>16626</v>
       </c>
       <c r="F54" t="n">
-        <v>42355</v>
+        <v>10261</v>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2y0u8Wrq</t>
+          <t>CCQGbik8</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>UiCmEP56</t>
+          <t>G2Op923t</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>0.51</v>
+        <v>0.95</v>
       </c>
       <c r="L54" t="n">
-        <v>1.39</v>
+        <v>1.95</v>
       </c>
       <c r="M54" t="n">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="N54" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="O54" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="P54" t="n">
         <v>13</v>
       </c>
       <c r="Q54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S54" t="n">
         <v>12</v>
       </c>
       <c r="T54" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>YmfcAeCo</t>
+          <t>8E86CPuD</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>zyLSrbZQ</t>
+          <t>0AI1QUJH</t>
         </is>
       </c>
       <c r="W54" t="n">
@@ -11174,56 +11146,84 @@
       <c r="Z54" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="n">
-        <v>22.90909090909091</v>
+        <v>25</v>
       </c>
       <c r="AD54" t="n">
-        <v>181.9090909090909</v>
+        <v>183.1</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.181818181818182</v>
+        <v>1</v>
       </c>
       <c r="AF54" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AG54" t="n">
-        <v>2354545.454545455</v>
+        <v>1480000</v>
       </c>
       <c r="AH54" t="n">
-        <v>76.09090909090909</v>
-      </c>
-      <c r="AI54" t="inlineStr"/>
-      <c r="AJ54" t="inlineStr"/>
-      <c r="AK54" t="inlineStr"/>
-      <c r="AL54" t="inlineStr"/>
-      <c r="AM54" t="inlineStr"/>
-      <c r="AN54" t="inlineStr"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>183.375</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>66.625</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>1384375</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>72.625</v>
+      </c>
       <c r="AO54" t="n">
-        <v>24.28571428571428</v>
+        <v>23.1</v>
       </c>
       <c r="AP54" t="n">
-        <v>183.7619047619048</v>
+        <v>183.4</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.19047619047619</v>
+        <v>1</v>
       </c>
       <c r="AR54" t="n">
-        <v>69.76190476190476</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="AS54" t="n">
-        <v>2355952.380952381</v>
+        <v>1551250</v>
       </c>
       <c r="AT54" t="n">
-        <v>75.14285714285714</v>
-      </c>
-      <c r="AU54" t="inlineStr"/>
-      <c r="AV54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr"/>
-      <c r="AX54" t="inlineStr"/>
-      <c r="AY54" t="inlineStr"/>
-      <c r="AZ54" t="inlineStr"/>
+        <v>73.45</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>67.6875</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>1481250</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>71.9375</v>
+      </c>
       <c r="BA54" t="inlineStr"/>
       <c r="BB54" t="inlineStr"/>
       <c r="BC54" t="inlineStr"/>
@@ -11462,7 +11462,7 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>800QQx7C</t>
+          <t>zm2ISbx0</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -11470,76 +11470,76 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">alt p 
+          <t xml:space="preserve">prigan f 
   ger </t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">heinz von heiden arena
-  hannover </t>
+          <t xml:space="preserve">bbbank wildpark
+  karlsruhe </t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>49200</v>
+        <v>34302</v>
       </c>
       <c r="F56" t="n">
-        <v>49000</v>
+        <v>26838</v>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>dfNCCCzS</t>
+          <t>EB3q7jbk</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>v9k3aY5F</t>
+          <t>6in2Eknb</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="L56" t="n">
-        <v>0.74</v>
+        <v>1.3</v>
       </c>
       <c r="M56" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N56" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O56" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P56" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q56" t="n">
         <v>8</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="R56" t="n">
         <v>3</v>
       </c>
-      <c r="R56" t="n">
-        <v>1</v>
-      </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T56" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>t0ZPdkUl</t>
+          <t>OzPMRhK3</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>EDRZkDzS</t>
+          <t>8E8qmw3d</t>
         </is>
       </c>
       <c r="W56" t="n">
@@ -11556,85 +11556,81 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>QqLCC3il</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="n">
         <v>26.27272727272727</v>
       </c>
       <c r="AD56" t="n">
-        <v>182.4545454545455</v>
+        <v>184.3636363636364</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.181818181818182</v>
+        <v>1</v>
       </c>
       <c r="AF56" t="n">
-        <v>70.27272727272727</v>
+        <v>67.81818181818181</v>
       </c>
       <c r="AG56" t="n">
-        <v>2138636.363636364</v>
+        <v>1395454.545454545</v>
       </c>
       <c r="AH56" t="n">
-        <v>73.18181818181819</v>
+        <v>71.90909090909091</v>
       </c>
       <c r="AI56" t="n">
-        <v>25.4</v>
+        <v>23.81818181818182</v>
       </c>
       <c r="AJ56" t="n">
-        <v>184.5</v>
+        <v>182.5454545454545</v>
       </c>
       <c r="AK56" t="n">
         <v>1</v>
       </c>
       <c r="AL56" t="n">
-        <v>71.7</v>
+        <v>66.09090909090909</v>
       </c>
       <c r="AM56" t="n">
-        <v>2910000</v>
+        <v>1179545.454545455</v>
       </c>
       <c r="AN56" t="n">
-        <v>74.8</v>
+        <v>71.81818181818181</v>
       </c>
       <c r="AO56" t="n">
-        <v>24.1</v>
+        <v>23.73333333333333</v>
       </c>
       <c r="AP56" t="n">
-        <v>184.8</v>
+        <v>182.8666666666667</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AR56" t="n">
-        <v>68.25</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="AS56" t="n">
-        <v>1988750</v>
+        <v>1133000</v>
       </c>
       <c r="AT56" t="n">
-        <v>74.15000000000001</v>
+        <v>72.13333333333334</v>
       </c>
       <c r="AU56" t="n">
-        <v>26.71428571428572</v>
+        <v>24</v>
       </c>
       <c r="AV56" t="n">
-        <v>186.4285714285714</v>
+        <v>184</v>
       </c>
       <c r="AW56" t="n">
         <v>1</v>
       </c>
       <c r="AX56" t="n">
-        <v>70.28571428571429</v>
+        <v>66.33333333333333</v>
       </c>
       <c r="AY56" t="n">
-        <v>2541428.571428571</v>
+        <v>1441666.666666667</v>
       </c>
       <c r="AZ56" t="n">
-        <v>72.14285714285714</v>
+        <v>72</v>
       </c>
       <c r="BA56" t="inlineStr"/>
       <c r="BB56" t="inlineStr"/>
@@ -11654,7 +11650,7 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>zm2ISbx0</t>
+          <t>800QQx7C</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
@@ -11662,76 +11658,76 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">prigan f 
+          <t xml:space="preserve">alt p 
   ger </t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">bbbank wildpark
-  karlsruhe </t>
+          <t xml:space="preserve">heinz von heiden arena
+  hannover </t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>34302</v>
+        <v>49200</v>
       </c>
       <c r="F57" t="n">
-        <v>26838</v>
+        <v>49000</v>
       </c>
       <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M57" t="n">
+        <v>52</v>
+      </c>
+      <c r="N57" t="n">
+        <v>48</v>
+      </c>
+      <c r="O57" t="n">
+        <v>9</v>
+      </c>
+      <c r="P57" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q57" t="n">
         <v>3</v>
       </c>
-      <c r="H57" t="n">
-        <v>2</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>EB3q7jbk</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>6in2Eknb</t>
-        </is>
-      </c>
-      <c r="K57" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="L57" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M57" t="n">
-        <v>50</v>
-      </c>
-      <c r="N57" t="n">
-        <v>50</v>
-      </c>
-      <c r="O57" t="n">
-        <v>11</v>
-      </c>
-      <c r="P57" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>8</v>
-      </c>
       <c r="R57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T57" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>OzPMRhK3</t>
+          <t>t0ZPdkUl</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>8E8qmw3d</t>
+          <t>EDRZkDzS</t>
         </is>
       </c>
       <c r="W57" t="n">
@@ -11748,81 +11744,85 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>naWckLmC</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr"/>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
       <c r="AC57" t="n">
         <v>26.27272727272727</v>
       </c>
       <c r="AD57" t="n">
-        <v>184.3636363636364</v>
+        <v>182.4545454545455</v>
       </c>
       <c r="AE57" t="n">
-        <v>1</v>
+        <v>1.181818181818182</v>
       </c>
       <c r="AF57" t="n">
-        <v>67.81818181818181</v>
+        <v>70.27272727272727</v>
       </c>
       <c r="AG57" t="n">
-        <v>1395454.545454545</v>
+        <v>2138636.363636364</v>
       </c>
       <c r="AH57" t="n">
-        <v>71.90909090909091</v>
+        <v>73.18181818181819</v>
       </c>
       <c r="AI57" t="n">
-        <v>23.81818181818182</v>
+        <v>25.4</v>
       </c>
       <c r="AJ57" t="n">
-        <v>182.5454545454545</v>
+        <v>184.5</v>
       </c>
       <c r="AK57" t="n">
         <v>1</v>
       </c>
       <c r="AL57" t="n">
-        <v>66.09090909090909</v>
+        <v>71.7</v>
       </c>
       <c r="AM57" t="n">
-        <v>1179545.454545455</v>
+        <v>2910000</v>
       </c>
       <c r="AN57" t="n">
-        <v>71.81818181818181</v>
+        <v>74.8</v>
       </c>
       <c r="AO57" t="n">
-        <v>23.73333333333333</v>
+        <v>24.1</v>
       </c>
       <c r="AP57" t="n">
-        <v>182.8666666666667</v>
+        <v>184.8</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AR57" t="n">
-        <v>65.59999999999999</v>
+        <v>68.25</v>
       </c>
       <c r="AS57" t="n">
-        <v>1133000</v>
+        <v>1988750</v>
       </c>
       <c r="AT57" t="n">
-        <v>72.13333333333334</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="AU57" t="n">
-        <v>24</v>
+        <v>26.71428571428572</v>
       </c>
       <c r="AV57" t="n">
-        <v>184</v>
+        <v>186.4285714285714</v>
       </c>
       <c r="AW57" t="n">
         <v>1</v>
       </c>
       <c r="AX57" t="n">
-        <v>66.33333333333333</v>
+        <v>70.28571428571429</v>
       </c>
       <c r="AY57" t="n">
-        <v>1441666.666666667</v>
+        <v>2541428.571428571</v>
       </c>
       <c r="AZ57" t="n">
-        <v>72</v>
+        <v>72.14285714285714</v>
       </c>
       <c r="BA57" t="inlineStr"/>
       <c r="BB57" t="inlineStr"/>
@@ -12190,7 +12190,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>Sff03OL7</t>
+          <t>06NAdG8N</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -12198,51 +12198,51 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">alt p 
+          <t xml:space="preserve">osmers h 
   ger </t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">bieberer berg stadion
-  offenbach am main </t>
+          <t xml:space="preserve">stadion der freundschaft
+  cottbus </t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>20500</v>
+        <v>22450</v>
       </c>
       <c r="F60" t="n">
-        <v>16847</v>
+        <v>20000</v>
       </c>
       <c r="G60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>YJURlaIO</t>
+          <t>6g44VD52</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>YFuz2RLm</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="N60" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q60" t="n">
         <v>3</v>
@@ -12251,19 +12251,19 @@
         <v>9</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="T60" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>GWkh67yH</t>
+          <t>tnTvQd1l</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>IgZoGKFn</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
       <c r="W60" t="n">
@@ -12279,19 +12279,35 @@
         <v>20242025</v>
       </c>
       <c r="AA60" t="inlineStr"/>
-      <c r="AB60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
       <c r="AC60" t="inlineStr"/>
       <c r="AD60" t="inlineStr"/>
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr"/>
-      <c r="AI60" t="inlineStr"/>
-      <c r="AJ60" t="inlineStr"/>
-      <c r="AK60" t="inlineStr"/>
-      <c r="AL60" t="inlineStr"/>
-      <c r="AM60" t="inlineStr"/>
-      <c r="AN60" t="inlineStr"/>
+      <c r="AI60" t="n">
+        <v>25.45454545454545</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>183.9090909090909</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>73.27272727272727</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>5290909.090909091</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>76.90909090909091</v>
+      </c>
       <c r="AO60" t="inlineStr"/>
       <c r="AP60" t="inlineStr"/>
       <c r="AQ60" t="inlineStr"/>
@@ -12299,22 +12315,22 @@
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr"/>
       <c r="AU60" t="n">
-        <v>25.31578947368421</v>
+        <v>25.58823529411765</v>
       </c>
       <c r="AV60" t="n">
-        <v>178.7368421052632</v>
+        <v>183</v>
       </c>
       <c r="AW60" t="n">
-        <v>1</v>
+        <v>1.235294117647059</v>
       </c>
       <c r="AX60" t="n">
-        <v>66.68421052631579</v>
+        <v>71.29411764705883</v>
       </c>
       <c r="AY60" t="n">
-        <v>1192105.263157895</v>
+        <v>3352941.176470588</v>
       </c>
       <c r="AZ60" t="n">
-        <v>69.10526315789474</v>
+        <v>76.11764705882354</v>
       </c>
       <c r="BA60" t="inlineStr"/>
       <c r="BB60" t="inlineStr"/>
@@ -12334,7 +12350,7 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>06NAdG8N</t>
+          <t>Sff03OL7</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
@@ -12342,51 +12358,51 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">osmers h 
+          <t xml:space="preserve">alt p 
   ger </t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion der freundschaft
-  cottbus </t>
+          <t xml:space="preserve">bieberer berg stadion
+  offenbach am main </t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>22450</v>
+        <v>20500</v>
       </c>
       <c r="F61" t="n">
-        <v>20000</v>
+        <v>16847</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>6g44VD52</t>
+          <t>YJURlaIO</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>YFuz2RLm</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="N61" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="O61" t="n">
         <v>8</v>
       </c>
       <c r="P61" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Q61" t="n">
         <v>3</v>
@@ -12395,19 +12411,19 @@
         <v>9</v>
       </c>
       <c r="S61" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="T61" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>tnTvQd1l</t>
+          <t>GWkh67yH</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>4fuCGs9P</t>
+          <t>IgZoGKFn</t>
         </is>
       </c>
       <c r="W61" t="n">
@@ -12423,35 +12439,19 @@
         <v>20242025</v>
       </c>
       <c r="AA61" t="inlineStr"/>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
+      <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="inlineStr"/>
       <c r="AD61" t="inlineStr"/>
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
-      <c r="AI61" t="n">
-        <v>25.45454545454545</v>
-      </c>
-      <c r="AJ61" t="n">
-        <v>183.9090909090909</v>
-      </c>
-      <c r="AK61" t="n">
-        <v>1.181818181818182</v>
-      </c>
-      <c r="AL61" t="n">
-        <v>73.27272727272727</v>
-      </c>
-      <c r="AM61" t="n">
-        <v>5290909.090909091</v>
-      </c>
-      <c r="AN61" t="n">
-        <v>76.90909090909091</v>
-      </c>
+      <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
+      <c r="AL61" t="inlineStr"/>
+      <c r="AM61" t="inlineStr"/>
+      <c r="AN61" t="inlineStr"/>
       <c r="AO61" t="inlineStr"/>
       <c r="AP61" t="inlineStr"/>
       <c r="AQ61" t="inlineStr"/>
@@ -12459,22 +12459,22 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr"/>
       <c r="AU61" t="n">
-        <v>25.58823529411765</v>
+        <v>25.31578947368421</v>
       </c>
       <c r="AV61" t="n">
-        <v>183</v>
+        <v>178.7368421052632</v>
       </c>
       <c r="AW61" t="n">
-        <v>1.235294117647059</v>
+        <v>1</v>
       </c>
       <c r="AX61" t="n">
-        <v>71.29411764705883</v>
+        <v>66.68421052631579</v>
       </c>
       <c r="AY61" t="n">
-        <v>3352941.176470588</v>
+        <v>1192105.263157895</v>
       </c>
       <c r="AZ61" t="n">
-        <v>76.11764705882354</v>
+        <v>69.10526315789474</v>
       </c>
       <c r="BA61" t="inlineStr"/>
       <c r="BB61" t="inlineStr"/>
@@ -12654,7 +12654,7 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>dCPKovw8</t>
+          <t>vXAKoaf5</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
@@ -12662,72 +12662,72 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">stegemann s 
   ger </t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">hansch arena
-  meppen </t>
+          <t xml:space="preserve">rudolf harbig stadion
+  dresden </t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>13696</v>
+        <v>32249</v>
       </c>
       <c r="F63" t="n">
-        <v>12959</v>
+        <v>29660</v>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H63" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>rXqBh2xP</t>
+          <t>zL1YsOi1</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>v9k3aY5F</t>
+          <t>ne1oL3y7</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="N63" t="n">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="O63" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="P63" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q63" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R63" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="S63" t="n">
         <v>8</v>
       </c>
       <c r="T63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>UqphGQrg</t>
+          <t>4YhTfKrD</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>EDRZkDzS</t>
+          <t>AoL97rX8</t>
         </is>
       </c>
       <c r="W63" t="n">
@@ -12745,7 +12745,7 @@
       <c r="AA63" t="inlineStr"/>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>WG9pOTse</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr"/>
@@ -12755,46 +12755,58 @@
       <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr"/>
       <c r="AI63" t="n">
-        <v>25.22222222222222</v>
+        <v>25.36363636363636</v>
       </c>
       <c r="AJ63" t="n">
-        <v>182.5555555555555</v>
+        <v>183.8181818181818</v>
       </c>
       <c r="AK63" t="n">
         <v>1</v>
       </c>
       <c r="AL63" t="n">
-        <v>71.66666666666667</v>
+        <v>69.54545454545455</v>
       </c>
       <c r="AM63" t="n">
-        <v>2911111.111111111</v>
+        <v>2061363.636363636</v>
       </c>
       <c r="AN63" t="n">
-        <v>74.77777777777777</v>
-      </c>
-      <c r="AO63" t="inlineStr"/>
-      <c r="AP63" t="inlineStr"/>
-      <c r="AQ63" t="inlineStr"/>
-      <c r="AR63" t="inlineStr"/>
-      <c r="AS63" t="inlineStr"/>
-      <c r="AT63" t="inlineStr"/>
+        <v>73.36363636363636</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>26.28571428571428</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>180.1428571428571</v>
+      </c>
+      <c r="AQ63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR63" t="n">
+        <v>65.57142857142857</v>
+      </c>
+      <c r="AS63" t="n">
+        <v>853571.4285714285</v>
+      </c>
+      <c r="AT63" t="n">
+        <v>67.28571428571429</v>
+      </c>
       <c r="AU63" t="n">
-        <v>26.68421052631579</v>
+        <v>21.5</v>
       </c>
       <c r="AV63" t="n">
-        <v>186.6315789473684</v>
+        <v>186.95</v>
       </c>
       <c r="AW63" t="n">
         <v>1</v>
       </c>
       <c r="AX63" t="n">
-        <v>70.57894736842105</v>
+        <v>64.8</v>
       </c>
       <c r="AY63" t="n">
-        <v>2598947.368421053</v>
+        <v>1241250</v>
       </c>
       <c r="AZ63" t="n">
-        <v>72.63157894736842</v>
+        <v>75.45</v>
       </c>
       <c r="BA63" t="inlineStr"/>
       <c r="BB63" t="inlineStr"/>
@@ -12814,7 +12826,7 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>vXAKoaf5</t>
+          <t>dCPKovw8</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -12822,72 +12834,72 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">stegemann s 
+          <t xml:space="preserve">zwayer f 
   ger </t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">rudolf harbig stadion
-  dresden </t>
+          <t xml:space="preserve">hansch arena
+  meppen </t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>32249</v>
+        <v>13696</v>
       </c>
       <c r="F64" t="n">
-        <v>29660</v>
+        <v>12959</v>
       </c>
       <c r="G64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>zL1YsOi1</t>
+          <t>rXqBh2xP</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>ne1oL3y7</t>
+          <t>v9k3aY5F</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="N64" t="n">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="O64" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="P64" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Q64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R64" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="S64" t="n">
         <v>8</v>
       </c>
       <c r="T64" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>4YhTfKrD</t>
+          <t>UqphGQrg</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>AoL97rX8</t>
+          <t>EDRZkDzS</t>
         </is>
       </c>
       <c r="W64" t="n">
@@ -12905,7 +12917,7 @@
       <c r="AA64" t="inlineStr"/>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr"/>
@@ -12915,58 +12927,46 @@
       <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="inlineStr"/>
       <c r="AI64" t="n">
-        <v>25.36363636363636</v>
+        <v>25.22222222222222</v>
       </c>
       <c r="AJ64" t="n">
-        <v>183.8181818181818</v>
+        <v>182.5555555555555</v>
       </c>
       <c r="AK64" t="n">
         <v>1</v>
       </c>
       <c r="AL64" t="n">
-        <v>69.54545454545455</v>
+        <v>71.66666666666667</v>
       </c>
       <c r="AM64" t="n">
-        <v>2061363.636363636</v>
+        <v>2911111.111111111</v>
       </c>
       <c r="AN64" t="n">
-        <v>73.36363636363636</v>
-      </c>
-      <c r="AO64" t="n">
-        <v>26.28571428571428</v>
-      </c>
-      <c r="AP64" t="n">
-        <v>180.1428571428571</v>
-      </c>
-      <c r="AQ64" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR64" t="n">
-        <v>65.57142857142857</v>
-      </c>
-      <c r="AS64" t="n">
-        <v>853571.4285714285</v>
-      </c>
-      <c r="AT64" t="n">
-        <v>67.28571428571429</v>
-      </c>
+        <v>74.77777777777777</v>
+      </c>
+      <c r="AO64" t="inlineStr"/>
+      <c r="AP64" t="inlineStr"/>
+      <c r="AQ64" t="inlineStr"/>
+      <c r="AR64" t="inlineStr"/>
+      <c r="AS64" t="inlineStr"/>
+      <c r="AT64" t="inlineStr"/>
       <c r="AU64" t="n">
-        <v>21.5</v>
+        <v>26.68421052631579</v>
       </c>
       <c r="AV64" t="n">
-        <v>186.95</v>
+        <v>186.6315789473684</v>
       </c>
       <c r="AW64" t="n">
         <v>1</v>
       </c>
       <c r="AX64" t="n">
-        <v>64.8</v>
+        <v>70.57894736842105</v>
       </c>
       <c r="AY64" t="n">
-        <v>1241250</v>
+        <v>2598947.368421053</v>
       </c>
       <c r="AZ64" t="n">
-        <v>75.45</v>
+        <v>72.63157894736842</v>
       </c>
       <c r="BA64" t="inlineStr"/>
       <c r="BB64" t="inlineStr"/>
@@ -12986,7 +12986,7 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>l0ueP5rR</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
@@ -12994,72 +12994,72 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">schroder r 
+          <t xml:space="preserve">speckner m 
   ger </t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">ostseestadion
-  rostock </t>
+          <t xml:space="preserve">stadion am panzenberg
+  bremen </t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>29000</v>
+        <v>5000</v>
       </c>
       <c r="F65" t="n">
-        <v>25600</v>
+        <v>3500</v>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>KIHmtCkL</t>
+          <t>tW75B1ei</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2y0u8Wrq</t>
+          <t>G2Op923t</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N65" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O65" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P65" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Q65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R65" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S65" t="n">
+        <v>13</v>
+      </c>
+      <c r="T65" t="n">
         <v>17</v>
       </c>
-      <c r="T65" t="n">
-        <v>11</v>
-      </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>G8THUSaE</t>
+          <t>4tvZg2Br</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>YmfcAeCo</t>
+          <t>0AI1QUJH</t>
         </is>
       </c>
       <c r="W65" t="n">
@@ -13074,83 +13074,43 @@
       <c r="Z65" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
+      <c r="AA65" t="inlineStr"/>
       <c r="AB65" t="inlineStr"/>
-      <c r="AC65" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>183.875</v>
-      </c>
-      <c r="AE65" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="AG65" t="n">
-        <v>1040625</v>
-      </c>
-      <c r="AH65" t="n">
-        <v>69.125</v>
-      </c>
-      <c r="AI65" t="n">
-        <v>24.09090909090909</v>
-      </c>
-      <c r="AJ65" t="n">
-        <v>181.7272727272727</v>
-      </c>
-      <c r="AK65" t="n">
-        <v>1.181818181818182</v>
-      </c>
-      <c r="AL65" t="n">
-        <v>69.72727272727273</v>
-      </c>
-      <c r="AM65" t="n">
-        <v>2318181.818181818</v>
-      </c>
-      <c r="AN65" t="n">
-        <v>75.27272727272727</v>
-      </c>
-      <c r="AO65" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="AP65" t="n">
-        <v>181.6</v>
-      </c>
-      <c r="AQ65" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR65" t="n">
-        <v>64</v>
-      </c>
-      <c r="AS65" t="n">
-        <v>997500</v>
-      </c>
-      <c r="AT65" t="n">
-        <v>70.8</v>
-      </c>
+      <c r="AC65" t="inlineStr"/>
+      <c r="AD65" t="inlineStr"/>
+      <c r="AE65" t="inlineStr"/>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="inlineStr"/>
+      <c r="AH65" t="inlineStr"/>
+      <c r="AI65" t="inlineStr"/>
+      <c r="AJ65" t="inlineStr"/>
+      <c r="AK65" t="inlineStr"/>
+      <c r="AL65" t="inlineStr"/>
+      <c r="AM65" t="inlineStr"/>
+      <c r="AN65" t="inlineStr"/>
+      <c r="AO65" t="inlineStr"/>
+      <c r="AP65" t="inlineStr"/>
+      <c r="AQ65" t="inlineStr"/>
+      <c r="AR65" t="inlineStr"/>
+      <c r="AS65" t="inlineStr"/>
+      <c r="AT65" t="inlineStr"/>
       <c r="AU65" t="n">
-        <v>23.85</v>
+        <v>24.15789473684211</v>
       </c>
       <c r="AV65" t="n">
-        <v>185.55</v>
+        <v>186.3684210526316</v>
       </c>
       <c r="AW65" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AX65" t="n">
-        <v>68.7</v>
+        <v>66.89473684210526</v>
       </c>
       <c r="AY65" t="n">
-        <v>1963750</v>
+        <v>1414473.684210526</v>
       </c>
       <c r="AZ65" t="n">
-        <v>74.90000000000001</v>
+        <v>72.31578947368421</v>
       </c>
       <c r="BA65" t="inlineStr"/>
       <c r="BB65" t="inlineStr"/>
@@ -13170,7 +13130,7 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>KSwfVwAO</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -13178,72 +13138,72 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">lechner f 
+          <t xml:space="preserve">schroder r 
   ger </t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">millerntor stadion
-  hamburg </t>
+          <t xml:space="preserve">ostseestadion
+  rostock </t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>29546</v>
+        <v>29000</v>
       </c>
       <c r="F66" t="n">
-        <v>6487</v>
+        <v>25600</v>
       </c>
       <c r="G66" t="n">
         <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>WrbkcjCd</t>
+          <t>KIHmtCkL</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>S0hPB9rA</t>
+          <t>2y0u8Wrq</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="N66" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="O66" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P66" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q66" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R66" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S66" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="T66" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>lC9J1RTa</t>
+          <t>G8THUSaE</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>MDhPV0RQ</t>
+          <t>YmfcAeCo</t>
         </is>
       </c>
       <c r="W66" t="n">
@@ -13258,47 +13218,83 @@
       <c r="Z66" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA66" t="inlineStr"/>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr"/>
-      <c r="AD66" t="inlineStr"/>
-      <c r="AE66" t="inlineStr"/>
-      <c r="AF66" t="inlineStr"/>
-      <c r="AG66" t="inlineStr"/>
-      <c r="AH66" t="inlineStr"/>
-      <c r="AI66" t="inlineStr"/>
-      <c r="AJ66" t="inlineStr"/>
-      <c r="AK66" t="inlineStr"/>
-      <c r="AL66" t="inlineStr"/>
-      <c r="AM66" t="inlineStr"/>
-      <c r="AN66" t="inlineStr"/>
-      <c r="AO66" t="inlineStr"/>
-      <c r="AP66" t="inlineStr"/>
-      <c r="AQ66" t="inlineStr"/>
-      <c r="AR66" t="inlineStr"/>
-      <c r="AS66" t="inlineStr"/>
-      <c r="AT66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr"/>
+      <c r="AC66" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>183.875</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>1040625</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>69.125</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>24.09090909090909</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>181.7272727272727</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>69.72727272727273</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>2318181.818181818</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>75.27272727272727</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>64</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>997500</v>
+      </c>
+      <c r="AT66" t="n">
+        <v>70.8</v>
+      </c>
       <c r="AU66" t="n">
-        <v>26.23529411764706</v>
+        <v>23.85</v>
       </c>
       <c r="AV66" t="n">
-        <v>187.3529411764706</v>
+        <v>185.55</v>
       </c>
       <c r="AW66" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AX66" t="n">
-        <v>69.58823529411765</v>
+        <v>68.7</v>
       </c>
       <c r="AY66" t="n">
-        <v>1819117.647058824</v>
+        <v>1963750</v>
       </c>
       <c r="AZ66" t="n">
-        <v>73.41176470588235</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="BA66" t="inlineStr"/>
       <c r="BB66" t="inlineStr"/>
@@ -13318,7 +13314,7 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>tvOIPExA</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
@@ -13326,72 +13322,72 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">brand b 
+          <t xml:space="preserve">nouhoum a 
   ger </t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">hardtwaldstadion
-  sandhausen </t>
+          <t xml:space="preserve">friedrich ebert stadium
+  hildesheim </t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>15414</v>
+        <v>10000</v>
       </c>
       <c r="F67" t="n">
-        <v>9705</v>
+        <v>5186</v>
       </c>
       <c r="G67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>UZxEj1R4</t>
+          <t>E3xs5mIe</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
+          <t>6in2Eknb</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="n">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="N67" t="n">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="O67" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="P67" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q67" t="n">
+        <v>1</v>
+      </c>
+      <c r="R67" t="n">
+        <v>9</v>
+      </c>
+      <c r="S67" t="n">
+        <v>6</v>
+      </c>
+      <c r="T67" t="n">
         <v>7</v>
       </c>
-      <c r="R67" t="n">
-        <v>14</v>
-      </c>
-      <c r="S67" t="n">
-        <v>18</v>
-      </c>
-      <c r="T67" t="n">
-        <v>24</v>
-      </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>rZtwKVAL</t>
+          <t>bJ0lIKrp</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>4fX0k7gg</t>
+          <t>8E8qmw3d</t>
         </is>
       </c>
       <c r="W67" t="n">
@@ -13407,11 +13403,7 @@
         <v>20242025</v>
       </c>
       <c r="AA67" t="inlineStr"/>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>88HSzjDr</t>
-        </is>
-      </c>
+      <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="inlineStr"/>
       <c r="AD67" t="inlineStr"/>
       <c r="AE67" t="inlineStr"/>
@@ -13419,22 +13411,22 @@
       <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="inlineStr"/>
       <c r="AI67" t="n">
-        <v>22.7</v>
+        <v>24.1</v>
       </c>
       <c r="AJ67" t="n">
-        <v>184.6</v>
+        <v>184</v>
       </c>
       <c r="AK67" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AL67" t="n">
-        <v>70.40000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="AM67" t="n">
-        <v>3820000</v>
+        <v>1177500</v>
       </c>
       <c r="AN67" t="n">
-        <v>78.3</v>
+        <v>71.2</v>
       </c>
       <c r="AO67" t="inlineStr"/>
       <c r="AP67" t="inlineStr"/>
@@ -13443,22 +13435,22 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr"/>
       <c r="AU67" t="n">
-        <v>26.04761904761905</v>
+        <v>26.26315789473684</v>
       </c>
       <c r="AV67" t="n">
-        <v>187.5714285714286</v>
+        <v>181</v>
       </c>
       <c r="AW67" t="n">
-        <v>1.238095238095238</v>
+        <v>1</v>
       </c>
       <c r="AX67" t="n">
-        <v>68.42857142857143</v>
+        <v>65.78947368421052</v>
       </c>
       <c r="AY67" t="n">
-        <v>2287619.047619048</v>
+        <v>959210.5263157894</v>
       </c>
       <c r="AZ67" t="n">
-        <v>72.23809523809524</v>
+        <v>67.52631578947368</v>
       </c>
       <c r="BA67" t="inlineStr"/>
       <c r="BB67" t="inlineStr"/>
@@ -13638,7 +13630,7 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>t2AoZLAa</t>
+          <t>tvOIPExA</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
@@ -13646,72 +13638,72 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">nouhoum a 
+          <t xml:space="preserve">brand b 
   ger </t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">friedrich ebert stadium
-  hildesheim </t>
+          <t xml:space="preserve">hardtwaldstadion
+  sandhausen </t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>10000</v>
+        <v>15414</v>
       </c>
       <c r="F69" t="n">
-        <v>5186</v>
+        <v>9705</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H69" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>E3xs5mIe</t>
+          <t>UZxEj1R4</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>6in2Eknb</t>
+          <t>WG9pOTse</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="n">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="N69" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="O69" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="P69" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q69" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R69" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="S69" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="T69" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>bJ0lIKrp</t>
+          <t>rZtwKVAL</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>8E8qmw3d</t>
+          <t>4fX0k7gg</t>
         </is>
       </c>
       <c r="W69" t="n">
@@ -13727,7 +13719,11 @@
         <v>20242025</v>
       </c>
       <c r="AA69" t="inlineStr"/>
-      <c r="AB69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
       <c r="AC69" t="inlineStr"/>
       <c r="AD69" t="inlineStr"/>
       <c r="AE69" t="inlineStr"/>
@@ -13735,22 +13731,22 @@
       <c r="AG69" t="inlineStr"/>
       <c r="AH69" t="inlineStr"/>
       <c r="AI69" t="n">
-        <v>24.1</v>
+        <v>22.7</v>
       </c>
       <c r="AJ69" t="n">
-        <v>184</v>
+        <v>184.6</v>
       </c>
       <c r="AK69" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AL69" t="n">
-        <v>66.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AM69" t="n">
-        <v>1177500</v>
+        <v>3820000</v>
       </c>
       <c r="AN69" t="n">
-        <v>71.2</v>
+        <v>78.3</v>
       </c>
       <c r="AO69" t="inlineStr"/>
       <c r="AP69" t="inlineStr"/>
@@ -13759,22 +13755,22 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr"/>
       <c r="AU69" t="n">
-        <v>26.26315789473684</v>
+        <v>26.04761904761905</v>
       </c>
       <c r="AV69" t="n">
-        <v>181</v>
+        <v>187.5714285714286</v>
       </c>
       <c r="AW69" t="n">
-        <v>1</v>
+        <v>1.238095238095238</v>
       </c>
       <c r="AX69" t="n">
-        <v>65.78947368421052</v>
+        <v>68.42857142857143</v>
       </c>
       <c r="AY69" t="n">
-        <v>959210.5263157894</v>
+        <v>2287619.047619048</v>
       </c>
       <c r="AZ69" t="n">
-        <v>67.52631578947368</v>
+        <v>72.23809523809524</v>
       </c>
       <c r="BA69" t="inlineStr"/>
       <c r="BB69" t="inlineStr"/>
@@ -13794,7 +13790,7 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>YV3TqwPH</t>
+          <t>KSwfVwAO</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -13802,72 +13798,72 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">speckner m 
+          <t xml:space="preserve">lechner f 
   ger </t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion am panzenberg
-  bremen </t>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5000</v>
+        <v>29546</v>
       </c>
       <c r="F70" t="n">
-        <v>3500</v>
+        <v>6487</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>tW75B1ei</t>
+          <t>WrbkcjCd</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>G2Op923t</t>
+          <t>S0hPB9rA</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="N70" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="O70" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P70" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="Q70" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R70" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S70" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T70" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>4tvZg2Br</t>
+          <t>lC9J1RTa</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>0AI1QUJH</t>
+          <t>MDhPV0RQ</t>
         </is>
       </c>
       <c r="W70" t="n">
@@ -13883,7 +13879,11 @@
         <v>20242025</v>
       </c>
       <c r="AA70" t="inlineStr"/>
-      <c r="AB70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
       <c r="AC70" t="inlineStr"/>
       <c r="AD70" t="inlineStr"/>
       <c r="AE70" t="inlineStr"/>
@@ -13903,22 +13903,22 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr"/>
       <c r="AU70" t="n">
-        <v>24.15789473684211</v>
+        <v>26.23529411764706</v>
       </c>
       <c r="AV70" t="n">
-        <v>186.3684210526316</v>
+        <v>187.3529411764706</v>
       </c>
       <c r="AW70" t="n">
         <v>1</v>
       </c>
       <c r="AX70" t="n">
-        <v>66.89473684210526</v>
+        <v>69.58823529411765</v>
       </c>
       <c r="AY70" t="n">
-        <v>1414473.684210526</v>
+        <v>1819117.647058824</v>
       </c>
       <c r="AZ70" t="n">
-        <v>72.31578947368421</v>
+        <v>73.41176470588235</v>
       </c>
       <c r="BA70" t="inlineStr"/>
       <c r="BB70" t="inlineStr"/>
@@ -14460,7 +14460,7 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>CpiTEcOi</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -14468,51 +14468,51 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">bacher m 
+          <t xml:space="preserve">hartmann r 
   ger </t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">new tivoli
-  aachen </t>
+          <t xml:space="preserve">schuco arena
+  bielefeld </t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>31026</v>
+        <v>27332</v>
       </c>
       <c r="F74" t="n">
-        <v>29555</v>
+        <v>26044</v>
       </c>
       <c r="G74" t="n">
         <v>2</v>
       </c>
       <c r="H74" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>j3PKcB4E</t>
+          <t>pp38UXK8</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>dfNCCCzS</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="N74" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="O74" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P74" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q74" t="n">
         <v>6</v>
@@ -14521,19 +14521,19 @@
         <v>5</v>
       </c>
       <c r="S74" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="T74" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>SfKt2E6n</t>
+          <t>KrFXELrR</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>t0ZPdkUl</t>
         </is>
       </c>
       <c r="W74" t="n">
@@ -14551,7 +14551,7 @@
       <c r="AA74" t="inlineStr"/>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>QqLCC3il</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr"/>
@@ -14561,46 +14561,58 @@
       <c r="AG74" t="inlineStr"/>
       <c r="AH74" t="inlineStr"/>
       <c r="AI74" t="n">
-        <v>25</v>
+        <v>25.5</v>
       </c>
       <c r="AJ74" t="n">
-        <v>185.8</v>
+        <v>184</v>
       </c>
       <c r="AK74" t="n">
         <v>1.1</v>
       </c>
       <c r="AL74" t="n">
-        <v>68.5</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AM74" t="n">
-        <v>1760000</v>
+        <v>1932500</v>
       </c>
       <c r="AN74" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="AO74" t="inlineStr"/>
-      <c r="AP74" t="inlineStr"/>
-      <c r="AQ74" t="inlineStr"/>
-      <c r="AR74" t="inlineStr"/>
-      <c r="AS74" t="inlineStr"/>
-      <c r="AT74" t="inlineStr"/>
+        <v>72.8</v>
+      </c>
+      <c r="AO74" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="AP74" t="n">
+        <v>186.1428571428571</v>
+      </c>
+      <c r="AQ74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR74" t="n">
+        <v>65.28571428571429</v>
+      </c>
+      <c r="AS74" t="n">
+        <v>1321428.571428571</v>
+      </c>
+      <c r="AT74" t="n">
+        <v>72.28571428571429</v>
+      </c>
       <c r="AU74" t="n">
-        <v>24.4375</v>
+        <v>25.09523809523809</v>
       </c>
       <c r="AV74" t="n">
-        <v>186.3125</v>
+        <v>184.2857142857143</v>
       </c>
       <c r="AW74" t="n">
-        <v>1</v>
+        <v>1.047619047619048</v>
       </c>
       <c r="AX74" t="n">
-        <v>66.625</v>
+        <v>69.04761904761905</v>
       </c>
       <c r="AY74" t="n">
-        <v>1476562.5</v>
+        <v>1947619.047619048</v>
       </c>
       <c r="AZ74" t="n">
-        <v>71.375</v>
+        <v>72.95238095238095</v>
       </c>
       <c r="BA74" t="inlineStr"/>
       <c r="BB74" t="inlineStr"/>
@@ -14620,7 +14632,7 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>8CpxDyg4</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
@@ -14628,72 +14640,72 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">hartmann r 
+          <t xml:space="preserve">burda m 
   ger </t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">schuco arena
-  bielefeld </t>
+          <t xml:space="preserve">volksparkstadion
+  hamburg </t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>27332</v>
+        <v>57274</v>
       </c>
       <c r="F75" t="n">
-        <v>26044</v>
+        <v>50971</v>
       </c>
       <c r="G75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>pp38UXK8</t>
+          <t>I1Vk6k3R</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>dfNCCCzS</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="N75" t="n">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="O75" t="n">
+        <v>7</v>
+      </c>
+      <c r="P75" t="n">
         <v>12</v>
       </c>
-      <c r="P75" t="n">
-        <v>13</v>
-      </c>
       <c r="Q75" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R75" t="n">
+        <v>9</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="n">
         <v>5</v>
       </c>
-      <c r="S75" t="n">
-        <v>21</v>
-      </c>
-      <c r="T75" t="n">
-        <v>24</v>
-      </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>KrFXELrR</t>
+          <t>AgnJojCs</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>t0ZPdkUl</t>
+          <t>IkCftsQm</t>
         </is>
       </c>
       <c r="W75" t="n">
@@ -14711,7 +14723,7 @@
       <c r="AA75" t="inlineStr"/>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>QqLCC3il</t>
+          <t>0Ija0Ej9</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr"/>
@@ -14721,58 +14733,46 @@
       <c r="AG75" t="inlineStr"/>
       <c r="AH75" t="inlineStr"/>
       <c r="AI75" t="n">
-        <v>25.5</v>
+        <v>25.63636363636364</v>
       </c>
       <c r="AJ75" t="n">
-        <v>184</v>
+        <v>185.4545454545455</v>
       </c>
       <c r="AK75" t="n">
-        <v>1.1</v>
+        <v>2.454545454545455</v>
       </c>
       <c r="AL75" t="n">
-        <v>68.90000000000001</v>
+        <v>80.90909090909091</v>
       </c>
       <c r="AM75" t="n">
-        <v>1932500</v>
+        <v>33045454.54545455</v>
       </c>
       <c r="AN75" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="AO75" t="n">
-        <v>22.85714285714286</v>
-      </c>
-      <c r="AP75" t="n">
-        <v>186.1428571428571</v>
-      </c>
-      <c r="AQ75" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR75" t="n">
-        <v>65.28571428571429</v>
-      </c>
-      <c r="AS75" t="n">
-        <v>1321428.571428571</v>
-      </c>
-      <c r="AT75" t="n">
-        <v>72.28571428571429</v>
-      </c>
+        <v>83.63636363636364</v>
+      </c>
+      <c r="AO75" t="inlineStr"/>
+      <c r="AP75" t="inlineStr"/>
+      <c r="AQ75" t="inlineStr"/>
+      <c r="AR75" t="inlineStr"/>
+      <c r="AS75" t="inlineStr"/>
+      <c r="AT75" t="inlineStr"/>
       <c r="AU75" t="n">
-        <v>25.09523809523809</v>
+        <v>23.29166666666667</v>
       </c>
       <c r="AV75" t="n">
-        <v>184.2857142857143</v>
+        <v>181.75</v>
       </c>
       <c r="AW75" t="n">
-        <v>1.047619047619048</v>
+        <v>1.541666666666667</v>
       </c>
       <c r="AX75" t="n">
-        <v>69.04761904761905</v>
+        <v>76.95833333333333</v>
       </c>
       <c r="AY75" t="n">
-        <v>1947619.047619048</v>
+        <v>22458333.33333333</v>
       </c>
       <c r="AZ75" t="n">
-        <v>72.95238095238095</v>
+        <v>83.29166666666667</v>
       </c>
       <c r="BA75" t="inlineStr"/>
       <c r="BB75" t="inlineStr"/>
@@ -14792,7 +14792,7 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>hzyf0b9b</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -14800,72 +14800,72 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">burda m 
+          <t xml:space="preserve">bacher m 
   ger </t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">volksparkstadion
-  hamburg </t>
+          <t xml:space="preserve">new tivoli
+  aachen </t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>57274</v>
+        <v>31026</v>
       </c>
       <c r="F76" t="n">
-        <v>50971</v>
+        <v>29555</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>I1Vk6k3R</t>
+          <t>j3PKcB4E</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="N76" t="n">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="O76" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P76" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Q76" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R76" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T76" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>AgnJojCs</t>
+          <t>SfKt2E6n</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>IkCftsQm</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
       <c r="W76" t="n">
@@ -14883,7 +14883,7 @@
       <c r="AA76" t="inlineStr"/>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr"/>
@@ -14893,22 +14893,22 @@
       <c r="AG76" t="inlineStr"/>
       <c r="AH76" t="inlineStr"/>
       <c r="AI76" t="n">
-        <v>25.63636363636364</v>
+        <v>25</v>
       </c>
       <c r="AJ76" t="n">
-        <v>185.4545454545455</v>
+        <v>185.8</v>
       </c>
       <c r="AK76" t="n">
-        <v>2.454545454545455</v>
+        <v>1.1</v>
       </c>
       <c r="AL76" t="n">
-        <v>80.90909090909091</v>
+        <v>68.5</v>
       </c>
       <c r="AM76" t="n">
-        <v>33045454.54545455</v>
+        <v>1760000</v>
       </c>
       <c r="AN76" t="n">
-        <v>83.63636363636364</v>
+        <v>72.5</v>
       </c>
       <c r="AO76" t="inlineStr"/>
       <c r="AP76" t="inlineStr"/>
@@ -14917,22 +14917,22 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr"/>
       <c r="AU76" t="n">
-        <v>23.29166666666667</v>
+        <v>24.4375</v>
       </c>
       <c r="AV76" t="n">
-        <v>181.75</v>
+        <v>186.3125</v>
       </c>
       <c r="AW76" t="n">
-        <v>1.541666666666667</v>
+        <v>1</v>
       </c>
       <c r="AX76" t="n">
-        <v>76.95833333333333</v>
+        <v>66.625</v>
       </c>
       <c r="AY76" t="n">
-        <v>22458333.33333333</v>
+        <v>1476562.5</v>
       </c>
       <c r="AZ76" t="n">
-        <v>83.29166666666667</v>
+        <v>71.375</v>
       </c>
       <c r="BA76" t="inlineStr"/>
       <c r="BB76" t="inlineStr"/>
@@ -14952,7 +14952,7 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>8QPARz8c</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
@@ -14960,72 +14960,72 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">benen l 
+          <t xml:space="preserve">michel f 
   ger </t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">volksstadion greifswald
-  greifswald </t>
+          <t xml:space="preserve">ms technologie arena
+  villingen schwenningen </t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4990</v>
+        <v>8000</v>
       </c>
       <c r="F77" t="n">
-        <v>4990</v>
+        <v>6800</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Q1yNyI5t</t>
+          <t>lKLJUxeT</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="N77" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="O77" t="n">
         <v>6</v>
       </c>
       <c r="P77" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R77" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S77" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T77" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>Wbz1kusU</t>
+          <t>lli2SfLl</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>hpYJ6izc</t>
+          <t>4ljanukM</t>
         </is>
       </c>
       <c r="W77" t="n">
@@ -15049,22 +15049,22 @@
       <c r="AG77" t="inlineStr"/>
       <c r="AH77" t="inlineStr"/>
       <c r="AI77" t="n">
-        <v>27</v>
+        <v>26.25</v>
       </c>
       <c r="AJ77" t="n">
-        <v>185.5555555555555</v>
+        <v>188.25</v>
       </c>
       <c r="AK77" t="n">
-        <v>1.666666666666667</v>
+        <v>1</v>
       </c>
       <c r="AL77" t="n">
-        <v>75.44444444444444</v>
+        <v>72.125</v>
       </c>
       <c r="AM77" t="n">
-        <v>7833333.333333333</v>
+        <v>2837500</v>
       </c>
       <c r="AN77" t="n">
-        <v>77.22222222222223</v>
+        <v>74.125</v>
       </c>
       <c r="AO77" t="inlineStr"/>
       <c r="AP77" t="inlineStr"/>
@@ -15073,22 +15073,22 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr"/>
       <c r="AU77" t="n">
-        <v>25.69565217391304</v>
+        <v>25.66666666666667</v>
       </c>
       <c r="AV77" t="n">
-        <v>184.304347826087</v>
+        <v>187.1111111111111</v>
       </c>
       <c r="AW77" t="n">
-        <v>1.391304347826087</v>
+        <v>1</v>
       </c>
       <c r="AX77" t="n">
-        <v>71.65217391304348</v>
+        <v>69.77777777777777</v>
       </c>
       <c r="AY77" t="n">
-        <v>4054347.826086957</v>
+        <v>2063888.888888889</v>
       </c>
       <c r="AZ77" t="n">
-        <v>76.30434782608695</v>
+        <v>72.61111111111111</v>
       </c>
       <c r="BA77" t="inlineStr"/>
       <c r="BB77" t="inlineStr"/>
@@ -15108,7 +15108,7 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>bF2q76Mr</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -15116,72 +15116,72 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
+          <t xml:space="preserve">brych f 
   ger </t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion an der hafenstrasse
-  essen </t>
+          <t xml:space="preserve">ostalb arena
+  aalen </t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>20352</v>
+        <v>14500</v>
       </c>
       <c r="F78" t="n">
-        <v>17000</v>
+        <v>10850</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>EB0xsr77</t>
+          <t>Oh2C15j0</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>0Ija0Ej9</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="N78" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="O78" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R78" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S78" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="T78" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>0KMe4S4D</t>
+          <t>8bJFOfzK</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>pfoInmcq</t>
+          <t>txZLBQVC</t>
         </is>
       </c>
       <c r="W78" t="n">
@@ -15209,22 +15209,22 @@
       <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="inlineStr"/>
       <c r="AI78" t="n">
-        <v>25.45454545454545</v>
+        <v>24.5</v>
       </c>
       <c r="AJ78" t="n">
-        <v>182.2727272727273</v>
+        <v>186.625</v>
       </c>
       <c r="AK78" t="n">
-        <v>2.090909090909091</v>
+        <v>1</v>
       </c>
       <c r="AL78" t="n">
-        <v>79.81818181818181</v>
+        <v>68.625</v>
       </c>
       <c r="AM78" t="n">
-        <v>26636363.63636364</v>
+        <v>1825000</v>
       </c>
       <c r="AN78" t="n">
-        <v>83.36363636363636</v>
+        <v>72.5</v>
       </c>
       <c r="AO78" t="inlineStr"/>
       <c r="AP78" t="inlineStr"/>
@@ -15233,22 +15233,22 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr"/>
       <c r="AU78" t="n">
-        <v>23.875</v>
+        <v>25.28571428571428</v>
       </c>
       <c r="AV78" t="n">
-        <v>183.6875</v>
+        <v>188.5714285714286</v>
       </c>
       <c r="AW78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX78" t="n">
-        <v>77.3125</v>
+        <v>66.14285714285714</v>
       </c>
       <c r="AY78" t="n">
-        <v>21798437.5</v>
+        <v>1089285.714285714</v>
       </c>
       <c r="AZ78" t="n">
-        <v>81.5</v>
+        <v>70.28571428571429</v>
       </c>
       <c r="BA78" t="inlineStr"/>
       <c r="BB78" t="inlineStr"/>
@@ -15268,7 +15268,7 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
+          <t>vyk5gjdE</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
@@ -15276,72 +15276,72 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">michel f 
+          <t xml:space="preserve">benen l 
   ger </t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">ms technologie arena
-  villingen schwenningen </t>
+          <t xml:space="preserve">volksstadion greifswald
+  greifswald </t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>8000</v>
+        <v>4990</v>
       </c>
       <c r="F79" t="n">
-        <v>6800</v>
+        <v>4990</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>lKLJUxeT</t>
+          <t>Q1yNyI5t</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="N79" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="O79" t="n">
         <v>6</v>
       </c>
       <c r="P79" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Q79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R79" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="S79" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T79" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>lli2SfLl</t>
+          <t>Wbz1kusU</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>4ljanukM</t>
+          <t>hpYJ6izc</t>
         </is>
       </c>
       <c r="W79" t="n">
@@ -15365,22 +15365,22 @@
       <c r="AG79" t="inlineStr"/>
       <c r="AH79" t="inlineStr"/>
       <c r="AI79" t="n">
-        <v>26.25</v>
+        <v>27</v>
       </c>
       <c r="AJ79" t="n">
-        <v>188.25</v>
+        <v>185.5555555555555</v>
       </c>
       <c r="AK79" t="n">
-        <v>1</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AL79" t="n">
-        <v>72.125</v>
+        <v>75.44444444444444</v>
       </c>
       <c r="AM79" t="n">
-        <v>2837500</v>
+        <v>7833333.333333333</v>
       </c>
       <c r="AN79" t="n">
-        <v>74.125</v>
+        <v>77.22222222222223</v>
       </c>
       <c r="AO79" t="inlineStr"/>
       <c r="AP79" t="inlineStr"/>
@@ -15389,22 +15389,22 @@
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="inlineStr"/>
       <c r="AU79" t="n">
-        <v>25.66666666666667</v>
+        <v>25.69565217391304</v>
       </c>
       <c r="AV79" t="n">
-        <v>187.1111111111111</v>
+        <v>184.304347826087</v>
       </c>
       <c r="AW79" t="n">
-        <v>1</v>
+        <v>1.391304347826087</v>
       </c>
       <c r="AX79" t="n">
-        <v>69.77777777777777</v>
+        <v>71.65217391304348</v>
       </c>
       <c r="AY79" t="n">
-        <v>2063888.888888889</v>
+        <v>4054347.826086957</v>
       </c>
       <c r="AZ79" t="n">
-        <v>72.61111111111111</v>
+        <v>76.30434782608695</v>
       </c>
       <c r="BA79" t="inlineStr"/>
       <c r="BB79" t="inlineStr"/>
@@ -15580,7 +15580,7 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>MZjh9ghT</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
@@ -15588,72 +15588,72 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">reichel t 
+          <t xml:space="preserve">dingert c 
   ger </t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion an der bremer bruck
-  osnabruck </t>
+          <t xml:space="preserve">stadion an der hafenstrasse
+  essen </t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>16667</v>
+        <v>20352</v>
       </c>
       <c r="F81" t="n">
-        <v>15500</v>
+        <v>17000</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81" t="n">
         <v>4</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>88Xgj1Y5</t>
+          <t>EB0xsr77</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="N81" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="O81" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P81" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>2</v>
+      </c>
+      <c r="R81" t="n">
         <v>9</v>
       </c>
-      <c r="Q81" t="n">
-        <v>1</v>
-      </c>
-      <c r="R81" t="n">
-        <v>6</v>
-      </c>
       <c r="S81" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T81" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>lxrr7DgN</t>
+          <t>0KMe4S4D</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>YZPE6Sx7</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
       <c r="W81" t="n">
@@ -15671,7 +15671,7 @@
       <c r="AA81" t="inlineStr"/>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr"/>
@@ -15681,58 +15681,46 @@
       <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="inlineStr"/>
       <c r="AI81" t="n">
-        <v>25.88888888888889</v>
+        <v>25.45454545454545</v>
       </c>
       <c r="AJ81" t="n">
-        <v>183.3333333333333</v>
+        <v>182.2727272727273</v>
       </c>
       <c r="AK81" t="n">
-        <v>1.777777777777778</v>
+        <v>2.090909090909091</v>
       </c>
       <c r="AL81" t="n">
-        <v>75.11111111111111</v>
+        <v>79.81818181818181</v>
       </c>
       <c r="AM81" t="n">
-        <v>10033333.33333333</v>
+        <v>26636363.63636364</v>
       </c>
       <c r="AN81" t="n">
-        <v>77.44444444444444</v>
-      </c>
-      <c r="AO81" t="n">
-        <v>22.58333333333333</v>
-      </c>
-      <c r="AP81" t="n">
-        <v>186.0833333333333</v>
-      </c>
-      <c r="AQ81" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR81" t="n">
-        <v>63.08333333333334</v>
-      </c>
-      <c r="AS81" t="n">
-        <v>862500</v>
-      </c>
-      <c r="AT81" t="n">
-        <v>71.5</v>
-      </c>
+        <v>83.36363636363636</v>
+      </c>
+      <c r="AO81" t="inlineStr"/>
+      <c r="AP81" t="inlineStr"/>
+      <c r="AQ81" t="inlineStr"/>
+      <c r="AR81" t="inlineStr"/>
+      <c r="AS81" t="inlineStr"/>
+      <c r="AT81" t="inlineStr"/>
       <c r="AU81" t="n">
-        <v>26.95652173913043</v>
+        <v>23.875</v>
       </c>
       <c r="AV81" t="n">
-        <v>182.1304347826087</v>
+        <v>183.6875</v>
       </c>
       <c r="AW81" t="n">
-        <v>1.608695652173913</v>
+        <v>2</v>
       </c>
       <c r="AX81" t="n">
-        <v>74.08695652173913</v>
+        <v>77.3125</v>
       </c>
       <c r="AY81" t="n">
-        <v>6278260.869565218</v>
+        <v>21798437.5</v>
       </c>
       <c r="AZ81" t="n">
-        <v>76.04347826086956</v>
+        <v>81.5</v>
       </c>
       <c r="BA81" t="inlineStr"/>
       <c r="BB81" t="inlineStr"/>
@@ -15752,7 +15740,7 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>f1nnRRDE</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -15760,72 +15748,72 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">brych f 
+          <t xml:space="preserve">reichel t 
   ger </t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">ostalb arena
-  aalen </t>
+          <t xml:space="preserve">stadion an der bremer bruck
+  osnabruck </t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>14500</v>
+        <v>16667</v>
       </c>
       <c r="F82" t="n">
-        <v>10850</v>
+        <v>15500</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Oh2C15j0</t>
+          <t>88Xgj1Y5</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="N82" t="n">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O82" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P82" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Q82" t="n">
         <v>1</v>
       </c>
       <c r="R82" t="n">
+        <v>6</v>
+      </c>
+      <c r="S82" t="n">
+        <v>6</v>
+      </c>
+      <c r="T82" t="n">
         <v>8</v>
       </c>
-      <c r="S82" t="n">
-        <v>17</v>
-      </c>
-      <c r="T82" t="n">
-        <v>16</v>
-      </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>8bJFOfzK</t>
+          <t>lxrr7DgN</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>txZLBQVC</t>
+          <t>YZPE6Sx7</t>
         </is>
       </c>
       <c r="W82" t="n">
@@ -15843,7 +15831,7 @@
       <c r="AA82" t="inlineStr"/>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr"/>
@@ -15853,46 +15841,58 @@
       <c r="AG82" t="inlineStr"/>
       <c r="AH82" t="inlineStr"/>
       <c r="AI82" t="n">
-        <v>24.5</v>
+        <v>25.88888888888889</v>
       </c>
       <c r="AJ82" t="n">
-        <v>186.625</v>
+        <v>183.3333333333333</v>
       </c>
       <c r="AK82" t="n">
-        <v>1</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="AL82" t="n">
-        <v>68.625</v>
+        <v>75.11111111111111</v>
       </c>
       <c r="AM82" t="n">
-        <v>1825000</v>
+        <v>10033333.33333333</v>
       </c>
       <c r="AN82" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="AO82" t="inlineStr"/>
-      <c r="AP82" t="inlineStr"/>
-      <c r="AQ82" t="inlineStr"/>
-      <c r="AR82" t="inlineStr"/>
-      <c r="AS82" t="inlineStr"/>
-      <c r="AT82" t="inlineStr"/>
+        <v>77.44444444444444</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>22.58333333333333</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>186.0833333333333</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>63.08333333333334</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>862500</v>
+      </c>
+      <c r="AT82" t="n">
+        <v>71.5</v>
+      </c>
       <c r="AU82" t="n">
-        <v>25.28571428571428</v>
+        <v>26.95652173913043</v>
       </c>
       <c r="AV82" t="n">
-        <v>188.5714285714286</v>
+        <v>182.1304347826087</v>
       </c>
       <c r="AW82" t="n">
-        <v>1</v>
+        <v>1.608695652173913</v>
       </c>
       <c r="AX82" t="n">
-        <v>66.14285714285714</v>
+        <v>74.08695652173913</v>
       </c>
       <c r="AY82" t="n">
-        <v>1089285.714285714</v>
+        <v>6278260.869565218</v>
       </c>
       <c r="AZ82" t="n">
-        <v>70.28571428571429</v>
+        <v>76.04347826086956</v>
       </c>
       <c r="BA82" t="inlineStr"/>
       <c r="BB82" t="inlineStr"/>
@@ -15912,7 +15912,7 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
+          <t>Kj4sifWp</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
@@ -15920,72 +15920,72 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">badstubner f 
+          <t xml:space="preserve">prigan f 
   ger </t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">erzgebirgsstadion
-  aue </t>
+          <t xml:space="preserve">bruchwegstadion
+  mainz </t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>16485</v>
+        <v>7134</v>
       </c>
       <c r="F83" t="n">
-        <v>14811</v>
+        <v>4235</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>vsXIDreP</t>
+          <t>WzEYqEyg</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>CCQGbik8</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="n">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="N83" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="O83" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P83" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="Q83" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="S83" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T83" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>rPfNaCdg</t>
+          <t>pvucOaW7</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>8E86CPuD</t>
         </is>
       </c>
       <c r="W83" t="n">
@@ -16003,7 +16003,7 @@
       <c r="AA83" t="inlineStr"/>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
+          <t>6FDqshzF</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr"/>
@@ -16013,22 +16013,22 @@
       <c r="AG83" t="inlineStr"/>
       <c r="AH83" t="inlineStr"/>
       <c r="AI83" t="n">
-        <v>24.81818181818182</v>
+        <v>25</v>
       </c>
       <c r="AJ83" t="n">
-        <v>183.7272727272727</v>
+        <v>183.3</v>
       </c>
       <c r="AK83" t="n">
-        <v>1.545454545454545</v>
+        <v>1</v>
       </c>
       <c r="AL83" t="n">
-        <v>75.27272727272727</v>
+        <v>67.5</v>
       </c>
       <c r="AM83" t="n">
-        <v>9627272.727272727</v>
+        <v>1605000</v>
       </c>
       <c r="AN83" t="n">
-        <v>79</v>
+        <v>71.8</v>
       </c>
       <c r="AO83" t="inlineStr"/>
       <c r="AP83" t="inlineStr"/>
@@ -16037,22 +16037,22 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr"/>
       <c r="AU83" t="n">
-        <v>24.43478260869565</v>
+        <v>22.60869565217391</v>
       </c>
       <c r="AV83" t="n">
-        <v>184.3913043478261</v>
+        <v>183.2173913043478</v>
       </c>
       <c r="AW83" t="n">
-        <v>1.347826086956522</v>
+        <v>1</v>
       </c>
       <c r="AX83" t="n">
-        <v>73.47826086956522</v>
+        <v>64.08695652173913</v>
       </c>
       <c r="AY83" t="n">
-        <v>7100000</v>
+        <v>1201086.956521739</v>
       </c>
       <c r="AZ83" t="n">
-        <v>77.95652173913044</v>
+        <v>72.73913043478261</v>
       </c>
       <c r="BA83" t="inlineStr"/>
       <c r="BB83" t="inlineStr"/>
@@ -16072,7 +16072,7 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
+          <t>0K2qBFNG</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -16080,72 +16080,72 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">prigan f 
+          <t xml:space="preserve">badstubner f 
   ger </t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">bruchwegstadion
-  mainz </t>
+          <t xml:space="preserve">erzgebirgsstadion
+  aue </t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>7134</v>
+        <v>16485</v>
       </c>
       <c r="F84" t="n">
-        <v>4235</v>
+        <v>14811</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>WzEYqEyg</t>
+          <t>vsXIDreP</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>CCQGbik8</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="N84" t="n">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="O84" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P84" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R84" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T84" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>pvucOaW7</t>
+          <t>rPfNaCdg</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>8E86CPuD</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
       <c r="W84" t="n">
@@ -16163,7 +16163,7 @@
       <c r="AA84" t="inlineStr"/>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>6FDqshzF</t>
+          <t>WG9pOTse</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr"/>
@@ -16173,22 +16173,22 @@
       <c r="AG84" t="inlineStr"/>
       <c r="AH84" t="inlineStr"/>
       <c r="AI84" t="n">
-        <v>25</v>
+        <v>24.81818181818182</v>
       </c>
       <c r="AJ84" t="n">
-        <v>183.3</v>
+        <v>183.7272727272727</v>
       </c>
       <c r="AK84" t="n">
-        <v>1</v>
+        <v>1.545454545454545</v>
       </c>
       <c r="AL84" t="n">
-        <v>67.5</v>
+        <v>75.27272727272727</v>
       </c>
       <c r="AM84" t="n">
-        <v>1605000</v>
+        <v>9627272.727272727</v>
       </c>
       <c r="AN84" t="n">
-        <v>71.8</v>
+        <v>79</v>
       </c>
       <c r="AO84" t="inlineStr"/>
       <c r="AP84" t="inlineStr"/>
@@ -16197,22 +16197,22 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr"/>
       <c r="AU84" t="n">
-        <v>22.60869565217391</v>
+        <v>24.43478260869565</v>
       </c>
       <c r="AV84" t="n">
-        <v>183.2173913043478</v>
+        <v>184.3913043478261</v>
       </c>
       <c r="AW84" t="n">
-        <v>1</v>
+        <v>1.347826086956522</v>
       </c>
       <c r="AX84" t="n">
-        <v>64.08695652173913</v>
+        <v>73.47826086956522</v>
       </c>
       <c r="AY84" t="n">
-        <v>1201086.956521739</v>
+        <v>7100000</v>
       </c>
       <c r="AZ84" t="n">
-        <v>72.73913043478261</v>
+        <v>77.95652173913044</v>
       </c>
       <c r="BA84" t="inlineStr"/>
       <c r="BB84" t="inlineStr"/>
@@ -16388,7 +16388,7 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>EF8gXauC</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -16396,21 +16396,21 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">siebert d 
+          <t xml:space="preserve">petersen m 
   ger </t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">leuna chemie stadion
-  halle </t>
+          <t xml:space="preserve">flyeralarm arena
+  wurzburger </t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>15057</v>
+        <v>13090</v>
       </c>
       <c r="F86" t="n">
-        <v>14000</v>
+        <v>12000</v>
       </c>
       <c r="G86" t="n">
         <v>2</v>
@@ -16420,48 +16420,48 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>boX3cIQa</t>
+          <t>nVM1YUFj</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="N86" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="O86" t="n">
         <v>9</v>
       </c>
       <c r="P86" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R86" t="n">
         <v>8</v>
       </c>
       <c r="S86" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T86" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>02hM7hzd</t>
+          <t>lEwgk7go</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>0jdIgO6t</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
       <c r="W86" t="n">
@@ -16479,7 +16479,7 @@
       <c r="AA86" t="inlineStr"/>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>v9k3aY5F</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr"/>
@@ -16489,22 +16489,22 @@
       <c r="AG86" t="inlineStr"/>
       <c r="AH86" t="inlineStr"/>
       <c r="AI86" t="n">
-        <v>25.6</v>
+        <v>26.4</v>
       </c>
       <c r="AJ86" t="n">
-        <v>186.1</v>
+        <v>186.8</v>
       </c>
       <c r="AK86" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="AL86" t="n">
-        <v>70.5</v>
+        <v>73.2</v>
       </c>
       <c r="AM86" t="n">
-        <v>2460000</v>
+        <v>7325000</v>
       </c>
       <c r="AN86" t="n">
-        <v>74</v>
+        <v>76.7</v>
       </c>
       <c r="AO86" t="inlineStr"/>
       <c r="AP86" t="inlineStr"/>
@@ -16513,22 +16513,22 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr"/>
       <c r="AU86" t="n">
-        <v>24</v>
+        <v>23.94444444444444</v>
       </c>
       <c r="AV86" t="n">
-        <v>184.2105263157895</v>
+        <v>184.3333333333333</v>
       </c>
       <c r="AW86" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AX86" t="n">
-        <v>68.63157894736842</v>
+        <v>72.11111111111111</v>
       </c>
       <c r="AY86" t="n">
-        <v>2057894.736842105</v>
+        <v>7190277.777777778</v>
       </c>
       <c r="AZ86" t="n">
-        <v>73.47368421052632</v>
+        <v>78.38888888888889</v>
       </c>
       <c r="BA86" t="inlineStr"/>
       <c r="BB86" t="inlineStr"/>
@@ -16724,7 +16724,7 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
+          <t>pWQQJq6l</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -16732,21 +16732,21 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">petersen m 
+          <t xml:space="preserve">siebert d 
   ger </t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">flyeralarm arena
-  wurzburger </t>
+          <t xml:space="preserve">leuna chemie stadion
+  halle </t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>13090</v>
+        <v>15057</v>
       </c>
       <c r="F88" t="n">
-        <v>12000</v>
+        <v>14000</v>
       </c>
       <c r="G88" t="n">
         <v>2</v>
@@ -16756,48 +16756,48 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>nVM1YUFj</t>
+          <t>boX3cIQa</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="N88" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="O88" t="n">
         <v>9</v>
       </c>
       <c r="P88" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R88" t="n">
         <v>8</v>
       </c>
       <c r="S88" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T88" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>lEwgk7go</t>
+          <t>02hM7hzd</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>KUx4Q7x1</t>
+          <t>0jdIgO6t</t>
         </is>
       </c>
       <c r="W88" t="n">
@@ -16815,7 +16815,7 @@
       <c r="AA88" t="inlineStr"/>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>v9k3aY5F</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr"/>
@@ -16825,22 +16825,22 @@
       <c r="AG88" t="inlineStr"/>
       <c r="AH88" t="inlineStr"/>
       <c r="AI88" t="n">
-        <v>26.4</v>
+        <v>25.6</v>
       </c>
       <c r="AJ88" t="n">
-        <v>186.8</v>
+        <v>186.1</v>
       </c>
       <c r="AK88" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="AL88" t="n">
-        <v>73.2</v>
+        <v>70.5</v>
       </c>
       <c r="AM88" t="n">
-        <v>7325000</v>
+        <v>2460000</v>
       </c>
       <c r="AN88" t="n">
-        <v>76.7</v>
+        <v>74</v>
       </c>
       <c r="AO88" t="inlineStr"/>
       <c r="AP88" t="inlineStr"/>
@@ -16849,22 +16849,22 @@
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr"/>
       <c r="AU88" t="n">
-        <v>23.94444444444444</v>
+        <v>24</v>
       </c>
       <c r="AV88" t="n">
-        <v>184.3333333333333</v>
+        <v>184.2105263157895</v>
       </c>
       <c r="AW88" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AX88" t="n">
-        <v>72.11111111111111</v>
+        <v>68.63157894736842</v>
       </c>
       <c r="AY88" t="n">
-        <v>7190277.777777778</v>
+        <v>2057894.736842105</v>
       </c>
       <c r="AZ88" t="n">
-        <v>78.38888888888889</v>
+        <v>73.47368421052632</v>
       </c>
       <c r="BA88" t="inlineStr"/>
       <c r="BB88" t="inlineStr"/>
@@ -17600,7 +17600,7 @@
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>YJ3eN30K</t>
+          <t>tC1Aa08D</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
@@ -17608,76 +17608,76 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">winter n 
+          <t xml:space="preserve">bauer t 
   ger </t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">max morlock stadion
-  nuremberg </t>
+          <t xml:space="preserve">waldstadion kaiserlinde
+  spiesen elversberg </t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>50000</v>
+        <v>9970</v>
       </c>
       <c r="F93" t="n">
-        <v>50000</v>
+        <v>9502</v>
       </c>
       <c r="G93" t="n">
+        <v>2</v>
+      </c>
+      <c r="H93" t="n">
+        <v>2</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="L93" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="M93" t="n">
+        <v>45</v>
+      </c>
+      <c r="N93" t="n">
+        <v>55</v>
+      </c>
+      <c r="O93" t="n">
+        <v>10</v>
+      </c>
+      <c r="P93" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q93" t="n">
         <v>3</v>
       </c>
-      <c r="H93" t="n">
-        <v>1</v>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>6FDqshzF</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>0Ija0Ej9</t>
-        </is>
-      </c>
-      <c r="K93" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="L93" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="M93" t="n">
-        <v>51</v>
-      </c>
-      <c r="N93" t="n">
-        <v>49</v>
-      </c>
-      <c r="O93" t="n">
-        <v>8</v>
-      </c>
-      <c r="P93" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>5</v>
-      </c>
       <c r="R93" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S93" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T93" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>tO31cZrF</t>
+          <t>8E8qmw3d</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>txZLBQVC</t>
+          <t>4fX0k7gg</t>
         </is>
       </c>
       <c r="W93" t="n">
@@ -17692,87 +17692,83 @@
       <c r="Z93" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>CCQGbik8</t>
-        </is>
-      </c>
+      <c r="AA93" t="inlineStr"/>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="AC93" t="n">
-        <v>22.77777777777778</v>
+        <v>24.9</v>
       </c>
       <c r="AD93" t="n">
-        <v>182</v>
+        <v>182.3</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.111111111111111</v>
+        <v>1</v>
       </c>
       <c r="AF93" t="n">
-        <v>66</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AG93" t="n">
-        <v>1697222.222222222</v>
+        <v>1200000</v>
       </c>
       <c r="AH93" t="n">
-        <v>72.55555555555556</v>
+        <v>70.5</v>
       </c>
       <c r="AI93" t="n">
-        <v>25.33333333333333</v>
+        <v>23</v>
       </c>
       <c r="AJ93" t="n">
-        <v>188.7777777777778</v>
+        <v>185.4545454545455</v>
       </c>
       <c r="AK93" t="n">
-        <v>1</v>
+        <v>1.181818181818182</v>
       </c>
       <c r="AL93" t="n">
-        <v>67.66666666666667</v>
+        <v>71.27272727272727</v>
       </c>
       <c r="AM93" t="n">
-        <v>1580555.555555556</v>
+        <v>4545454.545454546</v>
       </c>
       <c r="AN93" t="n">
-        <v>71.77777777777777</v>
+        <v>78.63636363636364</v>
       </c>
       <c r="AO93" t="n">
-        <v>28.125</v>
+        <v>25.30769230769231</v>
       </c>
       <c r="AP93" t="n">
-        <v>180</v>
+        <v>182.3076923076923</v>
       </c>
       <c r="AQ93" t="n">
         <v>1</v>
       </c>
       <c r="AR93" t="n">
-        <v>67.875</v>
+        <v>65.23076923076923</v>
       </c>
       <c r="AS93" t="n">
-        <v>1209375</v>
+        <v>975000</v>
       </c>
       <c r="AT93" t="n">
-        <v>70</v>
+        <v>69.07692307692308</v>
       </c>
       <c r="AU93" t="n">
-        <v>25.625</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="AV93" t="n">
-        <v>186.125</v>
+        <v>186.5714285714286</v>
       </c>
       <c r="AW93" t="n">
-        <v>1</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="AX93" t="n">
-        <v>68.125</v>
+        <v>69.47619047619048</v>
       </c>
       <c r="AY93" t="n">
-        <v>1425000</v>
+        <v>2787619.047619048</v>
       </c>
       <c r="AZ93" t="n">
-        <v>71</v>
+        <v>73.19047619047619</v>
       </c>
       <c r="BA93" t="inlineStr"/>
       <c r="BB93" t="inlineStr"/>
@@ -17792,7 +17788,7 @@
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>IViLLjPF</t>
+          <t>YJ3eN30K</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -17800,76 +17796,76 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">hartmann r 
+          <t xml:space="preserve">winter n 
   ger </t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">merkur spiel arena
-  dusseldorf </t>
+          <t xml:space="preserve">max morlock stadion
+  nuremberg </t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>54600</v>
+        <v>50000</v>
       </c>
       <c r="F94" t="n">
-        <v>36103</v>
+        <v>50000</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>ne1oL3y7</t>
+          <t>6FDqshzF</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>EB3q7jbk</t>
+          <t>0Ija0Ej9</t>
         </is>
       </c>
       <c r="K94" t="n">
-        <v>1.09</v>
+        <v>0.93</v>
       </c>
       <c r="L94" t="n">
-        <v>0.66</v>
+        <v>2.12</v>
       </c>
       <c r="M94" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N94" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O94" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="P94" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="Q94" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R94" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S94" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T94" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>AoL97rX8</t>
+          <t>tO31cZrF</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>OzPMRhK3</t>
+          <t>txZLBQVC</t>
         </is>
       </c>
       <c r="W94" t="n">
@@ -17886,85 +17882,85 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
+          <t>CCQGbik8</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>naWckLmC</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="AC94" t="n">
-        <v>25.63636363636364</v>
+        <v>22.77777777777778</v>
       </c>
       <c r="AD94" t="n">
-        <v>182.7272727272727</v>
+        <v>182</v>
       </c>
       <c r="AE94" t="n">
-        <v>1</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AF94" t="n">
+        <v>66</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>1697222.222222222</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>72.55555555555556</v>
+      </c>
+      <c r="AI94" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="AJ94" t="n">
+        <v>188.7777777777778</v>
+      </c>
+      <c r="AK94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL94" t="n">
+        <v>67.66666666666667</v>
+      </c>
+      <c r="AM94" t="n">
+        <v>1580555.555555556</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>71.77777777777777</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>28.125</v>
+      </c>
+      <c r="AP94" t="n">
+        <v>180</v>
+      </c>
+      <c r="AQ94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR94" t="n">
+        <v>67.875</v>
+      </c>
+      <c r="AS94" t="n">
+        <v>1209375</v>
+      </c>
+      <c r="AT94" t="n">
         <v>70</v>
       </c>
-      <c r="AG94" t="n">
-        <v>2334090.909090909</v>
-      </c>
-      <c r="AH94" t="n">
-        <v>73.90909090909091</v>
-      </c>
-      <c r="AI94" t="n">
-        <v>26.27272727272727</v>
-      </c>
-      <c r="AJ94" t="n">
-        <v>184.3636363636364</v>
-      </c>
-      <c r="AK94" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL94" t="n">
-        <v>67.81818181818181</v>
-      </c>
-      <c r="AM94" t="n">
-        <v>1395454.545454545</v>
-      </c>
-      <c r="AN94" t="n">
-        <v>71.90909090909091</v>
-      </c>
-      <c r="AO94" t="n">
-        <v>22.69230769230769</v>
-      </c>
-      <c r="AP94" t="n">
-        <v>186.3846153846154</v>
-      </c>
-      <c r="AQ94" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR94" t="n">
-        <v>66</v>
-      </c>
-      <c r="AS94" t="n">
-        <v>1753846.153846154</v>
-      </c>
-      <c r="AT94" t="n">
-        <v>73.53846153846153</v>
-      </c>
       <c r="AU94" t="n">
-        <v>23.3125</v>
+        <v>25.625</v>
       </c>
       <c r="AV94" t="n">
-        <v>181</v>
+        <v>186.125</v>
       </c>
       <c r="AW94" t="n">
         <v>1</v>
       </c>
       <c r="AX94" t="n">
-        <v>65.25</v>
+        <v>68.125</v>
       </c>
       <c r="AY94" t="n">
-        <v>1126250</v>
+        <v>1425000</v>
       </c>
       <c r="AZ94" t="n">
-        <v>72.5625</v>
+        <v>71</v>
       </c>
       <c r="BA94" t="inlineStr"/>
       <c r="BB94" t="inlineStr"/>
@@ -17984,7 +17980,7 @@
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>tC1Aa08D</t>
+          <t>IViLLjPF</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
@@ -17992,76 +17988,76 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">bauer t 
+          <t xml:space="preserve">hartmann r 
   ger </t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">waldstadion kaiserlinde
-  spiesen elversberg </t>
+          <t xml:space="preserve">merkur spiel arena
+  dusseldorf </t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>9970</v>
+        <v>54600</v>
       </c>
       <c r="F95" t="n">
-        <v>9502</v>
+        <v>36103</v>
       </c>
       <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>ne1oL3y7</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>EB3q7jbk</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M95" t="n">
+        <v>53</v>
+      </c>
+      <c r="N95" t="n">
+        <v>47</v>
+      </c>
+      <c r="O95" t="n">
+        <v>20</v>
+      </c>
+      <c r="P95" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>6</v>
+      </c>
+      <c r="R95" t="n">
         <v>2</v>
       </c>
-      <c r="H95" t="n">
-        <v>2</v>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>6in2Eknb</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="K95" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="L95" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="M95" t="n">
-        <v>45</v>
-      </c>
-      <c r="N95" t="n">
-        <v>55</v>
-      </c>
-      <c r="O95" t="n">
-        <v>10</v>
-      </c>
-      <c r="P95" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>3</v>
-      </c>
-      <c r="R95" t="n">
-        <v>9</v>
-      </c>
       <c r="S95" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T95" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>8E8qmw3d</t>
+          <t>AoL97rX8</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>4fX0k7gg</t>
+          <t>OzPMRhK3</t>
         </is>
       </c>
       <c r="W95" t="n">
@@ -18076,83 +18072,87 @@
       <c r="Z95" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA95" t="inlineStr"/>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>naWckLmC</t>
         </is>
       </c>
       <c r="AC95" t="n">
-        <v>24.9</v>
+        <v>25.63636363636364</v>
       </c>
       <c r="AD95" t="n">
-        <v>182.3</v>
+        <v>182.7272727272727</v>
       </c>
       <c r="AE95" t="n">
         <v>1</v>
       </c>
       <c r="AF95" t="n">
-        <v>66.90000000000001</v>
+        <v>70</v>
       </c>
       <c r="AG95" t="n">
-        <v>1200000</v>
+        <v>2334090.909090909</v>
       </c>
       <c r="AH95" t="n">
-        <v>70.5</v>
+        <v>73.90909090909091</v>
       </c>
       <c r="AI95" t="n">
-        <v>23</v>
+        <v>26.27272727272727</v>
       </c>
       <c r="AJ95" t="n">
-        <v>185.4545454545455</v>
+        <v>184.3636363636364</v>
       </c>
       <c r="AK95" t="n">
-        <v>1.181818181818182</v>
+        <v>1</v>
       </c>
       <c r="AL95" t="n">
-        <v>71.27272727272727</v>
+        <v>67.81818181818181</v>
       </c>
       <c r="AM95" t="n">
-        <v>4545454.545454546</v>
+        <v>1395454.545454545</v>
       </c>
       <c r="AN95" t="n">
-        <v>78.63636363636364</v>
+        <v>71.90909090909091</v>
       </c>
       <c r="AO95" t="n">
-        <v>25.30769230769231</v>
+        <v>22.69230769230769</v>
       </c>
       <c r="AP95" t="n">
-        <v>182.3076923076923</v>
+        <v>186.3846153846154</v>
       </c>
       <c r="AQ95" t="n">
         <v>1</v>
       </c>
       <c r="AR95" t="n">
-        <v>65.23076923076923</v>
+        <v>66</v>
       </c>
       <c r="AS95" t="n">
-        <v>975000</v>
+        <v>1753846.153846154</v>
       </c>
       <c r="AT95" t="n">
-        <v>69.07692307692308</v>
+        <v>73.53846153846153</v>
       </c>
       <c r="AU95" t="n">
-        <v>26.33333333333333</v>
+        <v>23.3125</v>
       </c>
       <c r="AV95" t="n">
-        <v>186.5714285714286</v>
+        <v>181</v>
       </c>
       <c r="AW95" t="n">
-        <v>1.380952380952381</v>
+        <v>1</v>
       </c>
       <c r="AX95" t="n">
-        <v>69.47619047619048</v>
+        <v>65.25</v>
       </c>
       <c r="AY95" t="n">
-        <v>2787619.047619048</v>
+        <v>1126250</v>
       </c>
       <c r="AZ95" t="n">
-        <v>73.19047619047619</v>
+        <v>72.5625</v>
       </c>
       <c r="BA95" t="inlineStr"/>
       <c r="BB95" t="inlineStr"/>
@@ -18508,7 +18508,7 @@
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>2Hl43AnC</t>
+          <t>SIOxI915</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -18516,76 +18516,76 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">hempel r 
+          <t xml:space="preserve">schroder r 
   ger </t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">sportpark ronhof thomas sommer
-  furth </t>
+          <t xml:space="preserve">donaustadion
+  ulm </t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>16626</v>
+        <v>19500</v>
       </c>
       <c r="F98" t="n">
-        <v>12664</v>
+        <v>17400</v>
       </c>
       <c r="G98" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" t="n">
+        <v>2</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>tbC3EcQn</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L98" t="n">
         <v>3</v>
       </c>
-      <c r="H98" t="n">
-        <v>1</v>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>CCQGbik8</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>zedZaSL7</t>
-        </is>
-      </c>
-      <c r="K98" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L98" t="n">
-        <v>3.65</v>
-      </c>
       <c r="M98" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="N98" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="O98" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="P98" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q98" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="R98" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S98" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T98" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>8E86CPuD</t>
+          <t>QevvB2nf</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>pdPRS0me</t>
+          <t>4bJLk19p</t>
         </is>
       </c>
       <c r="W98" t="n">
@@ -18600,71 +18600,55 @@
       <c r="Z98" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>6FDqshzF</t>
-        </is>
-      </c>
+      <c r="AA98" t="inlineStr"/>
       <c r="AB98" t="inlineStr"/>
-      <c r="AC98" t="n">
+      <c r="AC98" t="inlineStr"/>
+      <c r="AD98" t="inlineStr"/>
+      <c r="AE98" t="inlineStr"/>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="inlineStr"/>
+      <c r="AH98" t="inlineStr"/>
+      <c r="AI98" t="n">
         <v>25</v>
       </c>
-      <c r="AD98" t="n">
-        <v>183.1</v>
-      </c>
-      <c r="AE98" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF98" t="n">
-        <v>67</v>
-      </c>
-      <c r="AG98" t="n">
-        <v>1480000</v>
-      </c>
-      <c r="AH98" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="AI98" t="inlineStr"/>
-      <c r="AJ98" t="inlineStr"/>
-      <c r="AK98" t="inlineStr"/>
-      <c r="AL98" t="inlineStr"/>
-      <c r="AM98" t="inlineStr"/>
-      <c r="AN98" t="inlineStr"/>
-      <c r="AO98" t="n">
-        <v>22.72727272727273</v>
-      </c>
-      <c r="AP98" t="n">
-        <v>182.5454545454545</v>
-      </c>
-      <c r="AQ98" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR98" t="n">
-        <v>64.59090909090909</v>
-      </c>
-      <c r="AS98" t="n">
-        <v>1273863.636363636</v>
-      </c>
-      <c r="AT98" t="n">
-        <v>72.86363636363636</v>
-      </c>
+      <c r="AJ98" t="n">
+        <v>184.6363636363636</v>
+      </c>
+      <c r="AK98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL98" t="n">
+        <v>67.63636363636364</v>
+      </c>
+      <c r="AM98" t="n">
+        <v>1484090.909090909</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>70.63636363636364</v>
+      </c>
+      <c r="AO98" t="inlineStr"/>
+      <c r="AP98" t="inlineStr"/>
+      <c r="AQ98" t="inlineStr"/>
+      <c r="AR98" t="inlineStr"/>
+      <c r="AS98" t="inlineStr"/>
+      <c r="AT98" t="inlineStr"/>
       <c r="AU98" t="n">
-        <v>25.57142857142857</v>
+        <v>25.22222222222222</v>
       </c>
       <c r="AV98" t="n">
-        <v>181.8571428571429</v>
+        <v>180.9444444444445</v>
       </c>
       <c r="AW98" t="n">
         <v>1</v>
       </c>
       <c r="AX98" t="n">
-        <v>66.71428571428571</v>
+        <v>67.5</v>
       </c>
       <c r="AY98" t="n">
-        <v>1175000</v>
+        <v>1468055.555555556</v>
       </c>
       <c r="AZ98" t="n">
-        <v>68.42857142857143</v>
+        <v>71.11111111111111</v>
       </c>
       <c r="BA98" t="inlineStr"/>
       <c r="BB98" t="inlineStr"/>
@@ -18684,7 +18668,7 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>vJqPCEPP</t>
+          <t>2Hl43AnC</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
@@ -18692,43 +18676,43 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">kampka r 
+          <t xml:space="preserve">hempel r 
   ger </t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">merck stadion am bollenfalltor
-  darmstadt </t>
+          <t xml:space="preserve">sportpark ronhof thomas sommer
+  furth </t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>17810</v>
+        <v>16626</v>
       </c>
       <c r="F99" t="n">
-        <v>17810</v>
+        <v>12664</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>S0hPB9rA</t>
+          <t>CCQGbik8</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>ne1oL3y7</t>
+          <t>zedZaSL7</t>
         </is>
       </c>
       <c r="K99" t="n">
-        <v>0.79</v>
+        <v>3.3</v>
       </c>
       <c r="L99" t="n">
-        <v>1.49</v>
+        <v>3.65</v>
       </c>
       <c r="M99" t="n">
         <v>47</v>
@@ -18737,31 +18721,31 @@
         <v>53</v>
       </c>
       <c r="O99" t="n">
+        <v>22</v>
+      </c>
+      <c r="P99" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>9</v>
+      </c>
+      <c r="R99" t="n">
+        <v>5</v>
+      </c>
+      <c r="S99" t="n">
+        <v>9</v>
+      </c>
+      <c r="T99" t="n">
         <v>11</v>
       </c>
-      <c r="P99" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>6</v>
-      </c>
-      <c r="R99" t="n">
-        <v>4</v>
-      </c>
-      <c r="S99" t="n">
-        <v>16</v>
-      </c>
-      <c r="T99" t="n">
-        <v>7</v>
-      </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>MDhPV0RQ</t>
+          <t>8E86CPuD</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>AoL97rX8</t>
+          <t>pdPRS0me</t>
         </is>
       </c>
       <c r="W99" t="n">
@@ -18778,73 +18762,69 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr"/>
-      <c r="AD99" t="inlineStr"/>
-      <c r="AE99" t="inlineStr"/>
-      <c r="AF99" t="inlineStr"/>
-      <c r="AG99" t="inlineStr"/>
-      <c r="AH99" t="inlineStr"/>
-      <c r="AI99" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="AJ99" t="n">
-        <v>183.3</v>
-      </c>
-      <c r="AK99" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL99" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="AM99" t="n">
-        <v>2490000</v>
-      </c>
-      <c r="AN99" t="n">
-        <v>74</v>
-      </c>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr"/>
+      <c r="AC99" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>183.1</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>67</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>1480000</v>
+      </c>
+      <c r="AH99" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AI99" t="inlineStr"/>
+      <c r="AJ99" t="inlineStr"/>
+      <c r="AK99" t="inlineStr"/>
+      <c r="AL99" t="inlineStr"/>
+      <c r="AM99" t="inlineStr"/>
+      <c r="AN99" t="inlineStr"/>
       <c r="AO99" t="n">
-        <v>25.6875</v>
+        <v>22.72727272727273</v>
       </c>
       <c r="AP99" t="n">
-        <v>184.9375</v>
+        <v>182.5454545454545</v>
       </c>
       <c r="AQ99" t="n">
         <v>1</v>
       </c>
       <c r="AR99" t="n">
-        <v>68.75</v>
+        <v>64.59090909090909</v>
       </c>
       <c r="AS99" t="n">
-        <v>1679687.5</v>
+        <v>1273863.636363636</v>
       </c>
       <c r="AT99" t="n">
-        <v>73.1875</v>
+        <v>72.86363636363636</v>
       </c>
       <c r="AU99" t="n">
-        <v>21.95454545454545</v>
+        <v>25.57142857142857</v>
       </c>
       <c r="AV99" t="n">
-        <v>186.4545454545455</v>
+        <v>181.8571428571429</v>
       </c>
       <c r="AW99" t="n">
         <v>1</v>
       </c>
       <c r="AX99" t="n">
-        <v>64.04545454545455</v>
+        <v>66.71428571428571</v>
       </c>
       <c r="AY99" t="n">
-        <v>1346590.909090909</v>
+        <v>1175000</v>
       </c>
       <c r="AZ99" t="n">
-        <v>72.95454545454545</v>
+        <v>68.42857142857143</v>
       </c>
       <c r="BA99" t="inlineStr"/>
       <c r="BB99" t="inlineStr"/>
@@ -18864,7 +18844,7 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>SIOxI915</t>
+          <t>vJqPCEPP</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -18872,76 +18852,76 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">schroder r 
+          <t xml:space="preserve">kampka r 
   ger </t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">donaustadion
-  ulm </t>
+          <t xml:space="preserve">merck stadion am bollenfalltor
+  darmstadt </t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>19500</v>
+        <v>17810</v>
       </c>
       <c r="F100" t="n">
-        <v>17400</v>
+        <v>17810</v>
       </c>
       <c r="G100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
         <v>2</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>tbC3EcQn</t>
+          <t>S0hPB9rA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>naWckLmC</t>
+          <t>ne1oL3y7</t>
         </is>
       </c>
       <c r="K100" t="n">
-        <v>0.98</v>
+        <v>0.79</v>
       </c>
       <c r="L100" t="n">
-        <v>3</v>
+        <v>1.49</v>
       </c>
       <c r="M100" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="N100" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="O100" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P100" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q100" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R100" t="n">
         <v>4</v>
       </c>
       <c r="S100" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="T100" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>QevvB2nf</t>
+          <t>MDhPV0RQ</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>4bJLk19p</t>
+          <t>AoL97rX8</t>
         </is>
       </c>
       <c r="W100" t="n">
@@ -18956,8 +18936,16 @@
       <c r="Z100" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA100" t="inlineStr"/>
-      <c r="AB100" t="inlineStr"/>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
       <c r="AC100" t="inlineStr"/>
       <c r="AD100" t="inlineStr"/>
       <c r="AE100" t="inlineStr"/>
@@ -18965,46 +18953,58 @@
       <c r="AG100" t="inlineStr"/>
       <c r="AH100" t="inlineStr"/>
       <c r="AI100" t="n">
-        <v>25</v>
+        <v>26.3</v>
       </c>
       <c r="AJ100" t="n">
-        <v>184.6363636363636</v>
+        <v>183.3</v>
       </c>
       <c r="AK100" t="n">
         <v>1</v>
       </c>
       <c r="AL100" t="n">
-        <v>67.63636363636364</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="AM100" t="n">
-        <v>1484090.909090909</v>
+        <v>2490000</v>
       </c>
       <c r="AN100" t="n">
-        <v>70.63636363636364</v>
-      </c>
-      <c r="AO100" t="inlineStr"/>
-      <c r="AP100" t="inlineStr"/>
-      <c r="AQ100" t="inlineStr"/>
-      <c r="AR100" t="inlineStr"/>
-      <c r="AS100" t="inlineStr"/>
-      <c r="AT100" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="AO100" t="n">
+        <v>25.6875</v>
+      </c>
+      <c r="AP100" t="n">
+        <v>184.9375</v>
+      </c>
+      <c r="AQ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR100" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="AS100" t="n">
+        <v>1679687.5</v>
+      </c>
+      <c r="AT100" t="n">
+        <v>73.1875</v>
+      </c>
       <c r="AU100" t="n">
-        <v>25.22222222222222</v>
+        <v>21.95454545454545</v>
       </c>
       <c r="AV100" t="n">
-        <v>180.9444444444445</v>
+        <v>186.4545454545455</v>
       </c>
       <c r="AW100" t="n">
         <v>1</v>
       </c>
       <c r="AX100" t="n">
-        <v>67.5</v>
+        <v>64.04545454545455</v>
       </c>
       <c r="AY100" t="n">
-        <v>1468055.555555556</v>
+        <v>1346590.909090909</v>
       </c>
       <c r="AZ100" t="n">
-        <v>71.11111111111111</v>
+        <v>72.95454545454545</v>
       </c>
       <c r="BA100" t="inlineStr"/>
       <c r="BB100" t="inlineStr"/>
@@ -19216,7 +19216,7 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>OWxD1lHO</t>
+          <t>fiod5WHa</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
@@ -19224,76 +19224,76 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">haslberger w 
+          <t xml:space="preserve">bacher m 
   ger </t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">olympiastadion
-  berlin </t>
+          <t xml:space="preserve">heinz von heiden arena
+  hannover </t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>74667</v>
+        <v>49200</v>
       </c>
       <c r="F102" t="n">
-        <v>48591</v>
+        <v>31800</v>
       </c>
       <c r="G102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>UiCmEP56</t>
+        </is>
+      </c>
+      <c r="K102" t="n">
         <v>2</v>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>2y0u8Wrq</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>G2Op923t</t>
-        </is>
-      </c>
-      <c r="K102" t="n">
-        <v>1.4</v>
-      </c>
       <c r="L102" t="n">
-        <v>2.1</v>
+        <v>0.51</v>
       </c>
       <c r="M102" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N102" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O102" t="n">
+        <v>16</v>
+      </c>
+      <c r="P102" t="n">
         <v>10</v>
       </c>
-      <c r="P102" t="n">
-        <v>11</v>
-      </c>
       <c r="Q102" t="n">
+        <v>5</v>
+      </c>
+      <c r="R102" t="n">
         <v>3</v>
       </c>
-      <c r="R102" t="n">
-        <v>5</v>
-      </c>
       <c r="S102" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="T102" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>YmfcAeCo</t>
+          <t>t0ZPdkUl</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>0AI1QUJH</t>
+          <t>zyLSrbZQ</t>
         </is>
       </c>
       <c r="W102" t="n">
@@ -19308,80 +19308,60 @@
       <c r="Z102" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA102" t="inlineStr"/>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
       <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="n">
-        <v>24</v>
+        <v>26.4</v>
       </c>
       <c r="AD102" t="n">
-        <v>182.5</v>
+        <v>184.2</v>
       </c>
       <c r="AE102" t="n">
         <v>1.2</v>
       </c>
       <c r="AF102" t="n">
-        <v>69.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AG102" t="n">
-        <v>2390000</v>
+        <v>2082500</v>
       </c>
       <c r="AH102" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="AI102" t="n">
-        <v>25.125</v>
-      </c>
-      <c r="AJ102" t="n">
-        <v>183.625</v>
-      </c>
-      <c r="AK102" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL102" t="n">
-        <v>67</v>
-      </c>
-      <c r="AM102" t="n">
-        <v>1356250</v>
-      </c>
-      <c r="AN102" t="n">
-        <v>72</v>
-      </c>
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AI102" t="inlineStr"/>
+      <c r="AJ102" t="inlineStr"/>
+      <c r="AK102" t="inlineStr"/>
+      <c r="AL102" t="inlineStr"/>
+      <c r="AM102" t="inlineStr"/>
+      <c r="AN102" t="inlineStr"/>
       <c r="AO102" t="n">
-        <v>23.55</v>
+        <v>24.40909090909091</v>
       </c>
       <c r="AP102" t="n">
-        <v>184.2</v>
+        <v>183.4545454545455</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR102" t="n">
-        <v>69.25</v>
+        <v>68</v>
       </c>
       <c r="AS102" t="n">
-        <v>2360000</v>
+        <v>1812500</v>
       </c>
       <c r="AT102" t="n">
-        <v>74.75</v>
-      </c>
-      <c r="AU102" t="n">
-        <v>24.9375</v>
-      </c>
-      <c r="AV102" t="n">
-        <v>186.1875</v>
-      </c>
-      <c r="AW102" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX102" t="n">
-        <v>66.9375</v>
-      </c>
-      <c r="AY102" t="n">
-        <v>1417187.5</v>
-      </c>
-      <c r="AZ102" t="n">
-        <v>72.125</v>
-      </c>
+        <v>72.81818181818181</v>
+      </c>
+      <c r="AU102" t="inlineStr"/>
+      <c r="AV102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr"/>
+      <c r="AX102" t="inlineStr"/>
+      <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr"/>
       <c r="BA102" t="inlineStr"/>
       <c r="BB102" t="inlineStr"/>
       <c r="BC102" t="inlineStr"/>
@@ -19400,7 +19380,7 @@
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>fiod5WHa</t>
+          <t>OWxD1lHO</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
@@ -19408,76 +19388,76 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">bacher m 
+          <t xml:space="preserve">haslberger w 
   ger </t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">heinz von heiden arena
-  hannover </t>
+          <t xml:space="preserve">olympiastadion
+  berlin </t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>49200</v>
+        <v>74667</v>
       </c>
       <c r="F103" t="n">
-        <v>31800</v>
+        <v>48591</v>
       </c>
       <c r="G103" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" t="n">
         <v>2</v>
       </c>
-      <c r="H103" t="n">
-        <v>0</v>
-      </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>dfNCCCzS</t>
+          <t>2y0u8Wrq</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>UiCmEP56</t>
+          <t>G2Op923t</t>
         </is>
       </c>
       <c r="K103" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="L103" t="n">
-        <v>0.51</v>
+        <v>2.1</v>
       </c>
       <c r="M103" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N103" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O103" t="n">
+        <v>10</v>
+      </c>
+      <c r="P103" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>3</v>
+      </c>
+      <c r="R103" t="n">
+        <v>5</v>
+      </c>
+      <c r="S103" t="n">
         <v>16</v>
       </c>
-      <c r="P103" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>5</v>
-      </c>
-      <c r="R103" t="n">
-        <v>3</v>
-      </c>
-      <c r="S103" t="n">
-        <v>12</v>
-      </c>
       <c r="T103" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>t0ZPdkUl</t>
+          <t>YmfcAeCo</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>zyLSrbZQ</t>
+          <t>0AI1QUJH</t>
         </is>
       </c>
       <c r="W103" t="n">
@@ -19492,60 +19472,80 @@
       <c r="Z103" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA103" t="inlineStr">
-        <is>
-          <t>QqLCC3il</t>
-        </is>
-      </c>
+      <c r="AA103" t="inlineStr"/>
       <c r="AB103" t="inlineStr"/>
       <c r="AC103" t="n">
-        <v>26.4</v>
+        <v>24</v>
       </c>
       <c r="AD103" t="n">
-        <v>184.2</v>
+        <v>182.5</v>
       </c>
       <c r="AE103" t="n">
         <v>1.2</v>
       </c>
       <c r="AF103" t="n">
-        <v>70.40000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="AG103" t="n">
-        <v>2082500</v>
+        <v>2390000</v>
       </c>
       <c r="AH103" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="AI103" t="inlineStr"/>
-      <c r="AJ103" t="inlineStr"/>
-      <c r="AK103" t="inlineStr"/>
-      <c r="AL103" t="inlineStr"/>
-      <c r="AM103" t="inlineStr"/>
-      <c r="AN103" t="inlineStr"/>
+        <v>75.8</v>
+      </c>
+      <c r="AI103" t="n">
+        <v>25.125</v>
+      </c>
+      <c r="AJ103" t="n">
+        <v>183.625</v>
+      </c>
+      <c r="AK103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL103" t="n">
+        <v>67</v>
+      </c>
+      <c r="AM103" t="n">
+        <v>1356250</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>72</v>
+      </c>
       <c r="AO103" t="n">
-        <v>24.40909090909091</v>
+        <v>23.55</v>
       </c>
       <c r="AP103" t="n">
-        <v>183.4545454545455</v>
+        <v>184.2</v>
       </c>
       <c r="AQ103" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AR103" t="n">
-        <v>68</v>
+        <v>69.25</v>
       </c>
       <c r="AS103" t="n">
-        <v>1812500</v>
+        <v>2360000</v>
       </c>
       <c r="AT103" t="n">
-        <v>72.81818181818181</v>
-      </c>
-      <c r="AU103" t="inlineStr"/>
-      <c r="AV103" t="inlineStr"/>
-      <c r="AW103" t="inlineStr"/>
-      <c r="AX103" t="inlineStr"/>
-      <c r="AY103" t="inlineStr"/>
-      <c r="AZ103" t="inlineStr"/>
+        <v>74.75</v>
+      </c>
+      <c r="AU103" t="n">
+        <v>24.9375</v>
+      </c>
+      <c r="AV103" t="n">
+        <v>186.1875</v>
+      </c>
+      <c r="AW103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX103" t="n">
+        <v>66.9375</v>
+      </c>
+      <c r="AY103" t="n">
+        <v>1417187.5</v>
+      </c>
+      <c r="AZ103" t="n">
+        <v>72.125</v>
+      </c>
       <c r="BA103" t="inlineStr"/>
       <c r="BB103" t="inlineStr"/>
       <c r="BC103" t="inlineStr"/>
@@ -20867,226 +20867,6 @@
       <c r="BM110" t="inlineStr"/>
       <c r="BN110" t="inlineStr"/>
     </row>
-    <row r="111">
-      <c r="A111" s="1" t="inlineStr">
-        <is>
-          <t>dpwPbiGE</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="n">
-        <v>45435.64583333334</v>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">schroder r 
-  ger </t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vonovia ruhrstadion
-  bochum </t>
-        </is>
-      </c>
-      <c r="E111" t="n">
-        <v>26000</v>
-      </c>
-      <c r="F111" t="n">
-        <v>26000</v>
-      </c>
-      <c r="G111" t="n">
-        <v>0</v>
-      </c>
-      <c r="H111" t="n">
-        <v>3</v>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>8Y2m6ADe</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>ne1oL3y7</t>
-        </is>
-      </c>
-      <c r="K111" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="L111" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="M111" t="n">
-        <v>55</v>
-      </c>
-      <c r="N111" t="n">
-        <v>45</v>
-      </c>
-      <c r="O111" t="n">
-        <v>15</v>
-      </c>
-      <c r="P111" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q111" t="n">
-        <v>3</v>
-      </c>
-      <c r="R111" t="n">
-        <v>8</v>
-      </c>
-      <c r="S111" t="n">
-        <v>13</v>
-      </c>
-      <c r="T111" t="n">
-        <v>14</v>
-      </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>xzRzG0VI</t>
-        </is>
-      </c>
-      <c r="V111" t="inlineStr">
-        <is>
-          <t>AoL97rX8</t>
-        </is>
-      </c>
-      <c r="W111" t="n">
-        <v>59</v>
-      </c>
-      <c r="X111" t="n">
-        <v>591</v>
-      </c>
-      <c r="Y111" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z111" t="n">
-        <v>20232024</v>
-      </c>
-      <c r="AA111" t="inlineStr">
-        <is>
-          <t>0Ija0Ej9</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="AC111" t="n">
-        <v>28.09090909090909</v>
-      </c>
-      <c r="AD111" t="n">
-        <v>183.1818181818182</v>
-      </c>
-      <c r="AE111" t="n">
-        <v>1.181818181818182</v>
-      </c>
-      <c r="AF111" t="n">
-        <v>72.81818181818181</v>
-      </c>
-      <c r="AG111" t="n">
-        <v>3659090.909090909</v>
-      </c>
-      <c r="AH111" t="n">
-        <v>73.81818181818181</v>
-      </c>
-      <c r="AI111" t="n">
-        <v>26.36363636363636</v>
-      </c>
-      <c r="AJ111" t="n">
-        <v>185.5454545454545</v>
-      </c>
-      <c r="AK111" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL111" t="n">
-        <v>71.09090909090909</v>
-      </c>
-      <c r="AM111" t="n">
-        <v>2527272.727272727</v>
-      </c>
-      <c r="AN111" t="n">
-        <v>73.36363636363636</v>
-      </c>
-      <c r="AO111" t="n">
-        <v>27.28571428571428</v>
-      </c>
-      <c r="AP111" t="n">
-        <v>182.4761904761905</v>
-      </c>
-      <c r="AQ111" t="n">
-        <v>1.047619047619048</v>
-      </c>
-      <c r="AR111" t="n">
-        <v>71</v>
-      </c>
-      <c r="AS111" t="n">
-        <v>2392857.142857143</v>
-      </c>
-      <c r="AT111" t="n">
-        <v>73.95238095238095</v>
-      </c>
-      <c r="AU111" t="n">
-        <v>23.29166666666667</v>
-      </c>
-      <c r="AV111" t="n">
-        <v>183.7083333333333</v>
-      </c>
-      <c r="AW111" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX111" t="n">
-        <v>67.75</v>
-      </c>
-      <c r="AY111" t="n">
-        <v>2278125</v>
-      </c>
-      <c r="AZ111" t="n">
-        <v>73.45833333333333</v>
-      </c>
-      <c r="BA111" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB111" t="n">
-        <v>186.4</v>
-      </c>
-      <c r="BC111" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BD111" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE111" t="n">
-        <v>351</v>
-      </c>
-      <c r="BF111" t="n">
-        <v>6900000</v>
-      </c>
-      <c r="BG111" t="n">
-        <v>364</v>
-      </c>
-      <c r="BH111" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BI111" t="n">
-        <v>191.5</v>
-      </c>
-      <c r="BJ111" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK111" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL111" t="n">
-        <v>123</v>
-      </c>
-      <c r="BM111" t="n">
-        <v>3150000</v>
-      </c>
-      <c r="BN111" t="n">
-        <v>150</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
